--- a/leverage_journal.xlsx
+++ b/leverage_journal.xlsx
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>363.08</v>
+        <v>300.99</v>
       </c>
       <c r="C2" t="n">
         <v>50</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1872.04</v>
+        <v>1874.28</v>
       </c>
       <c r="C3" t="n">
         <v>50</v>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4121.4</v>
+        <v>4125.15</v>
       </c>
       <c r="C4" t="n">
         <v>50</v>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21424.64</v>
+        <v>21432.13</v>
       </c>
       <c r="C5" t="n">
         <v>50</v>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1641.85</v>
+        <v>1923.51</v>
       </c>
       <c r="C6" t="n">
         <v>50</v>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1089.17</v>
+        <v>-902.91</v>
       </c>
       <c r="C7" t="n">
         <v>50</v>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1722.53</v>
+        <v>-1412.1</v>
       </c>
       <c r="C8" t="n">
         <v>50</v>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6520.04</v>
+        <v>7140.9</v>
       </c>
       <c r="C9" t="n">
         <v>50</v>
@@ -1081,7 +1081,7 @@
         <v>0.10701</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07779</v>
+        <v>0.07554</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1093,13 +1093,13 @@
         <v>0.11</v>
       </c>
       <c r="J8" t="n">
-        <v>-27.31</v>
+        <v>-29.41</v>
       </c>
       <c r="K8" t="n">
         <v>-0.03</v>
       </c>
       <c r="L8" t="n">
-        <v>-81.92</v>
+        <v>-88.23</v>
       </c>
       <c r="M8" t="n">
         <v>-0.09</v>
@@ -1621,7 +1621,7 @@
         <v>0.002129</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00194</v>
+        <v>0.001958</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1633,30 +1633,30 @@
         <v>102.52</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.880000000000001</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-9.1</v>
+        <v>-8.23</v>
       </c>
       <c r="L16" t="n">
-        <v>-26.63</v>
+        <v>-24.1</v>
       </c>
       <c r="M16" t="n">
-        <v>-27.3</v>
+        <v>-24.7</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>-44.39</v>
+        <v>-40.16</v>
       </c>
       <c r="P16" t="n">
-        <v>-45.51</v>
+        <v>-41.17</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>-88.77</v>
+        <v>-80.31999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>-91.01000000000001</v>
+        <v>-82.34</v>
       </c>
       <c r="T16" t="inlineStr"/>
     </row>
@@ -2009,7 +2009,7 @@
         <v>2.68</v>
       </c>
       <c r="F22" t="n">
-        <v>2.585</v>
+        <v>2.531</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2021,30 +2021,30 @@
         <v>5.87</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.54</v>
+        <v>-5.56</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.21</v>
+        <v>-0.33</v>
       </c>
       <c r="L22" t="n">
-        <v>-10.63</v>
+        <v>-16.68</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.62</v>
+        <v>-0.98</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>-17.72</v>
+        <v>-27.8</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.04</v>
+        <v>-1.63</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>-35.45</v>
+        <v>-55.6</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.08</v>
+        <v>-3.26</v>
       </c>
       <c r="T22" t="inlineStr"/>
     </row>
@@ -3545,7 +3545,7 @@
         <v>0.1769</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0872</v>
+        <v>0.0798</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3557,10 +3557,10 @@
         <v>1502.06</v>
       </c>
       <c r="J46" t="n">
-        <v>-50.71</v>
+        <v>-54.89</v>
       </c>
       <c r="K46" t="n">
-        <v>-761.64</v>
+        <v>-824.48</v>
       </c>
       <c r="L46" t="n">
         <v>-100</v>
@@ -4542,7 +4542,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07779</v>
+        <v>0.07554</v>
       </c>
       <c r="F8" t="n">
         <v>0.10701</v>
@@ -4557,30 +4557,30 @@
         <v>0.11</v>
       </c>
       <c r="J8" t="n">
-        <v>37.56</v>
+        <v>41.66</v>
       </c>
       <c r="K8" t="n">
         <v>0.04</v>
       </c>
       <c r="L8" t="n">
-        <v>81.92</v>
+        <v>88.23</v>
       </c>
       <c r="M8" t="n">
         <v>0.09</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>136.53</v>
+        <v>147.04</v>
       </c>
       <c r="P8" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>273.06</v>
+        <v>294.08</v>
       </c>
       <c r="S8" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="T8" t="inlineStr"/>
     </row>
@@ -5050,7 +5050,7 @@
         <v>48154</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00194</v>
+        <v>0.001958</v>
       </c>
       <c r="F16" t="n">
         <v>0.002129</v>
@@ -5065,30 +5065,30 @@
         <v>102.52</v>
       </c>
       <c r="J16" t="n">
-        <v>9.74</v>
+        <v>8.73</v>
       </c>
       <c r="K16" t="n">
-        <v>9.99</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>26.63</v>
+        <v>24.1</v>
       </c>
       <c r="M16" t="n">
-        <v>27.3</v>
+        <v>24.7</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>44.39</v>
+        <v>40.16</v>
       </c>
       <c r="P16" t="n">
-        <v>45.51</v>
+        <v>41.17</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>88.77</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>91.01000000000001</v>
+        <v>82.34</v>
       </c>
       <c r="T16" t="inlineStr"/>
     </row>
@@ -5446,7 +5446,7 @@
         <v>2.19</v>
       </c>
       <c r="E22" t="n">
-        <v>2.585</v>
+        <v>2.531</v>
       </c>
       <c r="F22" t="n">
         <v>2.68</v>
@@ -5461,30 +5461,30 @@
         <v>5.87</v>
       </c>
       <c r="J22" t="n">
-        <v>3.68</v>
+        <v>5.89</v>
       </c>
       <c r="K22" t="n">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="L22" t="n">
-        <v>10.63</v>
+        <v>16.68</v>
       </c>
       <c r="M22" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>17.72</v>
+        <v>27.8</v>
       </c>
       <c r="P22" t="n">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>35.45</v>
+        <v>55.6</v>
       </c>
       <c r="S22" t="n">
-        <v>2.08</v>
+        <v>3.26</v>
       </c>
       <c r="T22" t="inlineStr"/>
     </row>
@@ -6994,7 +6994,7 @@
         <v>8491</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0872</v>
+        <v>0.0798</v>
       </c>
       <c r="F46" t="n">
         <v>0.1769</v>
@@ -7009,30 +7009,30 @@
         <v>1502.06</v>
       </c>
       <c r="J46" t="n">
-        <v>102.87</v>
+        <v>121.68</v>
       </c>
       <c r="K46" t="n">
-        <v>1545.12</v>
+        <v>1827.69</v>
       </c>
       <c r="L46" t="n">
-        <v>152.12</v>
+        <v>164.67</v>
       </c>
       <c r="M46" t="n">
-        <v>2284.93</v>
+        <v>2473.43</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
-        <v>253.53</v>
+        <v>274.45</v>
       </c>
       <c r="P46" t="n">
-        <v>3808.21</v>
+        <v>4122.38</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="n">
-        <v>507.07</v>
+        <v>548.9</v>
       </c>
       <c r="S46" t="n">
-        <v>7616.43</v>
+        <v>8244.76</v>
       </c>
       <c r="T46" t="inlineStr"/>
     </row>

--- a/leverage_journal.xlsx
+++ b/leverage_journal.xlsx
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>300.99</v>
+        <v>231.86</v>
       </c>
       <c r="C2" t="n">
         <v>50</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1874.28</v>
+        <v>1750.95</v>
       </c>
       <c r="C3" t="n">
         <v>50</v>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4125.15</v>
+        <v>3919.62</v>
       </c>
       <c r="C4" t="n">
         <v>50</v>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21432.13</v>
+        <v>21021.1</v>
       </c>
       <c r="C5" t="n">
         <v>50</v>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1923.51</v>
+        <v>2109.3</v>
       </c>
       <c r="C6" t="n">
         <v>50</v>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-902.91</v>
+        <v>-695.52</v>
       </c>
       <c r="C7" t="n">
         <v>50</v>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1412.1</v>
+        <v>-1066.46</v>
       </c>
       <c r="C8" t="n">
         <v>50</v>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7140.9</v>
+        <v>7832.15</v>
       </c>
       <c r="C9" t="n">
         <v>50</v>
@@ -713,7 +713,7 @@
         <v>1.589</v>
       </c>
       <c r="F2" t="n">
-        <v>1.447</v>
+        <v>1.462</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -725,30 +725,30 @@
         <v>20.04</v>
       </c>
       <c r="J2" t="n">
-        <v>-8.94</v>
+        <v>-7.99</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.79</v>
+        <v>-1.6</v>
       </c>
       <c r="L2" t="n">
-        <v>-26.81</v>
+        <v>-23.98</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.37</v>
+        <v>-4.8</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>-44.68</v>
+        <v>-39.96</v>
       </c>
       <c r="P2" t="n">
-        <v>-8.949999999999999</v>
+        <v>-8.01</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>-89.36</v>
+        <v>-79.92</v>
       </c>
       <c r="S2" t="n">
-        <v>-17.91</v>
+        <v>-16.01</v>
       </c>
       <c r="T2" t="inlineStr"/>
     </row>
@@ -773,7 +773,7 @@
         <v>1.588</v>
       </c>
       <c r="F3" t="n">
-        <v>1.447</v>
+        <v>1.462</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -785,30 +785,30 @@
         <v>19.99</v>
       </c>
       <c r="J3" t="n">
-        <v>-8.880000000000001</v>
+        <v>-7.93</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.77</v>
+        <v>-1.59</v>
       </c>
       <c r="L3" t="n">
-        <v>-26.64</v>
+        <v>-23.8</v>
       </c>
       <c r="M3" t="n">
-        <v>-5.32</v>
+        <v>-4.76</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>-44.4</v>
+        <v>-39.67</v>
       </c>
       <c r="P3" t="n">
-        <v>-8.869999999999999</v>
+        <v>-7.93</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>-88.79000000000001</v>
+        <v>-79.34999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>-17.75</v>
+        <v>-15.86</v>
       </c>
       <c r="T3" t="inlineStr"/>
     </row>
@@ -833,7 +833,7 @@
         <v>1.59</v>
       </c>
       <c r="F4" t="n">
-        <v>1.447</v>
+        <v>1.462</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -845,30 +845,30 @@
         <v>20.01</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.99</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.8</v>
+        <v>-1.61</v>
       </c>
       <c r="L4" t="n">
-        <v>-26.98</v>
+        <v>-24.15</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.4</v>
+        <v>-4.83</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>-44.97</v>
+        <v>-40.25</v>
       </c>
       <c r="P4" t="n">
-        <v>-9</v>
+        <v>-8.06</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>-89.94</v>
+        <v>-80.5</v>
       </c>
       <c r="S4" t="n">
-        <v>-18</v>
+        <v>-16.11</v>
       </c>
       <c r="T4" t="inlineStr"/>
     </row>
@@ -1081,7 +1081,7 @@
         <v>0.10701</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07554</v>
+        <v>0.07357</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1093,16 +1093,16 @@
         <v>0.11</v>
       </c>
       <c r="J8" t="n">
-        <v>-29.41</v>
+        <v>-31.25</v>
       </c>
       <c r="K8" t="n">
         <v>-0.03</v>
       </c>
       <c r="L8" t="n">
-        <v>-88.23</v>
+        <v>-93.75</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -1621,7 +1621,7 @@
         <v>0.002129</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001958</v>
+        <v>0.001969</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1633,30 +1633,30 @@
         <v>102.52</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.029999999999999</v>
+        <v>-7.52</v>
       </c>
       <c r="K16" t="n">
-        <v>-8.23</v>
+        <v>-7.7</v>
       </c>
       <c r="L16" t="n">
-        <v>-24.1</v>
+        <v>-22.55</v>
       </c>
       <c r="M16" t="n">
-        <v>-24.7</v>
+        <v>-23.11</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>-40.16</v>
+        <v>-37.58</v>
       </c>
       <c r="P16" t="n">
-        <v>-41.17</v>
+        <v>-38.52</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>-80.31999999999999</v>
+        <v>-75.15000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>-82.34</v>
+        <v>-77.05</v>
       </c>
       <c r="T16" t="inlineStr"/>
     </row>
@@ -2009,7 +2009,7 @@
         <v>2.68</v>
       </c>
       <c r="F22" t="n">
-        <v>2.531</v>
+        <v>2.495</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2021,30 +2021,30 @@
         <v>5.87</v>
       </c>
       <c r="J22" t="n">
-        <v>-5.56</v>
+        <v>-6.9</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.33</v>
+        <v>-0.41</v>
       </c>
       <c r="L22" t="n">
-        <v>-16.68</v>
+        <v>-20.71</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.98</v>
+        <v>-1.22</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>-27.8</v>
+        <v>-34.51</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.63</v>
+        <v>-2.03</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>-55.6</v>
+        <v>-69.03</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.26</v>
+        <v>-4.05</v>
       </c>
       <c r="T22" t="inlineStr"/>
     </row>
@@ -3545,7 +3545,7 @@
         <v>0.1769</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0798</v>
+        <v>0.0765</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3557,10 +3557,10 @@
         <v>1502.06</v>
       </c>
       <c r="J46" t="n">
-        <v>-54.89</v>
+        <v>-56.76</v>
       </c>
       <c r="K46" t="n">
-        <v>-824.48</v>
+        <v>-852.5</v>
       </c>
       <c r="L46" t="n">
         <v>-100</v>
@@ -3617,7 +3617,7 @@
         <v>0.1668545406313555</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1627</v>
+        <v>0.1623</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3629,30 +3629,30 @@
         <v>2264.35</v>
       </c>
       <c r="J47" t="n">
-        <v>-2.49</v>
+        <v>-2.73</v>
       </c>
       <c r="K47" t="n">
-        <v>-56.38</v>
+        <v>-61.81</v>
       </c>
       <c r="L47" t="n">
-        <v>-7.47</v>
+        <v>-8.19</v>
       </c>
       <c r="M47" t="n">
-        <v>-169.14</v>
+        <v>-185.43</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
-        <v>-12.45</v>
+        <v>-13.65</v>
       </c>
       <c r="P47" t="n">
-        <v>-281.9</v>
+        <v>-309.04</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="n">
-        <v>-24.9</v>
+        <v>-27.3</v>
       </c>
       <c r="S47" t="n">
-        <v>-563.8</v>
+        <v>-618.09</v>
       </c>
       <c r="T47" t="inlineStr"/>
     </row>
@@ -3869,7 +3869,7 @@
         <v>0.0675</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0672</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3881,30 +3881,30 @@
         <v>2251.56</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.44</v>
+        <v>-2.07</v>
       </c>
       <c r="K51" t="n">
-        <v>-10.01</v>
+        <v>-46.7</v>
       </c>
       <c r="L51" t="n">
-        <v>-1.33</v>
+        <v>-6.22</v>
       </c>
       <c r="M51" t="n">
-        <v>-30.02</v>
+        <v>-140.1</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
-        <v>-2.22</v>
+        <v>-10.37</v>
       </c>
       <c r="P51" t="n">
-        <v>-50.03</v>
+        <v>-233.49</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="n">
-        <v>-4.44</v>
+        <v>-20.74</v>
       </c>
       <c r="S51" t="n">
-        <v>-100.07</v>
+        <v>-466.99</v>
       </c>
       <c r="T51" t="inlineStr"/>
     </row>
@@ -4162,7 +4162,7 @@
         <v>12.61</v>
       </c>
       <c r="E2" t="n">
-        <v>1.447</v>
+        <v>1.462</v>
       </c>
       <c r="F2" t="n">
         <v>1.589</v>
@@ -4177,30 +4177,30 @@
         <v>20.04</v>
       </c>
       <c r="J2" t="n">
-        <v>9.81</v>
+        <v>8.69</v>
       </c>
       <c r="K2" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="L2" t="n">
-        <v>26.81</v>
+        <v>23.98</v>
       </c>
       <c r="M2" t="n">
-        <v>5.37</v>
+        <v>4.8</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>44.68</v>
+        <v>39.96</v>
       </c>
       <c r="P2" t="n">
-        <v>8.949999999999999</v>
+        <v>8.01</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>89.36</v>
+        <v>79.92</v>
       </c>
       <c r="S2" t="n">
-        <v>17.91</v>
+        <v>16.01</v>
       </c>
       <c r="T2" t="inlineStr"/>
     </row>
@@ -4222,7 +4222,7 @@
         <v>12.586</v>
       </c>
       <c r="E3" t="n">
-        <v>1.447</v>
+        <v>1.462</v>
       </c>
       <c r="F3" t="n">
         <v>1.588</v>
@@ -4237,30 +4237,30 @@
         <v>19.99</v>
       </c>
       <c r="J3" t="n">
-        <v>9.74</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="L3" t="n">
-        <v>26.64</v>
+        <v>23.8</v>
       </c>
       <c r="M3" t="n">
-        <v>5.32</v>
+        <v>4.76</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>44.4</v>
+        <v>39.67</v>
       </c>
       <c r="P3" t="n">
-        <v>8.869999999999999</v>
+        <v>7.93</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>88.79000000000001</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>17.75</v>
+        <v>15.86</v>
       </c>
       <c r="T3" t="inlineStr"/>
     </row>
@@ -4282,7 +4282,7 @@
         <v>12.586</v>
       </c>
       <c r="E4" t="n">
-        <v>1.447</v>
+        <v>1.462</v>
       </c>
       <c r="F4" t="n">
         <v>1.59</v>
@@ -4297,30 +4297,30 @@
         <v>20.01</v>
       </c>
       <c r="J4" t="n">
-        <v>9.880000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="K4" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="L4" t="n">
-        <v>26.98</v>
+        <v>24.15</v>
       </c>
       <c r="M4" t="n">
-        <v>5.4</v>
+        <v>4.83</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>44.97</v>
+        <v>40.25</v>
       </c>
       <c r="P4" t="n">
-        <v>9</v>
+        <v>8.06</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>89.94</v>
+        <v>80.5</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>16.11</v>
       </c>
       <c r="T4" t="inlineStr"/>
     </row>
@@ -4542,7 +4542,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07554</v>
+        <v>0.07357</v>
       </c>
       <c r="F8" t="n">
         <v>0.10701</v>
@@ -4557,30 +4557,30 @@
         <v>0.11</v>
       </c>
       <c r="J8" t="n">
-        <v>41.66</v>
+        <v>45.45</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="L8" t="n">
-        <v>88.23</v>
+        <v>93.75</v>
       </c>
       <c r="M8" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>147.04</v>
+        <v>156.25</v>
       </c>
       <c r="P8" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>294.08</v>
+        <v>312.49</v>
       </c>
       <c r="S8" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="T8" t="inlineStr"/>
     </row>
@@ -5050,7 +5050,7 @@
         <v>48154</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001958</v>
+        <v>0.001969</v>
       </c>
       <c r="F16" t="n">
         <v>0.002129</v>
@@ -5065,30 +5065,30 @@
         <v>102.52</v>
       </c>
       <c r="J16" t="n">
-        <v>8.73</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>8.949999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="L16" t="n">
-        <v>24.1</v>
+        <v>22.55</v>
       </c>
       <c r="M16" t="n">
-        <v>24.7</v>
+        <v>23.11</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>40.16</v>
+        <v>37.58</v>
       </c>
       <c r="P16" t="n">
-        <v>41.17</v>
+        <v>38.52</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>80.31999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>82.34</v>
+        <v>77.05</v>
       </c>
       <c r="T16" t="inlineStr"/>
     </row>
@@ -5446,7 +5446,7 @@
         <v>2.19</v>
       </c>
       <c r="E22" t="n">
-        <v>2.531</v>
+        <v>2.495</v>
       </c>
       <c r="F22" t="n">
         <v>2.68</v>
@@ -5461,30 +5461,30 @@
         <v>5.87</v>
       </c>
       <c r="J22" t="n">
-        <v>5.89</v>
+        <v>7.41</v>
       </c>
       <c r="K22" t="n">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="L22" t="n">
-        <v>16.68</v>
+        <v>20.71</v>
       </c>
       <c r="M22" t="n">
-        <v>0.98</v>
+        <v>1.22</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>27.8</v>
+        <v>34.51</v>
       </c>
       <c r="P22" t="n">
-        <v>1.63</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>55.6</v>
+        <v>69.03</v>
       </c>
       <c r="S22" t="n">
-        <v>3.26</v>
+        <v>4.05</v>
       </c>
       <c r="T22" t="inlineStr"/>
     </row>
@@ -6994,7 +6994,7 @@
         <v>8491</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0798</v>
+        <v>0.0765</v>
       </c>
       <c r="F46" t="n">
         <v>0.1769</v>
@@ -7009,30 +7009,30 @@
         <v>1502.06</v>
       </c>
       <c r="J46" t="n">
-        <v>121.68</v>
+        <v>131.24</v>
       </c>
       <c r="K46" t="n">
-        <v>1827.69</v>
+        <v>1971.33</v>
       </c>
       <c r="L46" t="n">
-        <v>164.67</v>
+        <v>170.27</v>
       </c>
       <c r="M46" t="n">
-        <v>2473.43</v>
+        <v>2557.49</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
-        <v>274.45</v>
+        <v>283.78</v>
       </c>
       <c r="P46" t="n">
-        <v>4122.38</v>
+        <v>4262.48</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="n">
-        <v>548.9</v>
+        <v>567.55</v>
       </c>
       <c r="S46" t="n">
-        <v>8244.76</v>
+        <v>8524.959999999999</v>
       </c>
       <c r="T46" t="inlineStr"/>
     </row>
@@ -7054,7 +7054,7 @@
         <v>13570.8</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1627</v>
+        <v>0.1623</v>
       </c>
       <c r="F47" t="n">
         <v>0.1668545406313555</v>
@@ -7069,30 +7069,30 @@
         <v>2264.35</v>
       </c>
       <c r="J47" t="n">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="K47" t="n">
-        <v>57.82</v>
+        <v>63.54</v>
       </c>
       <c r="L47" t="n">
-        <v>7.47</v>
+        <v>8.19</v>
       </c>
       <c r="M47" t="n">
-        <v>169.14</v>
+        <v>185.43</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
-        <v>12.45</v>
+        <v>13.65</v>
       </c>
       <c r="P47" t="n">
-        <v>281.9</v>
+        <v>309.04</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="n">
-        <v>24.9</v>
+        <v>27.3</v>
       </c>
       <c r="S47" t="n">
-        <v>563.8</v>
+        <v>618.09</v>
       </c>
       <c r="T47" t="inlineStr"/>
     </row>
@@ -7318,7 +7318,7 @@
         <v>33356.4</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0672</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="F51" t="n">
         <v>0.0675</v>
@@ -7333,30 +7333,30 @@
         <v>2251.56</v>
       </c>
       <c r="J51" t="n">
-        <v>0.45</v>
+        <v>2.12</v>
       </c>
       <c r="K51" t="n">
-        <v>10.05</v>
+        <v>47.69</v>
       </c>
       <c r="L51" t="n">
-        <v>1.33</v>
+        <v>6.22</v>
       </c>
       <c r="M51" t="n">
-        <v>30.02</v>
+        <v>140.1</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
-        <v>2.22</v>
+        <v>10.37</v>
       </c>
       <c r="P51" t="n">
-        <v>50.03</v>
+        <v>233.49</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="n">
-        <v>4.44</v>
+        <v>20.74</v>
       </c>
       <c r="S51" t="n">
-        <v>100.07</v>
+        <v>466.99</v>
       </c>
       <c r="T51" t="inlineStr"/>
     </row>

--- a/leverage_journal.xlsx
+++ b/leverage_journal.xlsx
@@ -459,10 +459,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>231.86</v>
+        <v>-232.95</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>45.6</v>
       </c>
       <c r="D2" t="inlineStr"/>
     </row>
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1750.95</v>
+        <v>888.99</v>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>45.6</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3919.62</v>
+        <v>2482.98</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>45.6</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21021.1</v>
+        <v>18967.34</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>45.6</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2109.3</v>
+        <v>3991.18</v>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>52.9</v>
       </c>
       <c r="D6" t="inlineStr"/>
     </row>
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-695.52</v>
+        <v>742.51</v>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>52.9</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1066.46</v>
+        <v>2229.88</v>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>52.9</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7832.15</v>
+        <v>15984.55</v>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>54.4</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T53"/>
+  <dimension ref="A1:T69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,7 +713,7 @@
         <v>1.589</v>
       </c>
       <c r="F2" t="n">
-        <v>1.462</v>
+        <v>1.426</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -725,32 +725,36 @@
         <v>20.04</v>
       </c>
       <c r="J2" t="n">
-        <v>-7.99</v>
+        <v>-10.26</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.6</v>
+        <v>-2.06</v>
       </c>
       <c r="L2" t="n">
-        <v>-23.98</v>
+        <v>-30.77</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.8</v>
+        <v>-6.17</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>-39.96</v>
+        <v>-51.29</v>
       </c>
       <c r="P2" t="n">
-        <v>-8.01</v>
+        <v>-10.28</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>-79.92</v>
+        <v>-100</v>
       </c>
       <c r="S2" t="n">
-        <v>-16.01</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
+        <v>-20.04</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -773,7 +777,7 @@
         <v>1.588</v>
       </c>
       <c r="F3" t="n">
-        <v>1.462</v>
+        <v>1.426</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -785,32 +789,36 @@
         <v>19.99</v>
       </c>
       <c r="J3" t="n">
-        <v>-7.93</v>
+        <v>-10.2</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.59</v>
+        <v>-2.04</v>
       </c>
       <c r="L3" t="n">
-        <v>-23.8</v>
+        <v>-30.6</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.76</v>
+        <v>-6.12</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>-39.67</v>
+        <v>-51.01</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.93</v>
+        <v>-10.19</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>-79.34999999999999</v>
+        <v>-100</v>
       </c>
       <c r="S3" t="n">
-        <v>-15.86</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
+        <v>-19.99</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -833,7 +841,7 @@
         <v>1.59</v>
       </c>
       <c r="F4" t="n">
-        <v>1.462</v>
+        <v>1.426</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -845,32 +853,36 @@
         <v>20.01</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.050000000000001</v>
+        <v>-10.31</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.61</v>
+        <v>-2.06</v>
       </c>
       <c r="L4" t="n">
-        <v>-24.15</v>
+        <v>-30.94</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.83</v>
+        <v>-6.19</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>-40.25</v>
+        <v>-51.57</v>
       </c>
       <c r="P4" t="n">
-        <v>-8.06</v>
+        <v>-10.32</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>-80.5</v>
+        <v>-100</v>
       </c>
       <c r="S4" t="n">
-        <v>-16.11</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
+        <v>-20.01</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -883,52 +895,56 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37807</v>
+        <v>37769</v>
       </c>
       <c r="E5" t="n">
         <v>0.000529</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000501</v>
+        <v>0.000511</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>2026-07-26 20:50</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:27</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>19.98</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.29</v>
+        <v>-3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.06</v>
+        <v>-0.68</v>
       </c>
       <c r="L5" t="n">
-        <v>-15.88</v>
+        <v>-10.21</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.18</v>
+        <v>-2.04</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>-26.47</v>
+        <v>-17.01</v>
       </c>
       <c r="P5" t="n">
-        <v>-5.29</v>
+        <v>-3.4</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>-52.93</v>
+        <v>-34.03</v>
       </c>
       <c r="S5" t="n">
-        <v>-10.59</v>
+        <v>-6.8</v>
       </c>
       <c r="T5" t="inlineStr"/>
     </row>
@@ -938,61 +954,57 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>MEME</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>123</v>
+        <v>38</v>
       </c>
       <c r="E6" t="n">
-        <v>0.10701</v>
+        <v>0.000529</v>
       </c>
       <c r="F6" t="n">
-        <v>0.12306</v>
+        <v>0.00051</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-26 21:08</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-07-27 00:05</t>
-        </is>
-      </c>
+          <t>2026-07-26 20:50</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>13.16</v>
+        <v>0.02</v>
       </c>
       <c r="J6" t="n">
-        <v>15</v>
+        <v>-3.59</v>
       </c>
       <c r="K6" t="n">
-        <v>1.97</v>
+        <v>-0</v>
       </c>
       <c r="L6" t="n">
-        <v>45</v>
+        <v>-10.78</v>
       </c>
       <c r="M6" t="n">
-        <v>5.92</v>
+        <v>-0</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>74.98999999999999</v>
+        <v>-17.96</v>
       </c>
       <c r="P6" t="n">
-        <v>9.869999999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>149.99</v>
+        <v>-35.92</v>
       </c>
       <c r="S6" t="n">
-        <v>19.74</v>
+        <v>-0.01</v>
       </c>
       <c r="T6" t="inlineStr"/>
     </row>
@@ -1011,13 +1023,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="E7" t="n">
         <v>0.10701</v>
       </c>
       <c r="F7" t="n">
-        <v>0.13911</v>
+        <v>0.12306</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1030,33 +1042,33 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>6.63</v>
+        <v>13.16</v>
       </c>
       <c r="J7" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="L7" t="n">
-        <v>89.98999999999999</v>
+        <v>45</v>
       </c>
       <c r="M7" t="n">
-        <v>5.97</v>
+        <v>5.92</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>149.99</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>9.949999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>299.97</v>
+        <v>149.99</v>
       </c>
       <c r="S7" t="n">
-        <v>19.9</v>
+        <v>19.74</v>
       </c>
       <c r="T7" t="inlineStr"/>
     </row>
@@ -1071,62 +1083,58 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="E8" t="n">
         <v>0.10701</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07357</v>
+        <v>0.13911</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>2026-07-26 21:08</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:05</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>0.11</v>
+        <v>6.63</v>
       </c>
       <c r="J8" t="n">
-        <v>-31.25</v>
+        <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.03</v>
+        <v>1.99</v>
       </c>
       <c r="L8" t="n">
-        <v>-93.75</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1</v>
+        <v>5.97</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>-100</v>
+        <v>149.99</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>9.949999999999999</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>-100</v>
+        <v>299.97</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>19.9</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1134,7 +1142,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1143,58 +1151,54 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>30.6</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4356</v>
+        <v>0.10701</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3689</v>
+        <v>0.09925</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-27 07:10</t>
+          <t>2026-07-26 21:08</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:13</t>
+          <t>2026-07-31 05:20</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>13.33</v>
+        <v>0.11</v>
       </c>
       <c r="J9" t="n">
-        <v>-15.31</v>
+        <v>-7.25</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.04</v>
+        <v>-0.01</v>
       </c>
       <c r="L9" t="n">
-        <v>-45.94</v>
+        <v>-21.75</v>
       </c>
       <c r="M9" t="n">
-        <v>-6.12</v>
+        <v>-0.02</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>-76.56</v>
+        <v>-36.26</v>
       </c>
       <c r="P9" t="n">
-        <v>-10.21</v>
+        <v>-0.04</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>-100</v>
+        <v>-72.52</v>
       </c>
       <c r="S9" t="n">
-        <v>-13.33</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>-0.08</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1211,7 +1215,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>30.6</v>
       </c>
       <c r="E10" t="n">
         <v>0.4356</v>
@@ -1230,33 +1234,33 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6.66</v>
+        <v>13.33</v>
       </c>
       <c r="J10" t="n">
         <v>-15.31</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.02</v>
+        <v>-2.04</v>
       </c>
       <c r="L10" t="n">
         <v>-45.94</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.06</v>
+        <v>-6.12</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
         <v>-76.56</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.1</v>
+        <v>-10.21</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
         <v>-100</v>
       </c>
       <c r="S10" t="n">
-        <v>-6.66</v>
+        <v>-13.33</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1270,7 +1274,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1279,52 +1283,52 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>53871.4</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1805085023364255</v>
+        <v>0.4356</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1529837884294821</v>
+        <v>0.3689</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-27 07:20</t>
+          <t>2026-07-27 07:10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-27 15:10</t>
+          <t>2026-07-27 08:13</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>9724.25</v>
+        <v>6.66</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.25</v>
+        <v>-15.31</v>
       </c>
       <c r="K11" t="n">
-        <v>-1482.79</v>
+        <v>-1.02</v>
       </c>
       <c r="L11" t="n">
-        <v>-45.75</v>
+        <v>-45.94</v>
       </c>
       <c r="M11" t="n">
-        <v>-4448.38</v>
+        <v>-3.06</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>-76.23999999999999</v>
+        <v>-76.56</v>
       </c>
       <c r="P11" t="n">
-        <v>-7413.97</v>
+        <v>-5.1</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
         <v>-100</v>
       </c>
       <c r="S11" t="n">
-        <v>-9724.25</v>
+        <v>-6.66</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1347,13 +1351,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>26935.8</v>
+        <v>53871.4</v>
       </c>
       <c r="E12" t="n">
         <v>0.1805085023364255</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1529</v>
+        <v>0.1529837884294821</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1366,33 +1370,33 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4862.14</v>
+        <v>9724.25</v>
       </c>
       <c r="J12" t="n">
-        <v>-15.29</v>
+        <v>-15.25</v>
       </c>
       <c r="K12" t="n">
-        <v>-743.66</v>
+        <v>-1482.79</v>
       </c>
       <c r="L12" t="n">
-        <v>-45.88</v>
+        <v>-45.75</v>
       </c>
       <c r="M12" t="n">
-        <v>-2230.97</v>
+        <v>-4448.38</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>-76.47</v>
+        <v>-76.23999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-3718.29</v>
+        <v>-7413.97</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
         <v>-100</v>
       </c>
       <c r="S12" t="n">
-        <v>-4862.14</v>
+        <v>-9724.25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1406,7 +1410,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KAITO</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1415,54 +1419,58 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6823</v>
+        <v>26935.8</v>
       </c>
       <c r="E13" t="n">
-        <v>1.194796722849186</v>
+        <v>0.1805085023364255</v>
       </c>
       <c r="F13" t="n">
-        <v>1.305925994430602</v>
+        <v>0.1529</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-27 07:30</t>
+          <t>2026-07-27 07:20</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-27 21:51</t>
+          <t>2026-07-27 15:10</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8152.1</v>
+        <v>4862.14</v>
       </c>
       <c r="J13" t="n">
-        <v>9.300000000000001</v>
+        <v>-15.29</v>
       </c>
       <c r="K13" t="n">
-        <v>758.24</v>
+        <v>-743.66</v>
       </c>
       <c r="L13" t="n">
-        <v>27.9</v>
+        <v>-45.88</v>
       </c>
       <c r="M13" t="n">
-        <v>2274.71</v>
+        <v>-2230.97</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>46.51</v>
+        <v>-76.47</v>
       </c>
       <c r="P13" t="n">
-        <v>3791.18</v>
+        <v>-3718.29</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>93.01000000000001</v>
+        <v>-100</v>
       </c>
       <c r="S13" t="n">
-        <v>7582.35</v>
-      </c>
-      <c r="T13" t="inlineStr"/>
+        <v>-4862.14</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1470,7 +1478,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NIL</t>
+          <t>KAITO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1479,58 +1487,54 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2669.9</v>
+        <v>6823</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04716</v>
+        <v>1.194796722849186</v>
       </c>
       <c r="F14" t="n">
-        <v>0.03987</v>
+        <v>1.305925994430602</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-27 10:43</t>
+          <t>2026-07-27 07:30</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-27 13:07</t>
+          <t>2026-07-27 21:51</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>125.91</v>
+        <v>8152.1</v>
       </c>
       <c r="J14" t="n">
-        <v>-15.46</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-19.46</v>
+        <v>758.24</v>
       </c>
       <c r="L14" t="n">
-        <v>-46.37</v>
+        <v>27.9</v>
       </c>
       <c r="M14" t="n">
-        <v>-58.39</v>
+        <v>2274.71</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>-77.29000000000001</v>
+        <v>46.51</v>
       </c>
       <c r="P14" t="n">
-        <v>-97.31999999999999</v>
+        <v>3791.18</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>-100</v>
+        <v>93.01000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-125.91</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>7582.35</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1547,7 +1551,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1335</v>
+        <v>2669.9</v>
       </c>
       <c r="E15" t="n">
         <v>0.04716</v>
@@ -1566,33 +1570,33 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>62.96</v>
+        <v>125.91</v>
       </c>
       <c r="J15" t="n">
         <v>-15.46</v>
       </c>
       <c r="K15" t="n">
-        <v>-9.73</v>
+        <v>-19.46</v>
       </c>
       <c r="L15" t="n">
         <v>-46.37</v>
       </c>
       <c r="M15" t="n">
-        <v>-29.2</v>
+        <v>-58.39</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
         <v>-77.29000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-48.66</v>
+        <v>-97.31999999999999</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
         <v>-100</v>
       </c>
       <c r="S15" t="n">
-        <v>-62.96</v>
+        <v>-125.91</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1606,59 +1610,67 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PUMP</t>
+          <t>NIL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>48154</v>
+        <v>1335</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002129</v>
+        <v>0.04716</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001969</v>
+        <v>0.03987</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-27 11:04</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>2026-07-27 10:43</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:07</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>102.52</v>
+        <v>62.96</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.52</v>
+        <v>-15.46</v>
       </c>
       <c r="K16" t="n">
-        <v>-7.7</v>
+        <v>-9.73</v>
       </c>
       <c r="L16" t="n">
-        <v>-22.55</v>
+        <v>-46.37</v>
       </c>
       <c r="M16" t="n">
-        <v>-23.11</v>
+        <v>-29.2</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>-37.58</v>
+        <v>-77.29000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-38.52</v>
+        <v>-48.66</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>-75.15000000000001</v>
+        <v>-100</v>
       </c>
       <c r="S16" t="n">
-        <v>-77.05</v>
-      </c>
-      <c r="T16" t="inlineStr"/>
+        <v>-62.96</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1666,7 +1678,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NIL</t>
+          <t>PUMP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1675,58 +1687,54 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6364.4</v>
+        <v>48154</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04534</v>
+        <v>0.002129</v>
       </c>
       <c r="F17" t="n">
-        <v>0.03846</v>
+        <v>0.001977</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-27 14:22</t>
+          <t>2026-07-27 11:04</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-28 00:46</t>
+          <t>2026-07-30 16:27</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>288.56</v>
+        <v>102.52</v>
       </c>
       <c r="J17" t="n">
-        <v>-15.17</v>
+        <v>-7.14</v>
       </c>
       <c r="K17" t="n">
-        <v>-43.79</v>
+        <v>-7.32</v>
       </c>
       <c r="L17" t="n">
-        <v>-45.52</v>
+        <v>-21.42</v>
       </c>
       <c r="M17" t="n">
-        <v>-131.36</v>
+        <v>-21.96</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>-75.87</v>
+        <v>-35.7</v>
       </c>
       <c r="P17" t="n">
-        <v>-218.94</v>
+        <v>-36.6</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>-100</v>
+        <v>-71.40000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>-288.56</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>-73.19</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1743,7 +1751,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3182.2</v>
+        <v>6364.4</v>
       </c>
       <c r="E18" t="n">
         <v>0.04534</v>
@@ -1762,33 +1770,33 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>144.28</v>
+        <v>288.56</v>
       </c>
       <c r="J18" t="n">
         <v>-15.17</v>
       </c>
       <c r="K18" t="n">
-        <v>-21.89</v>
+        <v>-43.79</v>
       </c>
       <c r="L18" t="n">
         <v>-45.52</v>
       </c>
       <c r="M18" t="n">
-        <v>-65.68000000000001</v>
+        <v>-131.36</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
         <v>-75.87</v>
       </c>
       <c r="P18" t="n">
-        <v>-109.47</v>
+        <v>-218.94</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
         <v>-100</v>
       </c>
       <c r="S18" t="n">
-        <v>-144.28</v>
+        <v>-288.56</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1802,7 +1810,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEXE</t>
+          <t>NIL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1811,54 +1819,58 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.19</v>
+        <v>3182.2</v>
       </c>
       <c r="E19" t="n">
-        <v>2.631</v>
+        <v>0.04534</v>
       </c>
       <c r="F19" t="n">
-        <v>3.082</v>
+        <v>0.03846</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-27 14:31</t>
+          <t>2026-07-27 14:22</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-28 03:22</t>
+          <t>2026-07-28 00:46</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.76</v>
+        <v>144.28</v>
       </c>
       <c r="J19" t="n">
-        <v>17.14</v>
+        <v>-15.17</v>
       </c>
       <c r="K19" t="n">
-        <v>0.99</v>
+        <v>-21.89</v>
       </c>
       <c r="L19" t="n">
-        <v>51.43</v>
+        <v>-45.52</v>
       </c>
       <c r="M19" t="n">
-        <v>2.96</v>
+        <v>-65.68000000000001</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>85.70999999999999</v>
+        <v>-75.87</v>
       </c>
       <c r="P19" t="n">
-        <v>4.94</v>
+        <v>-109.47</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>171.42</v>
+        <v>-100</v>
       </c>
       <c r="S19" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="T19" t="inlineStr"/>
+        <v>-144.28</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1875,17 +1887,17 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18.69</v>
+        <v>2.19</v>
       </c>
       <c r="E20" t="n">
-        <v>2.68</v>
+        <v>2.631</v>
       </c>
       <c r="F20" t="n">
         <v>3.082</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-27 14:42</t>
+          <t>2026-07-27 14:31</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1894,33 +1906,33 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>50.09</v>
+        <v>5.76</v>
       </c>
       <c r="J20" t="n">
-        <v>15</v>
+        <v>17.14</v>
       </c>
       <c r="K20" t="n">
-        <v>7.51</v>
+        <v>0.99</v>
       </c>
       <c r="L20" t="n">
-        <v>45</v>
+        <v>51.43</v>
       </c>
       <c r="M20" t="n">
-        <v>22.54</v>
+        <v>2.96</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>75</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>37.57</v>
+        <v>4.94</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>150</v>
+        <v>171.42</v>
       </c>
       <c r="S20" t="n">
-        <v>75.13</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="T20" t="inlineStr"/>
     </row>
@@ -1939,13 +1951,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.45</v>
+        <v>18.69</v>
       </c>
       <c r="E21" t="n">
         <v>2.68</v>
       </c>
       <c r="F21" t="n">
-        <v>3.338</v>
+        <v>3.082</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1954,37 +1966,37 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-28 08:00</t>
+          <t>2026-07-28 03:22</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>28.01</v>
+        <v>50.09</v>
       </c>
       <c r="J21" t="n">
-        <v>24.55</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>6.88</v>
+        <v>7.51</v>
       </c>
       <c r="L21" t="n">
-        <v>73.66</v>
+        <v>45</v>
       </c>
       <c r="M21" t="n">
-        <v>20.63</v>
+        <v>22.54</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>122.76</v>
+        <v>75</v>
       </c>
       <c r="P21" t="n">
-        <v>34.38</v>
+        <v>37.57</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
-        <v>245.52</v>
+        <v>150</v>
       </c>
       <c r="S21" t="n">
-        <v>68.76000000000001</v>
+        <v>75.13</v>
       </c>
       <c r="T21" t="inlineStr"/>
     </row>
@@ -1999,52 +2011,56 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.19</v>
+        <v>10.45</v>
       </c>
       <c r="E22" t="n">
         <v>2.68</v>
       </c>
       <c r="F22" t="n">
-        <v>2.495</v>
+        <v>3.338</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>2026-07-27 14:42</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-07-28 08:00</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>5.87</v>
+        <v>28.01</v>
       </c>
       <c r="J22" t="n">
-        <v>-6.9</v>
+        <v>24.55</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.41</v>
+        <v>6.88</v>
       </c>
       <c r="L22" t="n">
-        <v>-20.71</v>
+        <v>73.66</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.22</v>
+        <v>20.63</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>-34.51</v>
+        <v>122.76</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.03</v>
+        <v>34.38</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>-69.03</v>
+        <v>245.52</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.05</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="T22" t="inlineStr"/>
     </row>
@@ -2054,61 +2070,57 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RIF</t>
+          <t>DEXE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>57844</v>
+        <v>2.19</v>
       </c>
       <c r="E23" t="n">
-        <v>0.07580000000000001</v>
+        <v>2.68</v>
       </c>
       <c r="F23" t="n">
-        <v>0.08083306825254132</v>
+        <v>2.432</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-27 15:31</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-07-27 16:08</t>
-        </is>
-      </c>
+          <t>2026-07-27 14:42</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>4384.58</v>
+        <v>5.87</v>
       </c>
       <c r="J23" t="n">
-        <v>6.64</v>
+        <v>-9.25</v>
       </c>
       <c r="K23" t="n">
-        <v>291.13</v>
+        <v>-0.54</v>
       </c>
       <c r="L23" t="n">
-        <v>19.92</v>
+        <v>-27.76</v>
       </c>
       <c r="M23" t="n">
-        <v>873.4</v>
+        <v>-1.63</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>33.2</v>
+        <v>-46.27</v>
       </c>
       <c r="P23" t="n">
-        <v>1455.66</v>
+        <v>-2.72</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>66.40000000000001</v>
+        <v>-92.54000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>2911.33</v>
+        <v>-5.43</v>
       </c>
       <c r="T23" t="inlineStr"/>
     </row>
@@ -2127,52 +2139,52 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>53773</v>
+        <v>57844</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0813</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0885</v>
+        <v>0.08083306825254132</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-27 16:09</t>
+          <t>2026-07-27 15:31</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-27 17:03</t>
+          <t>2026-07-27 16:08</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4371.74</v>
+        <v>4384.58</v>
       </c>
       <c r="J24" t="n">
-        <v>8.859999999999999</v>
+        <v>6.64</v>
       </c>
       <c r="K24" t="n">
-        <v>387.17</v>
+        <v>291.13</v>
       </c>
       <c r="L24" t="n">
-        <v>26.57</v>
+        <v>19.92</v>
       </c>
       <c r="M24" t="n">
-        <v>1161.5</v>
+        <v>873.4</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
-        <v>44.28</v>
+        <v>33.2</v>
       </c>
       <c r="P24" t="n">
-        <v>1935.83</v>
+        <v>1455.66</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
-        <v>88.56</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>3871.66</v>
+        <v>2911.33</v>
       </c>
       <c r="T24" t="inlineStr"/>
     </row>
@@ -2191,17 +2203,17 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>51795</v>
+        <v>53773</v>
       </c>
       <c r="E25" t="n">
-        <v>0.083</v>
+        <v>0.0813</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08840365865431025</v>
+        <v>0.0885</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-27 16:43</t>
+          <t>2026-07-27 16:09</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2210,33 +2222,33 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4298.98</v>
+        <v>4371.74</v>
       </c>
       <c r="J25" t="n">
-        <v>6.51</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>279.88</v>
+        <v>387.17</v>
       </c>
       <c r="L25" t="n">
-        <v>19.53</v>
+        <v>26.57</v>
       </c>
       <c r="M25" t="n">
-        <v>839.65</v>
+        <v>1161.5</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>32.55</v>
+        <v>44.28</v>
       </c>
       <c r="P25" t="n">
-        <v>1399.41</v>
+        <v>1935.83</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
-        <v>65.09999999999999</v>
+        <v>88.56</v>
       </c>
       <c r="S25" t="n">
-        <v>2798.82</v>
+        <v>3871.66</v>
       </c>
       <c r="T25" t="inlineStr"/>
     </row>
@@ -2246,7 +2258,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>RIF</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2255,52 +2267,52 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>840945.7</v>
+        <v>51795</v>
       </c>
       <c r="E26" t="n">
-        <v>0.002913425293738117</v>
+        <v>0.083</v>
       </c>
       <c r="F26" t="n">
-        <v>0.00335</v>
+        <v>0.08840365865431025</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-27 21:57</t>
+          <t>2026-07-27 16:43</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-28 07:49</t>
+          <t>2026-07-27 17:03</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2450.03</v>
+        <v>4298.98</v>
       </c>
       <c r="J26" t="n">
-        <v>14.98</v>
+        <v>6.51</v>
       </c>
       <c r="K26" t="n">
-        <v>367.14</v>
+        <v>279.88</v>
       </c>
       <c r="L26" t="n">
-        <v>44.95</v>
+        <v>19.53</v>
       </c>
       <c r="M26" t="n">
-        <v>1101.41</v>
+        <v>839.65</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
-        <v>74.92</v>
+        <v>32.55</v>
       </c>
       <c r="P26" t="n">
-        <v>1835.68</v>
+        <v>1399.41</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>149.85</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>3671.36</v>
+        <v>2798.82</v>
       </c>
       <c r="T26" t="inlineStr"/>
     </row>
@@ -2319,13 +2331,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>526761.8</v>
+        <v>840945.7</v>
       </c>
       <c r="E27" t="n">
         <v>0.002913425293738117</v>
       </c>
       <c r="F27" t="n">
-        <v>0.00245</v>
+        <v>0.00335</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2334,43 +2346,39 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-29 12:18</t>
+          <t>2026-07-28 07:49</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1534.68</v>
+        <v>2450.03</v>
       </c>
       <c r="J27" t="n">
-        <v>-15.91</v>
+        <v>14.98</v>
       </c>
       <c r="K27" t="n">
-        <v>-244.11</v>
+        <v>367.14</v>
       </c>
       <c r="L27" t="n">
-        <v>-47.72</v>
+        <v>44.95</v>
       </c>
       <c r="M27" t="n">
-        <v>-732.34</v>
+        <v>1101.41</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
-        <v>-79.53</v>
+        <v>74.92</v>
       </c>
       <c r="P27" t="n">
-        <v>-1220.57</v>
+        <v>1835.68</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>-100</v>
+        <v>149.85</v>
       </c>
       <c r="S27" t="n">
-        <v>-1534.68</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>3671.36</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2387,7 +2395,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>212577.7</v>
+        <v>526761.8</v>
       </c>
       <c r="E28" t="n">
         <v>0.002913425293738117</v>
@@ -2406,33 +2414,33 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>619.33</v>
+        <v>1534.68</v>
       </c>
       <c r="J28" t="n">
         <v>-15.91</v>
       </c>
       <c r="K28" t="n">
-        <v>-98.51000000000001</v>
+        <v>-244.11</v>
       </c>
       <c r="L28" t="n">
         <v>-47.72</v>
       </c>
       <c r="M28" t="n">
-        <v>-295.54</v>
+        <v>-732.34</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
         <v>-79.53</v>
       </c>
       <c r="P28" t="n">
-        <v>-492.57</v>
+        <v>-1220.57</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
         <v>-100</v>
       </c>
       <c r="S28" t="n">
-        <v>-619.33</v>
+        <v>-1534.68</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2446,7 +2454,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ACH</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2455,54 +2463,58 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>683496</v>
+        <v>212577.7</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00432</v>
+        <v>0.002913425293738117</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00496</v>
+        <v>0.00245</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-27 22:08</t>
+          <t>2026-07-27 21:57</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-28 06:42</t>
+          <t>2026-07-29 12:18</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2952.7</v>
+        <v>619.33</v>
       </c>
       <c r="J29" t="n">
-        <v>14.81</v>
+        <v>-15.91</v>
       </c>
       <c r="K29" t="n">
-        <v>437.44</v>
+        <v>-98.51000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>44.44</v>
+        <v>-47.72</v>
       </c>
       <c r="M29" t="n">
-        <v>1312.31</v>
+        <v>-295.54</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
-        <v>74.06999999999999</v>
+        <v>-79.53</v>
       </c>
       <c r="P29" t="n">
-        <v>2187.19</v>
+        <v>-492.57</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>148.15</v>
+        <v>-100</v>
       </c>
       <c r="S29" t="n">
-        <v>4374.37</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
+        <v>-619.33</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2519,7 +2531,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>341748</v>
+        <v>683496</v>
       </c>
       <c r="E30" t="n">
         <v>0.00432</v>
@@ -2534,37 +2546,37 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-29 10:24</t>
+          <t>2026-07-28 06:42</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1476.35</v>
+        <v>2952.7</v>
       </c>
       <c r="J30" t="n">
         <v>14.81</v>
       </c>
       <c r="K30" t="n">
-        <v>218.72</v>
+        <v>437.44</v>
       </c>
       <c r="L30" t="n">
         <v>44.44</v>
       </c>
       <c r="M30" t="n">
-        <v>656.16</v>
+        <v>1312.31</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
         <v>74.06999999999999</v>
       </c>
       <c r="P30" t="n">
-        <v>1093.59</v>
+        <v>2187.19</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
         <v>148.15</v>
       </c>
       <c r="S30" t="n">
-        <v>2187.19</v>
+        <v>4374.37</v>
       </c>
       <c r="T30" t="inlineStr"/>
     </row>
@@ -2574,7 +2586,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>COTI</t>
+          <t>ACH</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2583,52 +2595,52 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>339015</v>
+        <v>341748</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01316130808371311</v>
+        <v>0.00432</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01354643759125702</v>
+        <v>0.00496</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-27 22:14</t>
+          <t>2026-07-27 22:08</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-27 22:30</t>
+          <t>2026-07-29 10:24</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4461.88</v>
+        <v>1476.35</v>
       </c>
       <c r="J31" t="n">
-        <v>2.93</v>
+        <v>14.81</v>
       </c>
       <c r="K31" t="n">
-        <v>130.56</v>
+        <v>218.72</v>
       </c>
       <c r="L31" t="n">
-        <v>8.779999999999999</v>
+        <v>44.44</v>
       </c>
       <c r="M31" t="n">
-        <v>391.69</v>
+        <v>656.16</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
-        <v>14.63</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="P31" t="n">
-        <v>652.8200000000001</v>
+        <v>1093.59</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
-        <v>29.26</v>
+        <v>148.15</v>
       </c>
       <c r="S31" t="n">
-        <v>1305.65</v>
+        <v>2187.19</v>
       </c>
       <c r="T31" t="inlineStr"/>
     </row>
@@ -2647,52 +2659,52 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>327219</v>
+        <v>339015</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01350763555905984</v>
+        <v>0.01316130808371311</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01372472677320082</v>
+        <v>0.01354643759125702</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-27 22:31</t>
+          <t>2026-07-27 22:14</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-27 22:53</t>
+          <t>2026-07-27 22:30</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4419.95</v>
+        <v>4461.88</v>
       </c>
       <c r="J32" t="n">
-        <v>1.61</v>
+        <v>2.93</v>
       </c>
       <c r="K32" t="n">
-        <v>71.04000000000001</v>
+        <v>130.56</v>
       </c>
       <c r="L32" t="n">
-        <v>4.82</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>213.11</v>
+        <v>391.69</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
-        <v>8.039999999999999</v>
+        <v>14.63</v>
       </c>
       <c r="P32" t="n">
-        <v>355.18</v>
+        <v>652.8200000000001</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="n">
-        <v>16.07</v>
+        <v>29.26</v>
       </c>
       <c r="S32" t="n">
-        <v>710.36</v>
+        <v>1305.65</v>
       </c>
       <c r="T32" t="inlineStr"/>
     </row>
@@ -2711,17 +2723,17 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>329868</v>
+        <v>327219</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0134805300301939</v>
+        <v>0.01350763555905984</v>
       </c>
       <c r="F33" t="n">
-        <v>0.01371</v>
+        <v>0.01372472677320082</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-27 22:48</t>
+          <t>2026-07-27 22:31</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2730,33 +2742,33 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4446.8</v>
+        <v>4419.95</v>
       </c>
       <c r="J33" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="K33" t="n">
-        <v>75.69</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>5.11</v>
+        <v>4.82</v>
       </c>
       <c r="M33" t="n">
-        <v>227.08</v>
+        <v>213.11</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
-        <v>8.51</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="P33" t="n">
-        <v>378.47</v>
+        <v>355.18</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
-        <v>17.02</v>
+        <v>16.07</v>
       </c>
       <c r="S33" t="n">
-        <v>756.95</v>
+        <v>710.36</v>
       </c>
       <c r="T33" t="inlineStr"/>
     </row>
@@ -2775,58 +2787,54 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>215458</v>
+        <v>329868</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0135</v>
+        <v>0.0134805300301939</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01141</v>
+        <v>0.01371</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-27 23:10</t>
+          <t>2026-07-27 22:48</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-27 23:58</t>
+          <t>2026-07-27 22:53</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2908.68</v>
+        <v>4446.8</v>
       </c>
       <c r="J34" t="n">
-        <v>-15.48</v>
+        <v>1.7</v>
       </c>
       <c r="K34" t="n">
-        <v>-450.31</v>
+        <v>75.69</v>
       </c>
       <c r="L34" t="n">
-        <v>-46.44</v>
+        <v>5.11</v>
       </c>
       <c r="M34" t="n">
-        <v>-1350.92</v>
+        <v>227.08</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
-        <v>-77.41</v>
+        <v>8.51</v>
       </c>
       <c r="P34" t="n">
-        <v>-2251.54</v>
+        <v>378.47</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="n">
-        <v>-100</v>
+        <v>17.02</v>
       </c>
       <c r="S34" t="n">
-        <v>-2908.68</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>756.95</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2843,7 +2851,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>107730</v>
+        <v>215458</v>
       </c>
       <c r="E35" t="n">
         <v>0.0135</v>
@@ -2862,33 +2870,33 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1454.36</v>
+        <v>2908.68</v>
       </c>
       <c r="J35" t="n">
         <v>-15.48</v>
       </c>
       <c r="K35" t="n">
-        <v>-225.16</v>
+        <v>-450.31</v>
       </c>
       <c r="L35" t="n">
         <v>-46.44</v>
       </c>
       <c r="M35" t="n">
-        <v>-675.47</v>
+        <v>-1350.92</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
         <v>-77.41</v>
       </c>
       <c r="P35" t="n">
-        <v>-1125.78</v>
+        <v>-2251.54</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="n">
         <v>-100</v>
       </c>
       <c r="S35" t="n">
-        <v>-1454.36</v>
+        <v>-2908.68</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -2902,59 +2910,67 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DGB</t>
+          <t>COTI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1094443.9</v>
+        <v>107730</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00407789726362402</v>
+        <v>0.0135</v>
       </c>
       <c r="F36" t="n">
-        <v>0.00392</v>
+        <v>0.01141</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-27 23:16</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>2026-07-27 23:10</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-07-27 23:58</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>4463.03</v>
+        <v>1454.36</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.87</v>
+        <v>-15.48</v>
       </c>
       <c r="K36" t="n">
-        <v>-172.81</v>
+        <v>-225.16</v>
       </c>
       <c r="L36" t="n">
-        <v>-11.62</v>
+        <v>-46.44</v>
       </c>
       <c r="M36" t="n">
-        <v>-518.4299999999999</v>
+        <v>-675.47</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
-        <v>-19.36</v>
+        <v>-77.41</v>
       </c>
       <c r="P36" t="n">
-        <v>-864.05</v>
+        <v>-1125.78</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="n">
-        <v>-38.72</v>
+        <v>-100</v>
       </c>
       <c r="S36" t="n">
-        <v>-1728.1</v>
-      </c>
-      <c r="T36" t="inlineStr"/>
+        <v>-1454.36</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2967,52 +2983,56 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>990569.4</v>
       </c>
       <c r="E37" t="n">
-        <v>0.004176841910319458</v>
+        <v>0.00407789726362402</v>
       </c>
       <c r="F37" t="n">
-        <v>0.00392</v>
+        <v>0.003901090282013557</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-27 23:22</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>2026-07-27 23:16</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:27</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>4137.45</v>
+        <v>4039.44</v>
       </c>
       <c r="J37" t="n">
-        <v>-6.15</v>
+        <v>-4.34</v>
       </c>
       <c r="K37" t="n">
-        <v>-254.42</v>
+        <v>-175.14</v>
       </c>
       <c r="L37" t="n">
-        <v>-18.45</v>
+        <v>-13.01</v>
       </c>
       <c r="M37" t="n">
-        <v>-763.26</v>
+        <v>-525.42</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
-        <v>-30.75</v>
+        <v>-21.68</v>
       </c>
       <c r="P37" t="n">
-        <v>-1272.1</v>
+        <v>-875.7</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="n">
-        <v>-61.49</v>
+        <v>-43.36</v>
       </c>
       <c r="S37" t="n">
-        <v>-2544.2</v>
+        <v>-1751.4</v>
       </c>
       <c r="T37" t="inlineStr"/>
     </row>
@@ -3022,57 +3042,61 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PROM</t>
+          <t>DGB</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2232.33</v>
+        <v>103874.5</v>
       </c>
       <c r="E38" t="n">
-        <v>2.026488516482778</v>
+        <v>0.00407789726362402</v>
       </c>
       <c r="F38" t="n">
-        <v>1.852</v>
+        <v>0.0039</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-28 08:52</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>2026-07-27 23:16</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:27</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>4523.79</v>
+        <v>423.59</v>
       </c>
       <c r="J38" t="n">
-        <v>-8.609999999999999</v>
+        <v>-4.36</v>
       </c>
       <c r="K38" t="n">
-        <v>-389.52</v>
+        <v>-18.48</v>
       </c>
       <c r="L38" t="n">
-        <v>-25.83</v>
+        <v>-13.09</v>
       </c>
       <c r="M38" t="n">
-        <v>-1168.55</v>
+        <v>-55.44</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
-        <v>-43.05</v>
+        <v>-21.81</v>
       </c>
       <c r="P38" t="n">
-        <v>-1947.58</v>
+        <v>-92.39</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="n">
-        <v>-86.09999999999999</v>
+        <v>-43.62</v>
       </c>
       <c r="S38" t="n">
-        <v>-3895.16</v>
+        <v>-184.79</v>
       </c>
       <c r="T38" t="inlineStr"/>
     </row>
@@ -3082,7 +3106,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>DGB</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3091,52 +3115,52 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13672</v>
+        <v>990569.4</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3214995318899941</v>
+        <v>0.004176841910319458</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3293</v>
+        <v>0.0039</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-28 10:28</t>
+          <t>2026-07-27 23:22</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-28 10:38</t>
+          <t>2026-07-30 16:27</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4395.54</v>
+        <v>4137.45</v>
       </c>
       <c r="J39" t="n">
-        <v>2.43</v>
+        <v>-6.63</v>
       </c>
       <c r="K39" t="n">
-        <v>106.65</v>
+        <v>-274.23</v>
       </c>
       <c r="L39" t="n">
-        <v>7.28</v>
+        <v>-19.88</v>
       </c>
       <c r="M39" t="n">
-        <v>319.94</v>
+        <v>-822.6900000000001</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
-        <v>12.13</v>
+        <v>-33.14</v>
       </c>
       <c r="P39" t="n">
-        <v>533.24</v>
+        <v>-1371.16</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
-        <v>24.26</v>
+        <v>-66.28</v>
       </c>
       <c r="S39" t="n">
-        <v>1066.48</v>
+        <v>-2742.31</v>
       </c>
       <c r="T39" t="inlineStr"/>
     </row>
@@ -3146,7 +3170,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>PROM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3155,54 +3179,58 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13363.4</v>
+        <v>2232.33</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3372</v>
+        <v>2.026488516482778</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3472084095364952</v>
+        <v>1.822</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-28 10:44</t>
+          <t>2026-07-28 08:52</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-28 11:31</t>
+          <t>2026-07-30 16:27</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4506.14</v>
+        <v>4523.79</v>
       </c>
       <c r="J40" t="n">
-        <v>2.97</v>
+        <v>-10.09</v>
       </c>
       <c r="K40" t="n">
-        <v>133.75</v>
+        <v>-456.49</v>
       </c>
       <c r="L40" t="n">
-        <v>8.9</v>
+        <v>-30.27</v>
       </c>
       <c r="M40" t="n">
-        <v>401.24</v>
+        <v>-1369.46</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
-        <v>14.84</v>
+        <v>-50.45</v>
       </c>
       <c r="P40" t="n">
-        <v>668.73</v>
+        <v>-2282.43</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="n">
-        <v>29.68</v>
+        <v>-100</v>
       </c>
       <c r="S40" t="n">
-        <v>1337.46</v>
-      </c>
-      <c r="T40" t="inlineStr"/>
+        <v>-4523.79</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3210,7 +3238,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>COTI</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3219,52 +3247,52 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>240574</v>
+        <v>13672</v>
       </c>
       <c r="E41" t="n">
-        <v>0.01232132044936846</v>
+        <v>0.3214995318899941</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01416</v>
+        <v>0.3293</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-28 11:38</t>
+          <t>2026-07-28 10:28</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-28 16:00</t>
+          <t>2026-07-28 10:38</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2964.19</v>
+        <v>4395.54</v>
       </c>
       <c r="J41" t="n">
-        <v>14.92</v>
+        <v>2.43</v>
       </c>
       <c r="K41" t="n">
-        <v>442.34</v>
+        <v>106.65</v>
       </c>
       <c r="L41" t="n">
-        <v>44.77</v>
+        <v>7.28</v>
       </c>
       <c r="M41" t="n">
-        <v>1327.02</v>
+        <v>319.94</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
-        <v>74.61</v>
+        <v>12.13</v>
       </c>
       <c r="P41" t="n">
-        <v>2211.69</v>
+        <v>533.24</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
-        <v>149.23</v>
+        <v>24.26</v>
       </c>
       <c r="S41" t="n">
-        <v>4423.38</v>
+        <v>1066.48</v>
       </c>
       <c r="T41" t="inlineStr"/>
     </row>
@@ -3274,7 +3302,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>COTI</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3283,52 +3311,52 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>120288</v>
+        <v>13363.4</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01232132044936846</v>
+        <v>0.3372</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01287637137536579</v>
+        <v>0.3472084095364952</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-28 11:38</t>
+          <t>2026-07-28 10:44</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-28 19:50</t>
+          <t>2026-07-28 11:31</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1482.11</v>
+        <v>4506.14</v>
       </c>
       <c r="J42" t="n">
-        <v>4.5</v>
+        <v>2.97</v>
       </c>
       <c r="K42" t="n">
-        <v>66.77</v>
+        <v>133.75</v>
       </c>
       <c r="L42" t="n">
-        <v>13.51</v>
+        <v>8.9</v>
       </c>
       <c r="M42" t="n">
-        <v>200.3</v>
+        <v>401.24</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
-        <v>22.52</v>
+        <v>14.84</v>
       </c>
       <c r="P42" t="n">
-        <v>333.83</v>
+        <v>668.73</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="n">
-        <v>45.05</v>
+        <v>29.68</v>
       </c>
       <c r="S42" t="n">
-        <v>667.66</v>
+        <v>1337.46</v>
       </c>
       <c r="T42" t="inlineStr"/>
     </row>
@@ -3338,7 +3366,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RIF</t>
+          <t>COTI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3347,52 +3375,52 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>32966</v>
+        <v>240574</v>
       </c>
       <c r="E43" t="n">
-        <v>0.08372395551061679</v>
+        <v>0.01232132044936846</v>
       </c>
       <c r="F43" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.01416</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-28 18:23</t>
+          <t>2026-07-28 11:38</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-29 00:08</t>
+          <t>2026-07-28 16:00</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2760.04</v>
+        <v>2964.19</v>
       </c>
       <c r="J43" t="n">
-        <v>14.9</v>
+        <v>14.92</v>
       </c>
       <c r="K43" t="n">
-        <v>411.29</v>
+        <v>442.34</v>
       </c>
       <c r="L43" t="n">
-        <v>44.7</v>
+        <v>44.77</v>
       </c>
       <c r="M43" t="n">
-        <v>1233.86</v>
+        <v>1327.02</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
-        <v>74.51000000000001</v>
+        <v>74.61</v>
       </c>
       <c r="P43" t="n">
-        <v>2056.43</v>
+        <v>2211.69</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="n">
-        <v>149.01</v>
+        <v>149.23</v>
       </c>
       <c r="S43" t="n">
-        <v>4112.85</v>
+        <v>4423.38</v>
       </c>
       <c r="T43" t="inlineStr"/>
     </row>
@@ -3402,7 +3430,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RIF</t>
+          <t>COTI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3411,52 +3439,52 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>16484</v>
+        <v>120288</v>
       </c>
       <c r="E44" t="n">
-        <v>0.08372395551061679</v>
+        <v>0.01232132044936846</v>
       </c>
       <c r="F44" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.01287637137536579</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-28 18:23</t>
+          <t>2026-07-28 11:38</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-29 14:11</t>
+          <t>2026-07-28 19:50</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1380.11</v>
+        <v>1482.11</v>
       </c>
       <c r="J44" t="n">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="K44" t="n">
-        <v>213.9</v>
+        <v>66.77</v>
       </c>
       <c r="L44" t="n">
-        <v>46.5</v>
+        <v>13.51</v>
       </c>
       <c r="M44" t="n">
-        <v>641.6900000000001</v>
+        <v>200.3</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
-        <v>77.48999999999999</v>
+        <v>22.52</v>
       </c>
       <c r="P44" t="n">
-        <v>1069.49</v>
+        <v>333.83</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="n">
-        <v>154.99</v>
+        <v>45.05</v>
       </c>
       <c r="S44" t="n">
-        <v>2138.97</v>
+        <v>667.66</v>
       </c>
       <c r="T44" t="inlineStr"/>
     </row>
@@ -3466,7 +3494,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>RIF</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3475,52 +3503,52 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>16982</v>
+        <v>32966</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1769</v>
+        <v>0.08372395551061679</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2034</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47</t>
+          <t>2026-07-28 18:23</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-30 02:38</t>
+          <t>2026-07-29 00:08</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3004.12</v>
+        <v>2760.04</v>
       </c>
       <c r="J45" t="n">
-        <v>14.98</v>
+        <v>14.9</v>
       </c>
       <c r="K45" t="n">
-        <v>450.02</v>
+        <v>411.29</v>
       </c>
       <c r="L45" t="n">
-        <v>44.94</v>
+        <v>44.7</v>
       </c>
       <c r="M45" t="n">
-        <v>1350.07</v>
+        <v>1233.86</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
-        <v>74.90000000000001</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="P45" t="n">
-        <v>2250.11</v>
+        <v>2056.43</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="n">
-        <v>149.8</v>
+        <v>149.01</v>
       </c>
       <c r="S45" t="n">
-        <v>4500.23</v>
+        <v>4112.85</v>
       </c>
       <c r="T45" t="inlineStr"/>
     </row>
@@ -3530,71 +3558,63 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>RIF</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>8491</v>
+        <v>16484</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1769</v>
+        <v>0.08372395551061679</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0765</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>2026-07-28 18:23</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:11</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1502.06</v>
+        <v>1380.11</v>
       </c>
       <c r="J46" t="n">
-        <v>-56.76</v>
+        <v>15.5</v>
       </c>
       <c r="K46" t="n">
-        <v>-852.5</v>
+        <v>213.9</v>
       </c>
       <c r="L46" t="n">
-        <v>-100</v>
+        <v>46.5</v>
       </c>
       <c r="M46" t="n">
-        <v>-1502.06</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>641.6900000000001</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
-        <v>-100</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="P46" t="n">
-        <v>-1502.06</v>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>1069.49</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="n">
-        <v>-100</v>
+        <v>154.99</v>
       </c>
       <c r="S46" t="n">
-        <v>-1502.06</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>2138.97</v>
+      </c>
+      <c r="T46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3602,57 +3622,61 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SYRUP</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13570.8</v>
+        <v>16982</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1668545406313555</v>
+        <v>0.1769</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1623</v>
+        <v>0.2034</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-29 16:18</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>2026-07-29 10:47</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:38</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>2264.35</v>
+        <v>3004.12</v>
       </c>
       <c r="J47" t="n">
-        <v>-2.73</v>
+        <v>14.98</v>
       </c>
       <c r="K47" t="n">
-        <v>-61.81</v>
+        <v>450.02</v>
       </c>
       <c r="L47" t="n">
-        <v>-8.19</v>
+        <v>44.94</v>
       </c>
       <c r="M47" t="n">
-        <v>-185.43</v>
+        <v>1350.07</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
-        <v>-13.65</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="P47" t="n">
-        <v>-309.04</v>
+        <v>2250.11</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="n">
-        <v>-27.3</v>
+        <v>149.8</v>
       </c>
       <c r="S47" t="n">
-        <v>-618.09</v>
+        <v>4500.23</v>
       </c>
       <c r="T47" t="inlineStr"/>
     </row>
@@ -3662,63 +3686,71 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>23567.8</v>
+        <v>8491</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1230380629502966</v>
+        <v>0.1769</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1300912787786726</v>
+        <v>0.0556</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-29 16:35</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2026-07-29 19:30</t>
-        </is>
-      </c>
+          <t>2026-07-29 10:47</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>2899.74</v>
+        <v>1502.06</v>
       </c>
       <c r="J48" t="n">
-        <v>5.73</v>
+        <v>-68.56999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>166.23</v>
+        <v>-1029.96</v>
       </c>
       <c r="L48" t="n">
-        <v>17.2</v>
+        <v>-100</v>
       </c>
       <c r="M48" t="n">
-        <v>498.69</v>
-      </c>
-      <c r="N48" t="inlineStr"/>
+        <v>-1502.06</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="O48" t="n">
-        <v>28.66</v>
+        <v>-100</v>
       </c>
       <c r="P48" t="n">
-        <v>831.14</v>
-      </c>
-      <c r="Q48" t="inlineStr"/>
+        <v>-1502.06</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="R48" t="n">
-        <v>57.33</v>
+        <v>-100</v>
       </c>
       <c r="S48" t="n">
-        <v>1662.29</v>
-      </c>
-      <c r="T48" t="inlineStr"/>
+        <v>-1502.06</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3726,7 +3758,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EPIC</t>
+          <t>SYRUP</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3735,52 +3767,52 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2027.9</v>
+        <v>13570.8</v>
       </c>
       <c r="E49" t="n">
-        <v>0.7345917025543246</v>
+        <v>0.1668545406313555</v>
       </c>
       <c r="F49" t="n">
-        <v>0.844</v>
+        <v>0.1617</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-29 20:39</t>
+          <t>2026-07-29 16:18</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-30 06:19</t>
+          <t>2026-07-30 16:27</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1489.68</v>
+        <v>2264.35</v>
       </c>
       <c r="J49" t="n">
-        <v>14.89</v>
+        <v>-3.09</v>
       </c>
       <c r="K49" t="n">
-        <v>221.87</v>
+        <v>-69.95</v>
       </c>
       <c r="L49" t="n">
-        <v>44.68</v>
+        <v>-9.27</v>
       </c>
       <c r="M49" t="n">
-        <v>665.61</v>
+        <v>-209.85</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="n">
-        <v>74.47</v>
+        <v>-15.45</v>
       </c>
       <c r="P49" t="n">
-        <v>1109.35</v>
+        <v>-349.76</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="n">
-        <v>148.94</v>
+        <v>-30.89</v>
       </c>
       <c r="S49" t="n">
-        <v>2218.69</v>
+        <v>-699.51</v>
       </c>
       <c r="T49" t="inlineStr"/>
     </row>
@@ -3790,7 +3822,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EPIC</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3799,52 +3831,52 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1014</v>
+        <v>23567.8</v>
       </c>
       <c r="E50" t="n">
-        <v>0.7345917025543246</v>
+        <v>0.1230380629502966</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8978792899408284</v>
+        <v>0.1300912787786726</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-29 20:39</t>
+          <t>2026-07-29 16:35</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-30 06:51</t>
+          <t>2026-07-29 19:30</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>744.88</v>
+        <v>2899.74</v>
       </c>
       <c r="J50" t="n">
-        <v>22.23</v>
+        <v>5.73</v>
       </c>
       <c r="K50" t="n">
-        <v>165.57</v>
+        <v>166.23</v>
       </c>
       <c r="L50" t="n">
-        <v>66.69</v>
+        <v>17.2</v>
       </c>
       <c r="M50" t="n">
-        <v>496.72</v>
+        <v>498.69</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="n">
-        <v>111.14</v>
+        <v>28.66</v>
       </c>
       <c r="P50" t="n">
-        <v>827.87</v>
+        <v>831.14</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="n">
-        <v>222.28</v>
+        <v>57.33</v>
       </c>
       <c r="S50" t="n">
-        <v>1655.74</v>
+        <v>1662.29</v>
       </c>
       <c r="T50" t="inlineStr"/>
     </row>
@@ -3854,57 +3886,61 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ERA</t>
+          <t>EPIC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>33356.4</v>
+        <v>2027.9</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0675</v>
+        <v>0.7345917025543246</v>
       </c>
       <c r="F51" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.844</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-30 07:57</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>2026-07-29 20:39</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:19</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2251.56</v>
+        <v>1489.68</v>
       </c>
       <c r="J51" t="n">
-        <v>-2.07</v>
+        <v>14.89</v>
       </c>
       <c r="K51" t="n">
-        <v>-46.7</v>
+        <v>221.87</v>
       </c>
       <c r="L51" t="n">
-        <v>-6.22</v>
+        <v>44.68</v>
       </c>
       <c r="M51" t="n">
-        <v>-140.1</v>
+        <v>665.61</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
-        <v>-10.37</v>
+        <v>74.47</v>
       </c>
       <c r="P51" t="n">
-        <v>-233.49</v>
+        <v>1109.35</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="n">
-        <v>-20.74</v>
+        <v>148.94</v>
       </c>
       <c r="S51" t="n">
-        <v>-466.99</v>
+        <v>2218.69</v>
       </c>
       <c r="T51" t="inlineStr"/>
     </row>
@@ -3914,57 +3950,61 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AGLD</t>
+          <t>EPIC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>14834.6</v>
+        <v>1014</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1517843959392232</v>
+        <v>0.7345917025543246</v>
       </c>
       <c r="F52" t="n">
-        <v>0.147</v>
+        <v>0.8978792899408284</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-30 08:04</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>2026-07-29 20:39</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:51</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2251.66</v>
+        <v>744.88</v>
       </c>
       <c r="J52" t="n">
-        <v>-3.15</v>
+        <v>22.23</v>
       </c>
       <c r="K52" t="n">
-        <v>-70.97</v>
+        <v>165.57</v>
       </c>
       <c r="L52" t="n">
-        <v>-9.460000000000001</v>
+        <v>66.69</v>
       </c>
       <c r="M52" t="n">
-        <v>-212.92</v>
+        <v>496.72</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
-        <v>-15.76</v>
+        <v>111.14</v>
       </c>
       <c r="P52" t="n">
-        <v>-354.87</v>
+        <v>827.87</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="n">
-        <v>-31.52</v>
+        <v>222.28</v>
       </c>
       <c r="S52" t="n">
-        <v>-709.75</v>
+        <v>1655.74</v>
       </c>
       <c r="T52" t="inlineStr"/>
     </row>
@@ -3974,59 +4014,1075 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PYTH</t>
+          <t>ERA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>55792.1</v>
+        <v>33356.4</v>
       </c>
       <c r="E53" t="n">
-        <v>0.041</v>
+        <v>0.0675</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0414</v>
+        <v>0.06544116361477857</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-30 08:11</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>2026-07-30 07:57</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:27</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>2287.48</v>
+        <v>2251.56</v>
       </c>
       <c r="J53" t="n">
-        <v>0.98</v>
+        <v>-3.05</v>
       </c>
       <c r="K53" t="n">
-        <v>22.32</v>
+        <v>-68.68000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>2.93</v>
+        <v>-9.15</v>
       </c>
       <c r="M53" t="n">
-        <v>66.95</v>
+        <v>-206.03</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
-        <v>4.88</v>
+        <v>-15.25</v>
       </c>
       <c r="P53" t="n">
-        <v>111.58</v>
+        <v>-343.38</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="n">
-        <v>9.76</v>
+        <v>-30.5</v>
       </c>
       <c r="S53" t="n">
-        <v>223.17</v>
+        <v>-686.75</v>
       </c>
       <c r="T53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AGLD</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>14834.6</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.1517843959392232</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-07-30 08:04</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:27</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>2251.66</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-41.31</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="M54" t="n">
+        <v>-123.92</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="n">
+        <v>-9.17</v>
+      </c>
+      <c r="P54" t="n">
+        <v>-206.53</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="n">
+        <v>-18.34</v>
+      </c>
+      <c r="S54" t="n">
+        <v>-413.05</v>
+      </c>
+      <c r="T54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PYTH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>55792.1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.0411</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-07-30 08:11</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:27</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>2287.48</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K55" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M55" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P55" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S55" t="n">
+        <v>55.79</v>
+      </c>
+      <c r="T55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FIL</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>6336.88</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:37</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:24</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>4473.84</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K56" t="n">
+        <v>76.04000000000001</v>
+      </c>
+      <c r="L56" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M56" t="n">
+        <v>228.13</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P56" t="n">
+        <v>380.21</v>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="n">
+        <v>17</v>
+      </c>
+      <c r="S56" t="n">
+        <v>760.4299999999999</v>
+      </c>
+      <c r="T56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NIGHT</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>125409</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.01825474902120262</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.01817</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:43</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>2289.31</v>
+      </c>
+      <c r="J57" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-10.63</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="M57" t="n">
+        <v>-31.88</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="P57" t="n">
+        <v>-53.14</v>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="n">
+        <v>-4.64</v>
+      </c>
+      <c r="S57" t="n">
+        <v>-106.28</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>20011</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.07548835965087614</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.09925</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:18</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-07-31 05:20</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>1510.6</v>
+      </c>
+      <c r="J58" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="K58" t="n">
+        <v>475.49</v>
+      </c>
+      <c r="L58" t="n">
+        <v>94.43000000000001</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1426.48</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>157.39</v>
+      </c>
+      <c r="P58" t="n">
+        <v>2377.47</v>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="n">
+        <v>314.77</v>
+      </c>
+      <c r="S58" t="n">
+        <v>4754.94</v>
+      </c>
+      <c r="T58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>651</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.07548835965087614</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.12302</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:18</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-07-31 08:17</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.14</v>
+      </c>
+      <c r="J59" t="n">
+        <v>62.97</v>
+      </c>
+      <c r="K59" t="n">
+        <v>30.94</v>
+      </c>
+      <c r="L59" t="n">
+        <v>188.9</v>
+      </c>
+      <c r="M59" t="n">
+        <v>92.83</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="n">
+        <v>314.83</v>
+      </c>
+      <c r="P59" t="n">
+        <v>154.72</v>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="n">
+        <v>629.66</v>
+      </c>
+      <c r="S59" t="n">
+        <v>309.43</v>
+      </c>
+      <c r="T59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>9356</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.07548835965087614</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.06426999999999999</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:18</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>706.27</v>
+      </c>
+      <c r="J60" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-104.96</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-44.58</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-314.88</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>-74.31</v>
+      </c>
+      <c r="P60" t="n">
+        <v>-524.79</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="n">
+        <v>-100</v>
+      </c>
+      <c r="S60" t="n">
+        <v>-706.27</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PEOPLE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>653866.1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.006940588409461815</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.00653</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:47</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>4538.22</v>
+      </c>
+      <c r="J61" t="n">
+        <v>-5.92</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-268.47</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-17.75</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-805.41</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>-29.58</v>
+      </c>
+      <c r="P61" t="n">
+        <v>-1342.35</v>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="n">
+        <v>-59.16</v>
+      </c>
+      <c r="S61" t="n">
+        <v>-2684.7</v>
+      </c>
+      <c r="T61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ROBO</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>220379</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.01228</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-07-31 08:27</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:30</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>2975.12</v>
+      </c>
+      <c r="J62" t="n">
+        <v>-9.039999999999999</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-268.86</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-27.11</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-806.59</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="n">
+        <v>-45.19</v>
+      </c>
+      <c r="P62" t="n">
+        <v>-1344.31</v>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="n">
+        <v>-90.37</v>
+      </c>
+      <c r="S62" t="n">
+        <v>-2688.62</v>
+      </c>
+      <c r="T62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ROBO</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>110190</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.01228</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-07-31 08:27</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:30</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>1487.57</v>
+      </c>
+      <c r="J63" t="n">
+        <v>-9.039999999999999</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-134.43</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-27.11</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-403.3</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="n">
+        <v>-45.19</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-672.16</v>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="n">
+        <v>-90.37</v>
+      </c>
+      <c r="S63" t="n">
+        <v>-1344.32</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CFX</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>106828</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.04149347287228067</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.04294</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-07-31 13:00</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="n">
+        <v>4432.66</v>
+      </c>
+      <c r="J64" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K64" t="n">
+        <v>154.53</v>
+      </c>
+      <c r="L64" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="M64" t="n">
+        <v>463.59</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="P64" t="n">
+        <v>772.65</v>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="n">
+        <v>34.86</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1545.3</v>
+      </c>
+      <c r="T64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>GMT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>325667.9</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.00676</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.00663</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-07-31 13:55</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="n">
+        <v>2201.52</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-42.34</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-5.77</v>
+      </c>
+      <c r="M65" t="n">
+        <v>-127.01</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="n">
+        <v>-9.619999999999999</v>
+      </c>
+      <c r="P65" t="n">
+        <v>-211.68</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="n">
+        <v>-19.23</v>
+      </c>
+      <c r="S65" t="n">
+        <v>-423.37</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SAGA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>339939.6</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.01236</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-07-31 17:04</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="n">
+        <v>4283.24</v>
+      </c>
+      <c r="J66" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-81.59</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="M66" t="n">
+        <v>-244.76</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="n">
+        <v>-9.52</v>
+      </c>
+      <c r="P66" t="n">
+        <v>-407.93</v>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="n">
+        <v>-19.05</v>
+      </c>
+      <c r="S66" t="n">
+        <v>-815.86</v>
+      </c>
+      <c r="T66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>97950.02</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.02804405102724839</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.03081</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-07-31 17:13</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:28</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>2746.92</v>
+      </c>
+      <c r="J67" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="K67" t="n">
+        <v>270.92</v>
+      </c>
+      <c r="L67" t="n">
+        <v>29.59</v>
+      </c>
+      <c r="M67" t="n">
+        <v>812.77</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1354.62</v>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="n">
+        <v>98.63</v>
+      </c>
+      <c r="S67" t="n">
+        <v>2709.25</v>
+      </c>
+      <c r="T67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>TLM</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>765466</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.001873560456366487</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.001648650814013947</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-08-01 07:57</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:31</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>1434.15</v>
+      </c>
+      <c r="J68" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-172.16</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-36.01</v>
+      </c>
+      <c r="M68" t="n">
+        <v>-516.48</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="n">
+        <v>-60.02</v>
+      </c>
+      <c r="P68" t="n">
+        <v>-860.8</v>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="n">
+        <v>-100</v>
+      </c>
+      <c r="S68" t="n">
+        <v>-1434.15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>TLM</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>382734</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.001873560456366487</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.001648</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-08-01 07:57</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:31</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>717.08</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-12.04</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-86.33</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-36.12</v>
+      </c>
+      <c r="M69" t="n">
+        <v>-258.99</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="n">
+        <v>-60.2</v>
+      </c>
+      <c r="P69" t="n">
+        <v>-431.65</v>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="n">
+        <v>-100</v>
+      </c>
+      <c r="S69" t="n">
+        <v>-717.08</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4039,7 +5095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T53"/>
+  <dimension ref="A1:T69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4162,7 +5218,7 @@
         <v>12.61</v>
       </c>
       <c r="E2" t="n">
-        <v>1.462</v>
+        <v>1.426</v>
       </c>
       <c r="F2" t="n">
         <v>1.589</v>
@@ -4177,30 +5233,30 @@
         <v>20.04</v>
       </c>
       <c r="J2" t="n">
-        <v>8.69</v>
+        <v>11.43</v>
       </c>
       <c r="K2" t="n">
-        <v>1.74</v>
+        <v>2.29</v>
       </c>
       <c r="L2" t="n">
-        <v>23.98</v>
+        <v>30.77</v>
       </c>
       <c r="M2" t="n">
-        <v>4.8</v>
+        <v>6.17</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>39.96</v>
+        <v>51.29</v>
       </c>
       <c r="P2" t="n">
-        <v>8.01</v>
+        <v>10.28</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>79.92</v>
+        <v>102.58</v>
       </c>
       <c r="S2" t="n">
-        <v>16.01</v>
+        <v>20.55</v>
       </c>
       <c r="T2" t="inlineStr"/>
     </row>
@@ -4222,7 +5278,7 @@
         <v>12.586</v>
       </c>
       <c r="E3" t="n">
-        <v>1.462</v>
+        <v>1.426</v>
       </c>
       <c r="F3" t="n">
         <v>1.588</v>
@@ -4237,30 +5293,30 @@
         <v>19.99</v>
       </c>
       <c r="J3" t="n">
-        <v>8.619999999999999</v>
+        <v>11.36</v>
       </c>
       <c r="K3" t="n">
-        <v>1.72</v>
+        <v>2.27</v>
       </c>
       <c r="L3" t="n">
-        <v>23.8</v>
+        <v>30.6</v>
       </c>
       <c r="M3" t="n">
-        <v>4.76</v>
+        <v>6.12</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>39.67</v>
+        <v>51.01</v>
       </c>
       <c r="P3" t="n">
-        <v>7.93</v>
+        <v>10.19</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>79.34999999999999</v>
+        <v>102.02</v>
       </c>
       <c r="S3" t="n">
-        <v>15.86</v>
+        <v>20.39</v>
       </c>
       <c r="T3" t="inlineStr"/>
     </row>
@@ -4282,7 +5338,7 @@
         <v>12.586</v>
       </c>
       <c r="E4" t="n">
-        <v>1.462</v>
+        <v>1.426</v>
       </c>
       <c r="F4" t="n">
         <v>1.59</v>
@@ -4297,30 +5353,30 @@
         <v>20.01</v>
       </c>
       <c r="J4" t="n">
-        <v>8.76</v>
+        <v>11.5</v>
       </c>
       <c r="K4" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="L4" t="n">
-        <v>24.15</v>
+        <v>30.94</v>
       </c>
       <c r="M4" t="n">
-        <v>4.83</v>
+        <v>6.19</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>40.25</v>
+        <v>51.57</v>
       </c>
       <c r="P4" t="n">
-        <v>8.06</v>
+        <v>10.32</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>80.5</v>
+        <v>103.14</v>
       </c>
       <c r="S4" t="n">
-        <v>16.11</v>
+        <v>20.64</v>
       </c>
       <c r="T4" t="inlineStr"/>
     </row>
@@ -4335,14 +5391,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37807</v>
+        <v>37769</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000501</v>
+        <v>0.000511</v>
       </c>
       <c r="F5" t="n">
         <v>0.000529</v>
@@ -4352,35 +5408,39 @@
           <t>2026-07-26 20:50</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:27</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>19.98</v>
       </c>
       <c r="J5" t="n">
-        <v>5.59</v>
+        <v>3.52</v>
       </c>
       <c r="K5" t="n">
-        <v>1.12</v>
+        <v>0.7</v>
       </c>
       <c r="L5" t="n">
-        <v>15.88</v>
+        <v>10.21</v>
       </c>
       <c r="M5" t="n">
-        <v>3.18</v>
+        <v>2.04</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>26.47</v>
+        <v>17.01</v>
       </c>
       <c r="P5" t="n">
-        <v>5.29</v>
+        <v>3.4</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>52.93</v>
+        <v>34.03</v>
       </c>
       <c r="S5" t="n">
-        <v>10.59</v>
+        <v>6.8</v>
       </c>
       <c r="T5" t="inlineStr"/>
     </row>
@@ -4390,67 +5450,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>MEME</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>123</v>
+        <v>38</v>
       </c>
       <c r="E6" t="n">
-        <v>0.12306</v>
+        <v>0.00051</v>
       </c>
       <c r="F6" t="n">
-        <v>0.10701</v>
+        <v>0.000529</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-26 21:08</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-07-27 00:05</t>
-        </is>
-      </c>
+          <t>2026-07-26 20:50</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>13.16</v>
+        <v>0.02</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.04</v>
+        <v>3.73</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.72</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-45</v>
+        <v>10.78</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.92</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>-74.98999999999999</v>
+        <v>17.96</v>
       </c>
       <c r="P6" t="n">
-        <v>-9.869999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>-100</v>
+        <v>35.92</v>
       </c>
       <c r="S6" t="n">
-        <v>-13.16</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4467,10 +5519,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="E7" t="n">
-        <v>0.13911</v>
+        <v>0.12306</v>
       </c>
       <c r="F7" t="n">
         <v>0.10701</v>
@@ -4486,37 +5538,33 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>6.63</v>
+        <v>13.16</v>
       </c>
       <c r="J7" t="n">
-        <v>-23.08</v>
+        <v>-13.04</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.53</v>
+        <v>-1.72</v>
       </c>
       <c r="L7" t="n">
-        <v>-89.98999999999999</v>
+        <v>-45</v>
       </c>
       <c r="M7" t="n">
-        <v>-5.97</v>
+        <v>-5.92</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>-100</v>
+        <v>-74.98999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-6.63</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>-9.869999999999999</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
         <v>-100</v>
       </c>
       <c r="S7" t="n">
-        <v>-6.63</v>
+        <v>-13.16</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -4535,14 +5583,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07357</v>
+        <v>0.13911</v>
       </c>
       <c r="F8" t="n">
         <v>0.10701</v>
@@ -4552,37 +5600,49 @@
           <t>2026-07-26 21:08</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:05</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>0.11</v>
+        <v>6.63</v>
       </c>
       <c r="J8" t="n">
-        <v>45.45</v>
+        <v>-23.08</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05</v>
+        <v>-1.53</v>
       </c>
       <c r="L8" t="n">
-        <v>93.75</v>
+        <v>-89.98999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1</v>
+        <v>-5.97</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>156.25</v>
+        <v>-100</v>
       </c>
       <c r="P8" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+        <v>-6.63</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="R8" t="n">
-        <v>312.49</v>
+        <v>-100</v>
       </c>
       <c r="S8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="T8" t="inlineStr"/>
+        <v>-6.63</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4590,7 +5650,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4599,52 +5659,52 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>30.6</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3689</v>
+        <v>0.09925</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4356</v>
+        <v>0.10701</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-27 07:10</t>
+          <t>2026-07-26 21:08</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:13</t>
+          <t>2026-07-31 05:20</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>13.33</v>
+        <v>0.11</v>
       </c>
       <c r="J9" t="n">
-        <v>18.08</v>
+        <v>7.82</v>
       </c>
       <c r="K9" t="n">
-        <v>2.41</v>
+        <v>0.01</v>
       </c>
       <c r="L9" t="n">
-        <v>45.94</v>
+        <v>21.75</v>
       </c>
       <c r="M9" t="n">
-        <v>6.12</v>
+        <v>0.02</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>76.56</v>
+        <v>36.26</v>
       </c>
       <c r="P9" t="n">
-        <v>10.21</v>
+        <v>0.04</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>153.12</v>
+        <v>72.52</v>
       </c>
       <c r="S9" t="n">
-        <v>20.41</v>
+        <v>0.08</v>
       </c>
       <c r="T9" t="inlineStr"/>
     </row>
@@ -4663,7 +5723,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>30.6</v>
       </c>
       <c r="E10" t="n">
         <v>0.3689</v>
@@ -4682,33 +5742,33 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6.66</v>
+        <v>13.33</v>
       </c>
       <c r="J10" t="n">
         <v>18.08</v>
       </c>
       <c r="K10" t="n">
-        <v>1.21</v>
+        <v>2.41</v>
       </c>
       <c r="L10" t="n">
         <v>45.94</v>
       </c>
       <c r="M10" t="n">
-        <v>3.06</v>
+        <v>6.12</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
         <v>76.56</v>
       </c>
       <c r="P10" t="n">
-        <v>5.1</v>
+        <v>10.21</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
         <v>153.12</v>
       </c>
       <c r="S10" t="n">
-        <v>10.21</v>
+        <v>20.41</v>
       </c>
       <c r="T10" t="inlineStr"/>
     </row>
@@ -4718,7 +5778,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4727,52 +5787,52 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>53871.4</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1529837884294821</v>
+        <v>0.3689</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1805085023364255</v>
+        <v>0.4356</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-27 07:20</t>
+          <t>2026-07-27 07:10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-27 15:10</t>
+          <t>2026-07-27 08:13</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>9724.25</v>
+        <v>6.66</v>
       </c>
       <c r="J11" t="n">
-        <v>17.99</v>
+        <v>18.08</v>
       </c>
       <c r="K11" t="n">
-        <v>1749.58</v>
+        <v>1.21</v>
       </c>
       <c r="L11" t="n">
-        <v>45.75</v>
+        <v>45.94</v>
       </c>
       <c r="M11" t="n">
-        <v>4448.38</v>
+        <v>3.06</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>76.23999999999999</v>
+        <v>76.56</v>
       </c>
       <c r="P11" t="n">
-        <v>7413.97</v>
+        <v>5.1</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>152.48</v>
+        <v>153.12</v>
       </c>
       <c r="S11" t="n">
-        <v>14827.95</v>
+        <v>10.21</v>
       </c>
       <c r="T11" t="inlineStr"/>
     </row>
@@ -4791,10 +5851,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>26935.8</v>
+        <v>53871.4</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1529</v>
+        <v>0.1529837884294821</v>
       </c>
       <c r="F12" t="n">
         <v>0.1805085023364255</v>
@@ -4810,33 +5870,33 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4862.14</v>
+        <v>9724.25</v>
       </c>
       <c r="J12" t="n">
-        <v>18.06</v>
+        <v>17.99</v>
       </c>
       <c r="K12" t="n">
-        <v>877.9400000000001</v>
+        <v>1749.58</v>
       </c>
       <c r="L12" t="n">
-        <v>45.88</v>
+        <v>45.75</v>
       </c>
       <c r="M12" t="n">
-        <v>2230.97</v>
+        <v>4448.38</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>76.47</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>3718.29</v>
+        <v>7413.97</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>152.95</v>
+        <v>152.48</v>
       </c>
       <c r="S12" t="n">
-        <v>7436.57</v>
+        <v>14827.95</v>
       </c>
       <c r="T12" t="inlineStr"/>
     </row>
@@ -4846,7 +5906,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KAITO</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4855,52 +5915,52 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6823</v>
+        <v>26935.8</v>
       </c>
       <c r="E13" t="n">
-        <v>1.305925994430602</v>
+        <v>0.1529</v>
       </c>
       <c r="F13" t="n">
-        <v>1.194796722849186</v>
+        <v>0.1805085023364255</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-27 07:30</t>
+          <t>2026-07-27 07:20</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-27 21:51</t>
+          <t>2026-07-27 15:10</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8152.1</v>
+        <v>4862.14</v>
       </c>
       <c r="J13" t="n">
-        <v>-8.51</v>
+        <v>18.06</v>
       </c>
       <c r="K13" t="n">
-        <v>-693.71</v>
+        <v>877.9400000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-27.9</v>
+        <v>45.88</v>
       </c>
       <c r="M13" t="n">
-        <v>-2274.71</v>
+        <v>2230.97</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>-46.51</v>
+        <v>76.47</v>
       </c>
       <c r="P13" t="n">
-        <v>-3791.18</v>
+        <v>3718.29</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>-93.01000000000001</v>
+        <v>152.95</v>
       </c>
       <c r="S13" t="n">
-        <v>-7582.35</v>
+        <v>7436.57</v>
       </c>
       <c r="T13" t="inlineStr"/>
     </row>
@@ -4910,7 +5970,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NIL</t>
+          <t>KAITO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4919,52 +5979,52 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2669.9</v>
+        <v>6823</v>
       </c>
       <c r="E14" t="n">
-        <v>0.03987</v>
+        <v>1.305925994430602</v>
       </c>
       <c r="F14" t="n">
-        <v>0.04716</v>
+        <v>1.194796722849186</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-27 10:43</t>
+          <t>2026-07-27 07:30</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-27 13:07</t>
+          <t>2026-07-27 21:51</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>125.91</v>
+        <v>8152.1</v>
       </c>
       <c r="J14" t="n">
-        <v>18.28</v>
+        <v>-8.51</v>
       </c>
       <c r="K14" t="n">
-        <v>23.02</v>
+        <v>-693.71</v>
       </c>
       <c r="L14" t="n">
-        <v>46.37</v>
+        <v>-27.9</v>
       </c>
       <c r="M14" t="n">
-        <v>58.39</v>
+        <v>-2274.71</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>77.29000000000001</v>
+        <v>-46.51</v>
       </c>
       <c r="P14" t="n">
-        <v>97.31999999999999</v>
+        <v>-3791.18</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>154.58</v>
+        <v>-93.01000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>194.64</v>
+        <v>-7582.35</v>
       </c>
       <c r="T14" t="inlineStr"/>
     </row>
@@ -4983,7 +6043,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1335</v>
+        <v>2669.9</v>
       </c>
       <c r="E15" t="n">
         <v>0.03987</v>
@@ -5002,33 +6062,33 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>62.96</v>
+        <v>125.91</v>
       </c>
       <c r="J15" t="n">
         <v>18.28</v>
       </c>
       <c r="K15" t="n">
-        <v>11.51</v>
+        <v>23.02</v>
       </c>
       <c r="L15" t="n">
         <v>46.37</v>
       </c>
       <c r="M15" t="n">
-        <v>29.2</v>
+        <v>58.39</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
         <v>77.29000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>48.66</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
         <v>154.58</v>
       </c>
       <c r="S15" t="n">
-        <v>97.31999999999999</v>
+        <v>194.64</v>
       </c>
       <c r="T15" t="inlineStr"/>
     </row>
@@ -5038,57 +6098,61 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PUMP</t>
+          <t>NIL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>48154</v>
+        <v>1335</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001969</v>
+        <v>0.03987</v>
       </c>
       <c r="F16" t="n">
-        <v>0.002129</v>
+        <v>0.04716</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-27 11:04</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>2026-07-27 10:43</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:07</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>102.52</v>
+        <v>62.96</v>
       </c>
       <c r="J16" t="n">
-        <v>8.130000000000001</v>
+        <v>18.28</v>
       </c>
       <c r="K16" t="n">
-        <v>8.33</v>
+        <v>11.51</v>
       </c>
       <c r="L16" t="n">
-        <v>22.55</v>
+        <v>46.37</v>
       </c>
       <c r="M16" t="n">
-        <v>23.11</v>
+        <v>29.2</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>37.58</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>38.52</v>
+        <v>48.66</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>75.15000000000001</v>
+        <v>154.58</v>
       </c>
       <c r="S16" t="n">
-        <v>77.05</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="T16" t="inlineStr"/>
     </row>
@@ -5098,7 +6162,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NIL</t>
+          <t>PUMP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5107,52 +6171,52 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6364.4</v>
+        <v>48154</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03846</v>
+        <v>0.001977</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04534</v>
+        <v>0.002129</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-27 14:22</t>
+          <t>2026-07-27 11:04</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-28 00:46</t>
+          <t>2026-07-30 16:27</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>288.56</v>
+        <v>102.52</v>
       </c>
       <c r="J17" t="n">
-        <v>17.89</v>
+        <v>7.69</v>
       </c>
       <c r="K17" t="n">
-        <v>51.62</v>
+        <v>7.88</v>
       </c>
       <c r="L17" t="n">
-        <v>45.52</v>
+        <v>21.42</v>
       </c>
       <c r="M17" t="n">
-        <v>131.36</v>
+        <v>21.96</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>75.87</v>
+        <v>35.7</v>
       </c>
       <c r="P17" t="n">
-        <v>218.94</v>
+        <v>36.6</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>151.74</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>437.87</v>
+        <v>73.19</v>
       </c>
       <c r="T17" t="inlineStr"/>
     </row>
@@ -5171,7 +6235,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3182.2</v>
+        <v>6364.4</v>
       </c>
       <c r="E18" t="n">
         <v>0.03846</v>
@@ -5190,33 +6254,33 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>144.28</v>
+        <v>288.56</v>
       </c>
       <c r="J18" t="n">
         <v>17.89</v>
       </c>
       <c r="K18" t="n">
-        <v>25.81</v>
+        <v>51.62</v>
       </c>
       <c r="L18" t="n">
         <v>45.52</v>
       </c>
       <c r="M18" t="n">
-        <v>65.68000000000001</v>
+        <v>131.36</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
         <v>75.87</v>
       </c>
       <c r="P18" t="n">
-        <v>109.47</v>
+        <v>218.94</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
         <v>151.74</v>
       </c>
       <c r="S18" t="n">
-        <v>218.94</v>
+        <v>437.87</v>
       </c>
       <c r="T18" t="inlineStr"/>
     </row>
@@ -5226,7 +6290,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEXE</t>
+          <t>NIL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5235,58 +6299,54 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.19</v>
+        <v>3182.2</v>
       </c>
       <c r="E19" t="n">
-        <v>3.082</v>
+        <v>0.03846</v>
       </c>
       <c r="F19" t="n">
-        <v>2.631</v>
+        <v>0.04534</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-27 14:31</t>
+          <t>2026-07-27 14:22</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-28 03:22</t>
+          <t>2026-07-28 00:46</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.76</v>
+        <v>144.28</v>
       </c>
       <c r="J19" t="n">
-        <v>-14.63</v>
+        <v>17.89</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.84</v>
+        <v>25.81</v>
       </c>
       <c r="L19" t="n">
-        <v>-51.43</v>
+        <v>45.52</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.96</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>-85.70999999999999</v>
+        <v>75.87</v>
       </c>
       <c r="P19" t="n">
-        <v>-4.94</v>
+        <v>109.47</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>-100</v>
+        <v>151.74</v>
       </c>
       <c r="S19" t="n">
-        <v>-5.76</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>218.94</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5303,17 +6363,17 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18.69</v>
+        <v>2.19</v>
       </c>
       <c r="E20" t="n">
         <v>3.082</v>
       </c>
       <c r="F20" t="n">
-        <v>2.68</v>
+        <v>2.631</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-27 14:42</t>
+          <t>2026-07-27 14:31</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -5322,33 +6382,33 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>50.09</v>
+        <v>5.76</v>
       </c>
       <c r="J20" t="n">
-        <v>-13.04</v>
+        <v>-14.63</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.53</v>
+        <v>-0.84</v>
       </c>
       <c r="L20" t="n">
-        <v>-45</v>
+        <v>-51.43</v>
       </c>
       <c r="M20" t="n">
-        <v>-22.54</v>
+        <v>-2.96</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>-75</v>
+        <v>-85.70999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-37.57</v>
+        <v>-4.94</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
         <v>-100</v>
       </c>
       <c r="S20" t="n">
-        <v>-50.09</v>
+        <v>-5.76</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -5371,10 +6431,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.45</v>
+        <v>18.69</v>
       </c>
       <c r="E21" t="n">
-        <v>3.338</v>
+        <v>3.082</v>
       </c>
       <c r="F21" t="n">
         <v>2.68</v>
@@ -5386,41 +6446,37 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-28 08:00</t>
+          <t>2026-07-28 03:22</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>28.01</v>
+        <v>50.09</v>
       </c>
       <c r="J21" t="n">
-        <v>-19.71</v>
+        <v>-13.04</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.52</v>
+        <v>-6.53</v>
       </c>
       <c r="L21" t="n">
-        <v>-73.66</v>
+        <v>-45</v>
       </c>
       <c r="M21" t="n">
-        <v>-20.63</v>
+        <v>-22.54</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="P21" t="n">
-        <v>-28.01</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>-37.57</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
         <v>-100</v>
       </c>
       <c r="S21" t="n">
-        <v>-28.01</v>
+        <v>-50.09</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -5439,14 +6495,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.19</v>
+        <v>10.45</v>
       </c>
       <c r="E22" t="n">
-        <v>2.495</v>
+        <v>3.338</v>
       </c>
       <c r="F22" t="n">
         <v>2.68</v>
@@ -5456,37 +6512,49 @@
           <t>2026-07-27 14:42</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-07-28 08:00</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>5.87</v>
+        <v>28.01</v>
       </c>
       <c r="J22" t="n">
-        <v>7.41</v>
+        <v>-19.71</v>
       </c>
       <c r="K22" t="n">
-        <v>0.44</v>
+        <v>-5.52</v>
       </c>
       <c r="L22" t="n">
-        <v>20.71</v>
+        <v>-73.66</v>
       </c>
       <c r="M22" t="n">
-        <v>1.22</v>
+        <v>-20.63</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>34.51</v>
+        <v>-100</v>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+        <v>-28.01</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="R22" t="n">
-        <v>69.03</v>
+        <v>-100</v>
       </c>
       <c r="S22" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="T22" t="inlineStr"/>
+        <v>-28.01</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5494,61 +6562,57 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RIF</t>
+          <t>DEXE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>57844</v>
+        <v>2.19</v>
       </c>
       <c r="E23" t="n">
-        <v>0.08083306825254132</v>
+        <v>2.432</v>
       </c>
       <c r="F23" t="n">
-        <v>0.07580000000000001</v>
+        <v>2.68</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-27 15:31</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-07-27 16:08</t>
-        </is>
-      </c>
+          <t>2026-07-27 14:42</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>4384.58</v>
+        <v>5.87</v>
       </c>
       <c r="J23" t="n">
-        <v>-6.23</v>
+        <v>10.2</v>
       </c>
       <c r="K23" t="n">
-        <v>-273.01</v>
+        <v>0.6</v>
       </c>
       <c r="L23" t="n">
-        <v>-19.92</v>
+        <v>27.76</v>
       </c>
       <c r="M23" t="n">
-        <v>-873.4</v>
+        <v>1.63</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>-33.2</v>
+        <v>46.27</v>
       </c>
       <c r="P23" t="n">
-        <v>-1455.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>-66.40000000000001</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>-2911.33</v>
+        <v>5.43</v>
       </c>
       <c r="T23" t="inlineStr"/>
     </row>
@@ -5567,52 +6631,52 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>53773</v>
+        <v>57844</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0885</v>
+        <v>0.08083306825254132</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0813</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-27 16:09</t>
+          <t>2026-07-27 15:31</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-27 17:03</t>
+          <t>2026-07-27 16:08</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4371.74</v>
+        <v>4384.58</v>
       </c>
       <c r="J24" t="n">
-        <v>-8.140000000000001</v>
+        <v>-6.23</v>
       </c>
       <c r="K24" t="n">
-        <v>-355.67</v>
+        <v>-273.01</v>
       </c>
       <c r="L24" t="n">
-        <v>-26.57</v>
+        <v>-19.92</v>
       </c>
       <c r="M24" t="n">
-        <v>-1161.5</v>
+        <v>-873.4</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
-        <v>-44.28</v>
+        <v>-33.2</v>
       </c>
       <c r="P24" t="n">
-        <v>-1935.83</v>
+        <v>-1455.66</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
-        <v>-88.56</v>
+        <v>-66.40000000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>-3871.66</v>
+        <v>-2911.33</v>
       </c>
       <c r="T24" t="inlineStr"/>
     </row>
@@ -5631,17 +6695,17 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>51795</v>
+        <v>53773</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08840365865431025</v>
+        <v>0.0885</v>
       </c>
       <c r="F25" t="n">
-        <v>0.083</v>
+        <v>0.0813</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-27 16:43</t>
+          <t>2026-07-27 16:09</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -5650,33 +6714,33 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4298.98</v>
+        <v>4371.74</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.11</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-262.77</v>
+        <v>-355.67</v>
       </c>
       <c r="L25" t="n">
-        <v>-19.53</v>
+        <v>-26.57</v>
       </c>
       <c r="M25" t="n">
-        <v>-839.65</v>
+        <v>-1161.5</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>-32.55</v>
+        <v>-44.28</v>
       </c>
       <c r="P25" t="n">
-        <v>-1399.41</v>
+        <v>-1935.83</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
-        <v>-65.09999999999999</v>
+        <v>-88.56</v>
       </c>
       <c r="S25" t="n">
-        <v>-2798.82</v>
+        <v>-3871.66</v>
       </c>
       <c r="T25" t="inlineStr"/>
     </row>
@@ -5686,7 +6750,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>RIF</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5695,58 +6759,54 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>840945.7</v>
+        <v>51795</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00335</v>
+        <v>0.08840365865431025</v>
       </c>
       <c r="F26" t="n">
-        <v>0.002913425293738117</v>
+        <v>0.083</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-27 21:57</t>
+          <t>2026-07-27 16:43</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-28 07:49</t>
+          <t>2026-07-27 17:03</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2450.03</v>
+        <v>4298.98</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.03</v>
+        <v>-6.11</v>
       </c>
       <c r="K26" t="n">
-        <v>-319.29</v>
+        <v>-262.77</v>
       </c>
       <c r="L26" t="n">
-        <v>-44.95</v>
+        <v>-19.53</v>
       </c>
       <c r="M26" t="n">
-        <v>-1101.41</v>
+        <v>-839.65</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
-        <v>-74.92</v>
+        <v>-32.55</v>
       </c>
       <c r="P26" t="n">
-        <v>-1835.68</v>
+        <v>-1399.41</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>-100</v>
+        <v>-65.09999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-2450.03</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>-2798.82</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -5763,10 +6823,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>526761.8</v>
+        <v>840945.7</v>
       </c>
       <c r="E27" t="n">
-        <v>0.00245</v>
+        <v>0.00335</v>
       </c>
       <c r="F27" t="n">
         <v>0.002913425293738117</v>
@@ -5778,39 +6838,43 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-29 12:18</t>
+          <t>2026-07-28 07:49</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1534.68</v>
+        <v>2450.03</v>
       </c>
       <c r="J27" t="n">
-        <v>18.92</v>
+        <v>-13.03</v>
       </c>
       <c r="K27" t="n">
-        <v>290.29</v>
+        <v>-319.29</v>
       </c>
       <c r="L27" t="n">
-        <v>47.72</v>
+        <v>-44.95</v>
       </c>
       <c r="M27" t="n">
-        <v>732.34</v>
+        <v>-1101.41</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
-        <v>79.53</v>
+        <v>-74.92</v>
       </c>
       <c r="P27" t="n">
-        <v>1220.57</v>
+        <v>-1835.68</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>159.07</v>
+        <v>-100</v>
       </c>
       <c r="S27" t="n">
-        <v>2441.15</v>
-      </c>
-      <c r="T27" t="inlineStr"/>
+        <v>-2450.03</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -5827,7 +6891,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>212577.7</v>
+        <v>526761.8</v>
       </c>
       <c r="E28" t="n">
         <v>0.00245</v>
@@ -5846,33 +6910,33 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>619.33</v>
+        <v>1534.68</v>
       </c>
       <c r="J28" t="n">
         <v>18.92</v>
       </c>
       <c r="K28" t="n">
-        <v>117.15</v>
+        <v>290.29</v>
       </c>
       <c r="L28" t="n">
         <v>47.72</v>
       </c>
       <c r="M28" t="n">
-        <v>295.54</v>
+        <v>732.34</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
         <v>79.53</v>
       </c>
       <c r="P28" t="n">
-        <v>492.57</v>
+        <v>1220.57</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
         <v>159.07</v>
       </c>
       <c r="S28" t="n">
-        <v>985.14</v>
+        <v>2441.15</v>
       </c>
       <c r="T28" t="inlineStr"/>
     </row>
@@ -5882,7 +6946,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ACH</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5891,58 +6955,54 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>683496</v>
+        <v>212577.7</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00496</v>
+        <v>0.00245</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00432</v>
+        <v>0.002913425293738117</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-27 22:08</t>
+          <t>2026-07-27 21:57</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-28 06:42</t>
+          <t>2026-07-29 12:18</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2952.7</v>
+        <v>619.33</v>
       </c>
       <c r="J29" t="n">
-        <v>-12.9</v>
+        <v>18.92</v>
       </c>
       <c r="K29" t="n">
-        <v>-380.99</v>
+        <v>117.15</v>
       </c>
       <c r="L29" t="n">
-        <v>-44.44</v>
+        <v>47.72</v>
       </c>
       <c r="M29" t="n">
-        <v>-1312.31</v>
+        <v>295.54</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
-        <v>-74.06999999999999</v>
+        <v>79.53</v>
       </c>
       <c r="P29" t="n">
-        <v>-2187.19</v>
+        <v>492.57</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>-100</v>
+        <v>159.07</v>
       </c>
       <c r="S29" t="n">
-        <v>-2952.7</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>985.14</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5959,7 +7019,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>341748</v>
+        <v>683496</v>
       </c>
       <c r="E30" t="n">
         <v>0.00496</v>
@@ -5974,37 +7034,37 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-29 10:24</t>
+          <t>2026-07-28 06:42</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1476.35</v>
+        <v>2952.7</v>
       </c>
       <c r="J30" t="n">
         <v>-12.9</v>
       </c>
       <c r="K30" t="n">
-        <v>-190.5</v>
+        <v>-380.99</v>
       </c>
       <c r="L30" t="n">
         <v>-44.44</v>
       </c>
       <c r="M30" t="n">
-        <v>-656.16</v>
+        <v>-1312.31</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
         <v>-74.06999999999999</v>
       </c>
       <c r="P30" t="n">
-        <v>-1093.59</v>
+        <v>-2187.19</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
         <v>-100</v>
       </c>
       <c r="S30" t="n">
-        <v>-1476.35</v>
+        <v>-2952.7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -6018,7 +7078,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>COTI</t>
+          <t>ACH</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6027,54 +7087,58 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>339015</v>
+        <v>341748</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01354643759125702</v>
+        <v>0.00496</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01316130808371311</v>
+        <v>0.00432</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-27 22:14</t>
+          <t>2026-07-27 22:08</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-27 22:30</t>
+          <t>2026-07-29 10:24</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4461.88</v>
+        <v>1476.35</v>
       </c>
       <c r="J31" t="n">
-        <v>-2.84</v>
+        <v>-12.9</v>
       </c>
       <c r="K31" t="n">
-        <v>-126.85</v>
+        <v>-190.5</v>
       </c>
       <c r="L31" t="n">
-        <v>-8.779999999999999</v>
+        <v>-44.44</v>
       </c>
       <c r="M31" t="n">
-        <v>-391.69</v>
+        <v>-656.16</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
-        <v>-14.63</v>
+        <v>-74.06999999999999</v>
       </c>
       <c r="P31" t="n">
-        <v>-652.8200000000001</v>
+        <v>-1093.59</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
-        <v>-29.26</v>
+        <v>-100</v>
       </c>
       <c r="S31" t="n">
-        <v>-1305.65</v>
-      </c>
-      <c r="T31" t="inlineStr"/>
+        <v>-1476.35</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -6091,52 +7155,52 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>327219</v>
+        <v>339015</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01372472677320082</v>
+        <v>0.01354643759125702</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01350763555905984</v>
+        <v>0.01316130808371311</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-27 22:31</t>
+          <t>2026-07-27 22:14</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-27 22:53</t>
+          <t>2026-07-27 22:30</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4419.95</v>
+        <v>4461.88</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.58</v>
+        <v>-2.84</v>
       </c>
       <c r="K32" t="n">
-        <v>-69.91</v>
+        <v>-126.85</v>
       </c>
       <c r="L32" t="n">
-        <v>-4.82</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>-213.11</v>
+        <v>-391.69</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
-        <v>-8.039999999999999</v>
+        <v>-14.63</v>
       </c>
       <c r="P32" t="n">
-        <v>-355.18</v>
+        <v>-652.8200000000001</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="n">
-        <v>-16.07</v>
+        <v>-29.26</v>
       </c>
       <c r="S32" t="n">
-        <v>-710.36</v>
+        <v>-1305.65</v>
       </c>
       <c r="T32" t="inlineStr"/>
     </row>
@@ -6155,17 +7219,17 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>329868</v>
+        <v>327219</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01371</v>
+        <v>0.01372472677320082</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0134805300301939</v>
+        <v>0.01350763555905984</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-27 22:48</t>
+          <t>2026-07-27 22:31</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -6174,33 +7238,33 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4446.8</v>
+        <v>4419.95</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.67</v>
+        <v>-1.58</v>
       </c>
       <c r="K33" t="n">
-        <v>-74.43000000000001</v>
+        <v>-69.91</v>
       </c>
       <c r="L33" t="n">
-        <v>-5.11</v>
+        <v>-4.82</v>
       </c>
       <c r="M33" t="n">
-        <v>-227.08</v>
+        <v>-213.11</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
-        <v>-8.51</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="P33" t="n">
-        <v>-378.47</v>
+        <v>-355.18</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
-        <v>-17.02</v>
+        <v>-16.07</v>
       </c>
       <c r="S33" t="n">
-        <v>-756.95</v>
+        <v>-710.36</v>
       </c>
       <c r="T33" t="inlineStr"/>
     </row>
@@ -6219,52 +7283,52 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>215458</v>
+        <v>329868</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01141</v>
+        <v>0.01371</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0135</v>
+        <v>0.0134805300301939</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-27 23:10</t>
+          <t>2026-07-27 22:48</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-27 23:58</t>
+          <t>2026-07-27 22:53</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2908.68</v>
+        <v>4446.8</v>
       </c>
       <c r="J34" t="n">
-        <v>18.32</v>
+        <v>-1.67</v>
       </c>
       <c r="K34" t="n">
-        <v>532.79</v>
+        <v>-74.43000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>46.44</v>
+        <v>-5.11</v>
       </c>
       <c r="M34" t="n">
-        <v>1350.92</v>
+        <v>-227.08</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
-        <v>77.41</v>
+        <v>-8.51</v>
       </c>
       <c r="P34" t="n">
-        <v>2251.54</v>
+        <v>-378.47</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="n">
-        <v>154.81</v>
+        <v>-17.02</v>
       </c>
       <c r="S34" t="n">
-        <v>4503.07</v>
+        <v>-756.95</v>
       </c>
       <c r="T34" t="inlineStr"/>
     </row>
@@ -6283,7 +7347,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>107730</v>
+        <v>215458</v>
       </c>
       <c r="E35" t="n">
         <v>0.01141</v>
@@ -6302,33 +7366,33 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1454.36</v>
+        <v>2908.68</v>
       </c>
       <c r="J35" t="n">
         <v>18.32</v>
       </c>
       <c r="K35" t="n">
-        <v>266.4</v>
+        <v>532.79</v>
       </c>
       <c r="L35" t="n">
         <v>46.44</v>
       </c>
       <c r="M35" t="n">
-        <v>675.47</v>
+        <v>1350.92</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
         <v>77.41</v>
       </c>
       <c r="P35" t="n">
-        <v>1125.78</v>
+        <v>2251.54</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="n">
         <v>154.81</v>
       </c>
       <c r="S35" t="n">
-        <v>2251.56</v>
+        <v>4503.07</v>
       </c>
       <c r="T35" t="inlineStr"/>
     </row>
@@ -6338,57 +7402,61 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DGB</t>
+          <t>COTI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1094443.9</v>
+        <v>107730</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00392</v>
+        <v>0.01141</v>
       </c>
       <c r="F36" t="n">
-        <v>0.00407789726362402</v>
+        <v>0.0135</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-27 23:16</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>2026-07-27 23:10</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-07-27 23:58</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>4463.03</v>
+        <v>1454.36</v>
       </c>
       <c r="J36" t="n">
-        <v>4.03</v>
+        <v>18.32</v>
       </c>
       <c r="K36" t="n">
-        <v>179.77</v>
+        <v>266.4</v>
       </c>
       <c r="L36" t="n">
-        <v>11.62</v>
+        <v>46.44</v>
       </c>
       <c r="M36" t="n">
-        <v>518.4299999999999</v>
+        <v>675.47</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
-        <v>19.36</v>
+        <v>77.41</v>
       </c>
       <c r="P36" t="n">
-        <v>864.05</v>
+        <v>1125.78</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="n">
-        <v>38.72</v>
+        <v>154.81</v>
       </c>
       <c r="S36" t="n">
-        <v>1728.1</v>
+        <v>2251.56</v>
       </c>
       <c r="T36" t="inlineStr"/>
     </row>
@@ -6403,52 +7471,56 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>990569.4</v>
       </c>
       <c r="E37" t="n">
-        <v>0.00392</v>
+        <v>0.003901090282013557</v>
       </c>
       <c r="F37" t="n">
-        <v>0.004176841910319458</v>
+        <v>0.00407789726362402</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-27 23:22</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>2026-07-27 23:16</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:27</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>4137.45</v>
+        <v>4039.44</v>
       </c>
       <c r="J37" t="n">
-        <v>6.55</v>
+        <v>4.53</v>
       </c>
       <c r="K37" t="n">
-        <v>271.09</v>
+        <v>183.08</v>
       </c>
       <c r="L37" t="n">
-        <v>18.45</v>
+        <v>13.01</v>
       </c>
       <c r="M37" t="n">
-        <v>763.26</v>
+        <v>525.42</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
-        <v>30.75</v>
+        <v>21.68</v>
       </c>
       <c r="P37" t="n">
-        <v>1272.1</v>
+        <v>875.7</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="n">
-        <v>61.49</v>
+        <v>43.36</v>
       </c>
       <c r="S37" t="n">
-        <v>2544.2</v>
+        <v>1751.4</v>
       </c>
       <c r="T37" t="inlineStr"/>
     </row>
@@ -6458,57 +7530,61 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PROM</t>
+          <t>DGB</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2232.33</v>
+        <v>103874.5</v>
       </c>
       <c r="E38" t="n">
-        <v>1.852</v>
+        <v>0.0039</v>
       </c>
       <c r="F38" t="n">
-        <v>2.026488516482778</v>
+        <v>0.00407789726362402</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-28 08:52</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>2026-07-27 23:16</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:27</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>4523.79</v>
+        <v>423.59</v>
       </c>
       <c r="J38" t="n">
-        <v>9.42</v>
+        <v>4.56</v>
       </c>
       <c r="K38" t="n">
-        <v>426.21</v>
+        <v>19.32</v>
       </c>
       <c r="L38" t="n">
-        <v>25.83</v>
+        <v>13.09</v>
       </c>
       <c r="M38" t="n">
-        <v>1168.55</v>
+        <v>55.44</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
-        <v>43.05</v>
+        <v>21.81</v>
       </c>
       <c r="P38" t="n">
-        <v>1947.58</v>
+        <v>92.39</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="n">
-        <v>86.09999999999999</v>
+        <v>43.62</v>
       </c>
       <c r="S38" t="n">
-        <v>3895.16</v>
+        <v>184.79</v>
       </c>
       <c r="T38" t="inlineStr"/>
     </row>
@@ -6518,7 +7594,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>DGB</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6527,52 +7603,52 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13672</v>
+        <v>990569.4</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3293</v>
+        <v>0.0039</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3214995318899941</v>
+        <v>0.004176841910319458</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-28 10:28</t>
+          <t>2026-07-27 23:22</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-28 10:38</t>
+          <t>2026-07-30 16:27</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4395.54</v>
+        <v>4137.45</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.37</v>
+        <v>7.1</v>
       </c>
       <c r="K39" t="n">
-        <v>-104.12</v>
+        <v>293.7</v>
       </c>
       <c r="L39" t="n">
-        <v>-7.28</v>
+        <v>19.88</v>
       </c>
       <c r="M39" t="n">
-        <v>-319.94</v>
+        <v>822.6900000000001</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
-        <v>-12.13</v>
+        <v>33.14</v>
       </c>
       <c r="P39" t="n">
-        <v>-533.24</v>
+        <v>1371.16</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
-        <v>-24.26</v>
+        <v>66.28</v>
       </c>
       <c r="S39" t="n">
-        <v>-1066.48</v>
+        <v>2742.31</v>
       </c>
       <c r="T39" t="inlineStr"/>
     </row>
@@ -6582,7 +7658,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>PROM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6591,52 +7667,52 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13363.4</v>
+        <v>2232.33</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3472084095364952</v>
+        <v>1.822</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3372</v>
+        <v>2.026488516482778</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-28 10:44</t>
+          <t>2026-07-28 08:52</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-28 11:31</t>
+          <t>2026-07-30 16:27</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4506.14</v>
+        <v>4523.79</v>
       </c>
       <c r="J40" t="n">
-        <v>-2.88</v>
+        <v>11.22</v>
       </c>
       <c r="K40" t="n">
-        <v>-129.89</v>
+        <v>507.72</v>
       </c>
       <c r="L40" t="n">
-        <v>-8.9</v>
+        <v>30.27</v>
       </c>
       <c r="M40" t="n">
-        <v>-401.24</v>
+        <v>1369.46</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
-        <v>-14.84</v>
+        <v>50.45</v>
       </c>
       <c r="P40" t="n">
-        <v>-668.73</v>
+        <v>2282.43</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="n">
-        <v>-29.68</v>
+        <v>100.91</v>
       </c>
       <c r="S40" t="n">
-        <v>-1337.46</v>
+        <v>4564.86</v>
       </c>
       <c r="T40" t="inlineStr"/>
     </row>
@@ -6646,7 +7722,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>COTI</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6655,58 +7731,54 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>240574</v>
+        <v>13672</v>
       </c>
       <c r="E41" t="n">
-        <v>0.01416</v>
+        <v>0.3293</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01232132044936846</v>
+        <v>0.3214995318899941</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-28 11:38</t>
+          <t>2026-07-28 10:28</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-28 16:00</t>
+          <t>2026-07-28 10:38</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2964.19</v>
+        <v>4395.54</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.99</v>
+        <v>-2.37</v>
       </c>
       <c r="K41" t="n">
-        <v>-384.9</v>
+        <v>-104.12</v>
       </c>
       <c r="L41" t="n">
-        <v>-44.77</v>
+        <v>-7.28</v>
       </c>
       <c r="M41" t="n">
-        <v>-1327.02</v>
+        <v>-319.94</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
-        <v>-74.61</v>
+        <v>-12.13</v>
       </c>
       <c r="P41" t="n">
-        <v>-2211.69</v>
+        <v>-533.24</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
-        <v>-100</v>
+        <v>-24.26</v>
       </c>
       <c r="S41" t="n">
-        <v>-2964.19</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>-1066.48</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6714,7 +7786,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>COTI</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6723,52 +7795,52 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>120288</v>
+        <v>13363.4</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01287637137536579</v>
+        <v>0.3472084095364952</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01232132044936846</v>
+        <v>0.3372</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-28 11:38</t>
+          <t>2026-07-28 10:44</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-28 19:50</t>
+          <t>2026-07-28 11:31</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1482.11</v>
+        <v>4506.14</v>
       </c>
       <c r="J42" t="n">
-        <v>-4.31</v>
+        <v>-2.88</v>
       </c>
       <c r="K42" t="n">
-        <v>-63.89</v>
+        <v>-129.89</v>
       </c>
       <c r="L42" t="n">
-        <v>-13.51</v>
+        <v>-8.9</v>
       </c>
       <c r="M42" t="n">
-        <v>-200.3</v>
+        <v>-401.24</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
-        <v>-22.52</v>
+        <v>-14.84</v>
       </c>
       <c r="P42" t="n">
-        <v>-333.83</v>
+        <v>-668.73</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="n">
-        <v>-45.05</v>
+        <v>-29.68</v>
       </c>
       <c r="S42" t="n">
-        <v>-667.66</v>
+        <v>-1337.46</v>
       </c>
       <c r="T42" t="inlineStr"/>
     </row>
@@ -6778,7 +7850,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RIF</t>
+          <t>COTI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6787,52 +7859,52 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>32966</v>
+        <v>240574</v>
       </c>
       <c r="E43" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.01416</v>
       </c>
       <c r="F43" t="n">
-        <v>0.08372395551061679</v>
+        <v>0.01232132044936846</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-28 18:23</t>
+          <t>2026-07-28 11:38</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-29 00:08</t>
+          <t>2026-07-28 16:00</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2760.04</v>
+        <v>2964.19</v>
       </c>
       <c r="J43" t="n">
-        <v>-12.97</v>
+        <v>-12.99</v>
       </c>
       <c r="K43" t="n">
-        <v>-357.95</v>
+        <v>-384.9</v>
       </c>
       <c r="L43" t="n">
-        <v>-44.7</v>
+        <v>-44.77</v>
       </c>
       <c r="M43" t="n">
-        <v>-1233.86</v>
+        <v>-1327.02</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
-        <v>-74.51000000000001</v>
+        <v>-74.61</v>
       </c>
       <c r="P43" t="n">
-        <v>-2056.43</v>
+        <v>-2211.69</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="n">
         <v>-100</v>
       </c>
       <c r="S43" t="n">
-        <v>-2760.04</v>
+        <v>-2964.19</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6846,7 +7918,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RIF</t>
+          <t>COTI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6855,58 +7927,54 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>16484</v>
+        <v>120288</v>
       </c>
       <c r="E44" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.01287637137536579</v>
       </c>
       <c r="F44" t="n">
-        <v>0.08372395551061679</v>
+        <v>0.01232132044936846</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-28 18:23</t>
+          <t>2026-07-28 11:38</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-29 14:11</t>
+          <t>2026-07-28 19:50</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1380.11</v>
+        <v>1482.11</v>
       </c>
       <c r="J44" t="n">
-        <v>-13.42</v>
+        <v>-4.31</v>
       </c>
       <c r="K44" t="n">
-        <v>-185.19</v>
+        <v>-63.89</v>
       </c>
       <c r="L44" t="n">
-        <v>-46.5</v>
+        <v>-13.51</v>
       </c>
       <c r="M44" t="n">
-        <v>-641.6900000000001</v>
+        <v>-200.3</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
-        <v>-77.48999999999999</v>
+        <v>-22.52</v>
       </c>
       <c r="P44" t="n">
-        <v>-1069.49</v>
+        <v>-333.83</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="n">
-        <v>-100</v>
+        <v>-45.05</v>
       </c>
       <c r="S44" t="n">
-        <v>-1380.11</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>-667.66</v>
+      </c>
+      <c r="T44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6914,7 +7982,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>RIF</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6923,52 +7991,52 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>16982</v>
+        <v>32966</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2034</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1769</v>
+        <v>0.08372395551061679</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47</t>
+          <t>2026-07-28 18:23</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-30 02:38</t>
+          <t>2026-07-29 00:08</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3004.12</v>
+        <v>2760.04</v>
       </c>
       <c r="J45" t="n">
-        <v>-13.03</v>
+        <v>-12.97</v>
       </c>
       <c r="K45" t="n">
-        <v>-391.39</v>
+        <v>-357.95</v>
       </c>
       <c r="L45" t="n">
-        <v>-44.94</v>
+        <v>-44.7</v>
       </c>
       <c r="M45" t="n">
-        <v>-1350.07</v>
+        <v>-1233.86</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
-        <v>-74.90000000000001</v>
+        <v>-74.51000000000001</v>
       </c>
       <c r="P45" t="n">
-        <v>-2250.11</v>
+        <v>-2056.43</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="n">
         <v>-100</v>
       </c>
       <c r="S45" t="n">
-        <v>-3004.12</v>
+        <v>-2760.04</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6982,59 +8050,67 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>RIF</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>8491</v>
+        <v>16484</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0765</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1769</v>
+        <v>0.08372395551061679</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>2026-07-28 18:23</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:11</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1502.06</v>
+        <v>1380.11</v>
       </c>
       <c r="J46" t="n">
-        <v>131.24</v>
+        <v>-13.42</v>
       </c>
       <c r="K46" t="n">
-        <v>1971.33</v>
+        <v>-185.19</v>
       </c>
       <c r="L46" t="n">
-        <v>170.27</v>
+        <v>-46.5</v>
       </c>
       <c r="M46" t="n">
-        <v>2557.49</v>
+        <v>-641.6900000000001</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
-        <v>283.78</v>
+        <v>-77.48999999999999</v>
       </c>
       <c r="P46" t="n">
-        <v>4262.48</v>
+        <v>-1069.49</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="n">
-        <v>567.55</v>
+        <v>-100</v>
       </c>
       <c r="S46" t="n">
-        <v>8524.959999999999</v>
-      </c>
-      <c r="T46" t="inlineStr"/>
+        <v>-1380.11</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -7042,59 +8118,67 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SYRUP</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13570.8</v>
+        <v>16982</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1623</v>
+        <v>0.2034</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1668545406313555</v>
+        <v>0.1769</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-29 16:18</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>2026-07-29 10:47</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:38</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>2264.35</v>
+        <v>3004.12</v>
       </c>
       <c r="J47" t="n">
-        <v>2.81</v>
+        <v>-13.03</v>
       </c>
       <c r="K47" t="n">
-        <v>63.54</v>
+        <v>-391.39</v>
       </c>
       <c r="L47" t="n">
-        <v>8.19</v>
+        <v>-44.94</v>
       </c>
       <c r="M47" t="n">
-        <v>185.43</v>
+        <v>-1350.07</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
-        <v>13.65</v>
+        <v>-74.90000000000001</v>
       </c>
       <c r="P47" t="n">
-        <v>309.04</v>
+        <v>-2250.11</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="n">
-        <v>27.3</v>
+        <v>-100</v>
       </c>
       <c r="S47" t="n">
-        <v>618.09</v>
-      </c>
-      <c r="T47" t="inlineStr"/>
+        <v>-3004.12</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7102,61 +8186,57 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>23567.8</v>
+        <v>8491</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1300912787786726</v>
+        <v>0.0556</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1230380629502966</v>
+        <v>0.1769</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-29 16:35</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2026-07-29 19:30</t>
-        </is>
-      </c>
+          <t>2026-07-29 10:47</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>2899.74</v>
+        <v>1502.06</v>
       </c>
       <c r="J48" t="n">
-        <v>-5.42</v>
+        <v>218.17</v>
       </c>
       <c r="K48" t="n">
-        <v>-157.22</v>
+        <v>3276.97</v>
       </c>
       <c r="L48" t="n">
-        <v>-17.2</v>
+        <v>205.71</v>
       </c>
       <c r="M48" t="n">
-        <v>-498.69</v>
+        <v>3089.87</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="n">
-        <v>-28.66</v>
+        <v>342.85</v>
       </c>
       <c r="P48" t="n">
-        <v>-831.14</v>
+        <v>5149.79</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="n">
-        <v>-57.33</v>
+        <v>685.7</v>
       </c>
       <c r="S48" t="n">
-        <v>-1662.29</v>
+        <v>10299.58</v>
       </c>
       <c r="T48" t="inlineStr"/>
     </row>
@@ -7166,7 +8246,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EPIC</t>
+          <t>SYRUP</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7175,58 +8255,54 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2027.9</v>
+        <v>13570.8</v>
       </c>
       <c r="E49" t="n">
-        <v>0.844</v>
+        <v>0.1617</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7345917025543246</v>
+        <v>0.1668545406313555</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-29 20:39</t>
+          <t>2026-07-29 16:18</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-30 06:19</t>
+          <t>2026-07-30 16:27</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1489.68</v>
+        <v>2264.35</v>
       </c>
       <c r="J49" t="n">
-        <v>-12.96</v>
+        <v>3.19</v>
       </c>
       <c r="K49" t="n">
-        <v>-193.11</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>-44.68</v>
+        <v>9.27</v>
       </c>
       <c r="M49" t="n">
-        <v>-665.61</v>
+        <v>209.85</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="n">
-        <v>-74.47</v>
+        <v>15.45</v>
       </c>
       <c r="P49" t="n">
-        <v>-1109.35</v>
+        <v>349.76</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="n">
-        <v>-100</v>
+        <v>30.89</v>
       </c>
       <c r="S49" t="n">
-        <v>-1489.68</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>699.51</v>
+      </c>
+      <c r="T49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7234,7 +8310,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EPIC</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7243,62 +8319,54 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1014</v>
+        <v>23567.8</v>
       </c>
       <c r="E50" t="n">
-        <v>0.8978792899408284</v>
+        <v>0.1300912787786726</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7345917025543246</v>
+        <v>0.1230380629502966</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-29 20:39</t>
+          <t>2026-07-29 16:35</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-30 06:51</t>
+          <t>2026-07-29 19:30</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>744.88</v>
+        <v>2899.74</v>
       </c>
       <c r="J50" t="n">
-        <v>-18.19</v>
+        <v>-5.42</v>
       </c>
       <c r="K50" t="n">
-        <v>-135.46</v>
+        <v>-157.22</v>
       </c>
       <c r="L50" t="n">
-        <v>-66.69</v>
+        <v>-17.2</v>
       </c>
       <c r="M50" t="n">
-        <v>-496.72</v>
+        <v>-498.69</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="n">
-        <v>-100</v>
+        <v>-28.66</v>
       </c>
       <c r="P50" t="n">
-        <v>-744.88</v>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>-831.14</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="n">
-        <v>-100</v>
+        <v>-57.33</v>
       </c>
       <c r="S50" t="n">
-        <v>-744.88</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>-1662.29</v>
+      </c>
+      <c r="T50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7306,59 +8374,67 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ERA</t>
+          <t>EPIC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>33356.4</v>
+        <v>2027.9</v>
       </c>
       <c r="E51" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.844</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0675</v>
+        <v>0.7345917025543246</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-30 07:57</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>2026-07-29 20:39</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:19</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2251.56</v>
+        <v>1489.68</v>
       </c>
       <c r="J51" t="n">
-        <v>2.12</v>
+        <v>-12.96</v>
       </c>
       <c r="K51" t="n">
-        <v>47.69</v>
+        <v>-193.11</v>
       </c>
       <c r="L51" t="n">
-        <v>6.22</v>
+        <v>-44.68</v>
       </c>
       <c r="M51" t="n">
-        <v>140.1</v>
+        <v>-665.61</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
-        <v>10.37</v>
+        <v>-74.47</v>
       </c>
       <c r="P51" t="n">
-        <v>233.49</v>
+        <v>-1109.35</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="n">
-        <v>20.74</v>
+        <v>-100</v>
       </c>
       <c r="S51" t="n">
-        <v>466.99</v>
-      </c>
-      <c r="T51" t="inlineStr"/>
+        <v>-1489.68</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7366,59 +8442,71 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AGLD</t>
+          <t>EPIC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>14834.6</v>
+        <v>1014</v>
       </c>
       <c r="E52" t="n">
-        <v>0.147</v>
+        <v>0.8978792899408284</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1517843959392232</v>
+        <v>0.7345917025543246</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-30 08:04</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>2026-07-29 20:39</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:51</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2251.66</v>
+        <v>744.88</v>
       </c>
       <c r="J52" t="n">
-        <v>3.25</v>
+        <v>-18.19</v>
       </c>
       <c r="K52" t="n">
-        <v>73.28</v>
+        <v>-135.46</v>
       </c>
       <c r="L52" t="n">
-        <v>9.460000000000001</v>
+        <v>-66.69</v>
       </c>
       <c r="M52" t="n">
-        <v>212.92</v>
+        <v>-496.72</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
-        <v>15.76</v>
+        <v>-100</v>
       </c>
       <c r="P52" t="n">
-        <v>354.87</v>
-      </c>
-      <c r="Q52" t="inlineStr"/>
+        <v>-744.88</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="R52" t="n">
-        <v>31.52</v>
+        <v>-100</v>
       </c>
       <c r="S52" t="n">
-        <v>709.75</v>
-      </c>
-      <c r="T52" t="inlineStr"/>
+        <v>-744.88</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7426,59 +8514,1083 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PYTH</t>
+          <t>ERA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>55792.1</v>
+        <v>33356.4</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0414</v>
+        <v>0.06544116361477857</v>
       </c>
       <c r="F53" t="n">
-        <v>0.041</v>
+        <v>0.0675</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-30 08:11</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>2026-07-30 07:57</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:27</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>2287.48</v>
+        <v>2251.56</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.97</v>
+        <v>3.15</v>
       </c>
       <c r="K53" t="n">
-        <v>-22.1</v>
+        <v>70.84</v>
       </c>
       <c r="L53" t="n">
-        <v>-2.93</v>
+        <v>9.15</v>
       </c>
       <c r="M53" t="n">
-        <v>-66.95</v>
+        <v>206.03</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
-        <v>-4.88</v>
+        <v>15.25</v>
       </c>
       <c r="P53" t="n">
-        <v>-111.58</v>
+        <v>343.38</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="n">
-        <v>-9.76</v>
+        <v>30.5</v>
       </c>
       <c r="S53" t="n">
-        <v>-223.17</v>
+        <v>686.75</v>
       </c>
       <c r="T53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AGLD</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>14834.6</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.1517843959392232</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-07-30 08:04</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:27</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>2251.66</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="K54" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="L54" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M54" t="n">
+        <v>123.92</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="P54" t="n">
+        <v>206.53</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="S54" t="n">
+        <v>413.05</v>
+      </c>
+      <c r="T54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PYTH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>55792.1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.0411</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-07-30 08:11</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:27</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>2287.48</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-5.57</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="M55" t="n">
+        <v>-16.74</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="P55" t="n">
+        <v>-27.9</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="S55" t="n">
+        <v>-55.79</v>
+      </c>
+      <c r="T55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FIL</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>6336.88</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:37</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:24</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>4473.84</v>
+      </c>
+      <c r="J56" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-74.77</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="M56" t="n">
+        <v>-228.13</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="P56" t="n">
+        <v>-380.21</v>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="n">
+        <v>-17</v>
+      </c>
+      <c r="S56" t="n">
+        <v>-760.4299999999999</v>
+      </c>
+      <c r="T56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NIGHT</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>125409</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.01817</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.01825474902120262</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-07-30 16:43</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>2289.31</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K57" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M57" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="P57" t="n">
+        <v>53.14</v>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="S57" t="n">
+        <v>106.28</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>20011</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.09925</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.07548835965087614</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:18</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-07-31 05:20</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>1510.6</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-23.94</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-361.66</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-94.43000000000001</v>
+      </c>
+      <c r="M58" t="n">
+        <v>-1426.48</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>-100</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-1510.6</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R58" t="n">
+        <v>-100</v>
+      </c>
+      <c r="S58" t="n">
+        <v>-1510.6</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>651</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.12302</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.07548835965087614</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:18</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-07-31 08:17</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.14</v>
+      </c>
+      <c r="J59" t="n">
+        <v>-38.64</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-18.99</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-100</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-49.14</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>-100</v>
+      </c>
+      <c r="P59" t="n">
+        <v>-49.14</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="R59" t="n">
+        <v>-100</v>
+      </c>
+      <c r="S59" t="n">
+        <v>-49.14</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>9356</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.06426999999999999</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.07548835965087614</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:18</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>706.27</v>
+      </c>
+      <c r="J60" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="K60" t="n">
+        <v>123.28</v>
+      </c>
+      <c r="L60" t="n">
+        <v>44.58</v>
+      </c>
+      <c r="M60" t="n">
+        <v>314.88</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>74.31</v>
+      </c>
+      <c r="P60" t="n">
+        <v>524.79</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="n">
+        <v>148.61</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1049.59</v>
+      </c>
+      <c r="T60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PEOPLE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>653866.1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.00653</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.006940588409461815</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:47</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>4538.22</v>
+      </c>
+      <c r="J61" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="K61" t="n">
+        <v>285.35</v>
+      </c>
+      <c r="L61" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="M61" t="n">
+        <v>805.41</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1342.35</v>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="n">
+        <v>59.16</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2684.7</v>
+      </c>
+      <c r="T61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ROBO</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>220379</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.01228</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-07-31 08:27</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:30</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>2975.12</v>
+      </c>
+      <c r="J62" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="K62" t="n">
+        <v>295.57</v>
+      </c>
+      <c r="L62" t="n">
+        <v>27.11</v>
+      </c>
+      <c r="M62" t="n">
+        <v>806.59</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="n">
+        <v>45.19</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1344.31</v>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="n">
+        <v>90.37</v>
+      </c>
+      <c r="S62" t="n">
+        <v>2688.62</v>
+      </c>
+      <c r="T62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ROBO</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>110190</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.01228</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-07-31 08:27</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:30</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>1487.57</v>
+      </c>
+      <c r="J63" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="K63" t="n">
+        <v>147.79</v>
+      </c>
+      <c r="L63" t="n">
+        <v>27.11</v>
+      </c>
+      <c r="M63" t="n">
+        <v>403.3</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="n">
+        <v>45.19</v>
+      </c>
+      <c r="P63" t="n">
+        <v>672.16</v>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="n">
+        <v>90.37</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1344.32</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CFX</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>106828</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.04294</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.04149347287228067</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-07-31 13:00</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="n">
+        <v>4432.66</v>
+      </c>
+      <c r="J64" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-149.32</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-10.46</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-463.59</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="n">
+        <v>-17.43</v>
+      </c>
+      <c r="P64" t="n">
+        <v>-772.65</v>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="n">
+        <v>-34.86</v>
+      </c>
+      <c r="S64" t="n">
+        <v>-1545.3</v>
+      </c>
+      <c r="T64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>GMT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>325667.9</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.00663</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.00676</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-07-31 13:55</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="n">
+        <v>2201.52</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="K65" t="n">
+        <v>43.17</v>
+      </c>
+      <c r="L65" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="M65" t="n">
+        <v>127.01</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="P65" t="n">
+        <v>211.68</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="S65" t="n">
+        <v>423.37</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SAGA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>339939.6</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.01236</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-07-31 17:04</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="n">
+        <v>4283.24</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="K66" t="n">
+        <v>83.17</v>
+      </c>
+      <c r="L66" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="M66" t="n">
+        <v>244.76</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="P66" t="n">
+        <v>407.93</v>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="S66" t="n">
+        <v>815.86</v>
+      </c>
+      <c r="T66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>FLOW</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>97950.02</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.03081</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.02804405102724839</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-07-31 17:13</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:28</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>2746.92</v>
+      </c>
+      <c r="J67" t="n">
+        <v>-8.98</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-246.6</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-29.59</v>
+      </c>
+      <c r="M67" t="n">
+        <v>-812.77</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="n">
+        <v>-49.31</v>
+      </c>
+      <c r="P67" t="n">
+        <v>-1354.62</v>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="n">
+        <v>-98.63</v>
+      </c>
+      <c r="S67" t="n">
+        <v>-2709.25</v>
+      </c>
+      <c r="T67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>TLM</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>765466</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.001648650814013947</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.001873560456366487</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-08-01 07:57</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:31</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>1434.15</v>
+      </c>
+      <c r="J68" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="K68" t="n">
+        <v>195.65</v>
+      </c>
+      <c r="L68" t="n">
+        <v>36.01</v>
+      </c>
+      <c r="M68" t="n">
+        <v>516.48</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="n">
+        <v>60.02</v>
+      </c>
+      <c r="P68" t="n">
+        <v>860.8</v>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="n">
+        <v>120.04</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1721.61</v>
+      </c>
+      <c r="T68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>TLM</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>382734</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.001648</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.001873560456366487</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-08-01 07:57</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:31</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>717.08</v>
+      </c>
+      <c r="J69" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="K69" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="L69" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="M69" t="n">
+        <v>258.99</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="P69" t="n">
+        <v>431.65</v>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="n">
+        <v>120.39</v>
+      </c>
+      <c r="S69" t="n">
+        <v>863.3</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/leverage_journal.xlsx
+++ b/leverage_journal.xlsx
@@ -459,10 +459,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-232.95</v>
+        <v>106.18</v>
       </c>
       <c r="C2" t="n">
-        <v>45.6</v>
+        <v>47.8</v>
       </c>
       <c r="D2" t="inlineStr"/>
     </row>
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>888.99</v>
+        <v>2227.31</v>
       </c>
       <c r="C3" t="n">
-        <v>45.6</v>
+        <v>47.8</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -489,10 +489,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2482.98</v>
+        <v>4713.47</v>
       </c>
       <c r="C4" t="n">
-        <v>45.6</v>
+        <v>47.8</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18967.34</v>
+        <v>23502.04</v>
       </c>
       <c r="C5" t="n">
-        <v>45.6</v>
+        <v>47.8</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3991.18</v>
+        <v>4937.17</v>
       </c>
       <c r="C6" t="n">
-        <v>52.9</v>
+        <v>50.7</v>
       </c>
       <c r="D6" t="inlineStr"/>
     </row>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>742.51</v>
+        <v>-274.85</v>
       </c>
       <c r="C7" t="n">
-        <v>52.9</v>
+        <v>50.7</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2229.88</v>
+        <v>534.3200000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>52.9</v>
+        <v>52.2</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15984.55</v>
+        <v>12593.43</v>
       </c>
       <c r="C9" t="n">
-        <v>54.4</v>
+        <v>52.2</v>
       </c>
       <c r="D9" t="n">
         <v>16</v>
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T69"/>
+  <dimension ref="A1:T70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,7 +713,7 @@
         <v>1.589</v>
       </c>
       <c r="F2" t="n">
-        <v>1.426</v>
+        <v>1.434</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -725,36 +725,32 @@
         <v>20.04</v>
       </c>
       <c r="J2" t="n">
-        <v>-10.26</v>
+        <v>-9.75</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.06</v>
+        <v>-1.95</v>
       </c>
       <c r="L2" t="n">
-        <v>-30.77</v>
+        <v>-29.26</v>
       </c>
       <c r="M2" t="n">
-        <v>-6.17</v>
+        <v>-5.86</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>-51.29</v>
+        <v>-48.77</v>
       </c>
       <c r="P2" t="n">
-        <v>-10.28</v>
+        <v>-9.77</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>-100</v>
+        <v>-97.55</v>
       </c>
       <c r="S2" t="n">
-        <v>-20.04</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>-19.55</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -777,7 +773,7 @@
         <v>1.588</v>
       </c>
       <c r="F3" t="n">
-        <v>1.426</v>
+        <v>1.434</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -789,36 +785,32 @@
         <v>19.99</v>
       </c>
       <c r="J3" t="n">
-        <v>-10.2</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.04</v>
+        <v>-1.94</v>
       </c>
       <c r="L3" t="n">
-        <v>-30.6</v>
+        <v>-29.09</v>
       </c>
       <c r="M3" t="n">
-        <v>-6.12</v>
+        <v>-5.81</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>-51.01</v>
+        <v>-48.49</v>
       </c>
       <c r="P3" t="n">
-        <v>-10.19</v>
+        <v>-9.69</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>-100</v>
+        <v>-96.98</v>
       </c>
       <c r="S3" t="n">
-        <v>-19.99</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>-19.38</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -841,7 +833,7 @@
         <v>1.59</v>
       </c>
       <c r="F4" t="n">
-        <v>1.426</v>
+        <v>1.434</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -853,36 +845,32 @@
         <v>20.01</v>
       </c>
       <c r="J4" t="n">
-        <v>-10.31</v>
+        <v>-9.81</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.06</v>
+        <v>-1.96</v>
       </c>
       <c r="L4" t="n">
-        <v>-30.94</v>
+        <v>-29.43</v>
       </c>
       <c r="M4" t="n">
-        <v>-6.19</v>
+        <v>-5.89</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>-51.57</v>
+        <v>-49.06</v>
       </c>
       <c r="P4" t="n">
-        <v>-10.32</v>
+        <v>-9.82</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>-100</v>
+        <v>-98.11</v>
       </c>
       <c r="S4" t="n">
-        <v>-20.01</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>-19.63</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -969,7 +957,7 @@
         <v>0.000529</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00051</v>
+        <v>0.000496</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -981,27 +969,27 @@
         <v>0.02</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.59</v>
+        <v>-6.24</v>
       </c>
       <c r="K6" t="n">
         <v>-0</v>
       </c>
       <c r="L6" t="n">
-        <v>-10.78</v>
+        <v>-18.71</v>
       </c>
       <c r="M6" t="n">
         <v>-0</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>-17.96</v>
+        <v>-31.19</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>-35.92</v>
+        <v>-62.38</v>
       </c>
       <c r="S6" t="n">
         <v>-0.01</v>
@@ -2085,7 +2073,7 @@
         <v>2.68</v>
       </c>
       <c r="F23" t="n">
-        <v>2.432</v>
+        <v>2.258</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2097,32 +2085,36 @@
         <v>5.87</v>
       </c>
       <c r="J23" t="n">
-        <v>-9.25</v>
+        <v>-15.75</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.54</v>
+        <v>-0.92</v>
       </c>
       <c r="L23" t="n">
-        <v>-27.76</v>
+        <v>-47.24</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.63</v>
+        <v>-2.77</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>-46.27</v>
+        <v>-78.73</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.72</v>
+        <v>-4.62</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>-92.54000000000001</v>
+        <v>-100</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.43</v>
-      </c>
-      <c r="T23" t="inlineStr"/>
+        <v>-5.87</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3701,7 +3693,7 @@
         <v>0.1769</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0556</v>
+        <v>0.043</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3713,10 +3705,10 @@
         <v>1502.06</v>
       </c>
       <c r="J48" t="n">
-        <v>-68.56999999999999</v>
+        <v>-75.69</v>
       </c>
       <c r="K48" t="n">
-        <v>-1029.96</v>
+        <v>-1136.94</v>
       </c>
       <c r="L48" t="n">
         <v>-100</v>
@@ -4285,7 +4277,7 @@
         <v>0.01825474902120262</v>
       </c>
       <c r="F57" t="n">
-        <v>0.01817</v>
+        <v>0.0191</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -4297,30 +4289,30 @@
         <v>2289.31</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.46</v>
+        <v>4.63</v>
       </c>
       <c r="K57" t="n">
-        <v>-10.63</v>
+        <v>106</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.39</v>
+        <v>13.89</v>
       </c>
       <c r="M57" t="n">
-        <v>-31.88</v>
+        <v>318.01</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
-        <v>-2.32</v>
+        <v>23.15</v>
       </c>
       <c r="P57" t="n">
-        <v>-53.14</v>
+        <v>530.01</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="n">
-        <v>-4.64</v>
+        <v>46.3</v>
       </c>
       <c r="S57" t="n">
-        <v>-106.28</v>
+        <v>1060.02</v>
       </c>
       <c r="T57" t="inlineStr"/>
     </row>
@@ -4463,52 +4455,56 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>9356</v>
+        <v>9355</v>
       </c>
       <c r="E60" t="n">
         <v>0.07548835965087614</v>
       </c>
       <c r="F60" t="n">
-        <v>0.06426999999999999</v>
+        <v>0.06350149652592196</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>2026-07-30 17:18</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-08-03 01:06</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>706.27</v>
+        <v>706.1900000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>-14.86</v>
+        <v>-15.88</v>
       </c>
       <c r="K60" t="n">
-        <v>-104.96</v>
+        <v>-112.14</v>
       </c>
       <c r="L60" t="n">
-        <v>-44.58</v>
+        <v>-47.64</v>
       </c>
       <c r="M60" t="n">
-        <v>-314.88</v>
+        <v>-336.41</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="n">
-        <v>-74.31</v>
+        <v>-79.40000000000001</v>
       </c>
       <c r="P60" t="n">
-        <v>-524.79</v>
+        <v>-560.6900000000001</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="n">
         <v>-100</v>
       </c>
       <c r="S60" t="n">
-        <v>-706.27</v>
+        <v>-706.1900000000001</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -4522,7 +4518,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PEOPLE</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4531,50 +4527,54 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>653866.1</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>0.006940588409461815</v>
+        <v>0.07548835965087614</v>
       </c>
       <c r="F61" t="n">
-        <v>0.00653</v>
+        <v>0.06585000000000001</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-30 17:47</t>
+          <t>2026-07-30 17:18</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>4538.22</v>
+        <v>0.08</v>
       </c>
       <c r="J61" t="n">
-        <v>-5.92</v>
+        <v>-12.77</v>
       </c>
       <c r="K61" t="n">
-        <v>-268.47</v>
+        <v>-0.01</v>
       </c>
       <c r="L61" t="n">
-        <v>-17.75</v>
+        <v>-38.3</v>
       </c>
       <c r="M61" t="n">
-        <v>-805.41</v>
+        <v>-0.03</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="n">
-        <v>-29.58</v>
+        <v>-63.84</v>
       </c>
       <c r="P61" t="n">
-        <v>-1342.35</v>
+        <v>-0.05</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="n">
-        <v>-59.16</v>
+        <v>-100</v>
       </c>
       <c r="S61" t="n">
-        <v>-2684.7</v>
-      </c>
-      <c r="T61" t="inlineStr"/>
+        <v>-0.08</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4582,61 +4582,57 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ROBO</t>
+          <t>PEOPLE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>220379</v>
+        <v>653866.1</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0135</v>
+        <v>0.006940588409461815</v>
       </c>
       <c r="F62" t="n">
-        <v>0.01228</v>
+        <v>0.00712</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-31 08:27</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>2026-07-31 16:30</t>
-        </is>
-      </c>
+          <t>2026-07-30 17:47</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>2975.12</v>
+        <v>4538.22</v>
       </c>
       <c r="J62" t="n">
-        <v>-9.039999999999999</v>
+        <v>2.58</v>
       </c>
       <c r="K62" t="n">
-        <v>-268.86</v>
+        <v>117.31</v>
       </c>
       <c r="L62" t="n">
-        <v>-27.11</v>
+        <v>7.75</v>
       </c>
       <c r="M62" t="n">
-        <v>-806.59</v>
+        <v>351.93</v>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
-        <v>-45.19</v>
+        <v>12.92</v>
       </c>
       <c r="P62" t="n">
-        <v>-1344.31</v>
+        <v>586.5599999999999</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="n">
-        <v>-90.37</v>
+        <v>25.85</v>
       </c>
       <c r="S62" t="n">
-        <v>-2688.62</v>
+        <v>1173.11</v>
       </c>
       <c r="T62" t="inlineStr"/>
     </row>
@@ -4655,7 +4651,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>110190</v>
+        <v>220379</v>
       </c>
       <c r="E63" t="n">
         <v>0.0135</v>
@@ -4674,33 +4670,33 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1487.57</v>
+        <v>2975.12</v>
       </c>
       <c r="J63" t="n">
         <v>-9.039999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-134.43</v>
+        <v>-268.86</v>
       </c>
       <c r="L63" t="n">
         <v>-27.11</v>
       </c>
       <c r="M63" t="n">
-        <v>-403.3</v>
+        <v>-806.59</v>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
         <v>-45.19</v>
       </c>
       <c r="P63" t="n">
-        <v>-672.16</v>
+        <v>-1344.31</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="n">
         <v>-90.37</v>
       </c>
       <c r="S63" t="n">
-        <v>-1344.32</v>
+        <v>-2688.62</v>
       </c>
       <c r="T63" t="inlineStr"/>
     </row>
@@ -4710,57 +4706,61 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CFX</t>
+          <t>ROBO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>106828</v>
+        <v>110190</v>
       </c>
       <c r="E64" t="n">
-        <v>0.04149347287228067</v>
+        <v>0.0135</v>
       </c>
       <c r="F64" t="n">
-        <v>0.04294</v>
+        <v>0.01228</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-31 13:00</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>2026-07-31 08:27</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:30</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>4432.66</v>
+        <v>1487.57</v>
       </c>
       <c r="J64" t="n">
-        <v>3.49</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>154.53</v>
+        <v>-134.43</v>
       </c>
       <c r="L64" t="n">
-        <v>10.46</v>
+        <v>-27.11</v>
       </c>
       <c r="M64" t="n">
-        <v>463.59</v>
+        <v>-403.3</v>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
-        <v>17.43</v>
+        <v>-45.19</v>
       </c>
       <c r="P64" t="n">
-        <v>772.65</v>
+        <v>-672.16</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="n">
-        <v>34.86</v>
+        <v>-90.37</v>
       </c>
       <c r="S64" t="n">
-        <v>1545.3</v>
+        <v>-1344.32</v>
       </c>
       <c r="T64" t="inlineStr"/>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GMT</t>
+          <t>CFX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4779,48 +4779,48 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>325667.9</v>
+        <v>106828</v>
       </c>
       <c r="E65" t="n">
-        <v>0.00676</v>
+        <v>0.04149347287228067</v>
       </c>
       <c r="F65" t="n">
-        <v>0.00663</v>
+        <v>0.04085</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-31 13:55</t>
+          <t>2026-07-31 13:00</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>2201.52</v>
+        <v>4432.66</v>
       </c>
       <c r="J65" t="n">
-        <v>-1.92</v>
+        <v>-1.55</v>
       </c>
       <c r="K65" t="n">
-        <v>-42.34</v>
+        <v>-68.73999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>-5.77</v>
+        <v>-4.65</v>
       </c>
       <c r="M65" t="n">
-        <v>-127.01</v>
+        <v>-206.22</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
-        <v>-9.619999999999999</v>
+        <v>-7.75</v>
       </c>
       <c r="P65" t="n">
-        <v>-211.68</v>
+        <v>-343.7</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="n">
-        <v>-19.23</v>
+        <v>-15.51</v>
       </c>
       <c r="S65" t="n">
-        <v>-423.37</v>
+        <v>-687.41</v>
       </c>
       <c r="T65" t="inlineStr"/>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SAGA</t>
+          <t>GMT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4839,48 +4839,48 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>339939.6</v>
+        <v>325667.9</v>
       </c>
       <c r="E66" t="n">
-        <v>0.0126</v>
+        <v>0.00676</v>
       </c>
       <c r="F66" t="n">
-        <v>0.01236</v>
+        <v>0.00657</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-31 17:04</t>
+          <t>2026-07-31 13:55</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
-        <v>4283.24</v>
+        <v>2201.52</v>
       </c>
       <c r="J66" t="n">
-        <v>-1.9</v>
+        <v>-2.81</v>
       </c>
       <c r="K66" t="n">
-        <v>-81.59</v>
+        <v>-61.88</v>
       </c>
       <c r="L66" t="n">
-        <v>-5.71</v>
+        <v>-8.43</v>
       </c>
       <c r="M66" t="n">
-        <v>-244.76</v>
+        <v>-185.63</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
-        <v>-9.52</v>
+        <v>-14.05</v>
       </c>
       <c r="P66" t="n">
-        <v>-407.93</v>
+        <v>-309.38</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="n">
-        <v>-19.05</v>
+        <v>-28.11</v>
       </c>
       <c r="S66" t="n">
-        <v>-815.86</v>
+        <v>-618.77</v>
       </c>
       <c r="T66" t="inlineStr"/>
     </row>
@@ -4890,61 +4890,57 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>SAGA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>97950.02</v>
+        <v>339939.6</v>
       </c>
       <c r="E67" t="n">
-        <v>0.02804405102724839</v>
+        <v>0.0126</v>
       </c>
       <c r="F67" t="n">
-        <v>0.03081</v>
+        <v>0.01293</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-31 17:13</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>2026-07-31 23:28</t>
-        </is>
-      </c>
+          <t>2026-07-31 17:04</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
-        <v>2746.92</v>
+        <v>4283.24</v>
       </c>
       <c r="J67" t="n">
-        <v>9.859999999999999</v>
+        <v>2.62</v>
       </c>
       <c r="K67" t="n">
-        <v>270.92</v>
+        <v>112.18</v>
       </c>
       <c r="L67" t="n">
-        <v>29.59</v>
+        <v>7.86</v>
       </c>
       <c r="M67" t="n">
-        <v>812.77</v>
+        <v>336.54</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
-        <v>49.31</v>
+        <v>13.1</v>
       </c>
       <c r="P67" t="n">
-        <v>1354.62</v>
+        <v>560.9</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="n">
-        <v>98.63</v>
+        <v>26.19</v>
       </c>
       <c r="S67" t="n">
-        <v>2709.25</v>
+        <v>1121.8</v>
       </c>
       <c r="T67" t="inlineStr"/>
     </row>
@@ -4954,7 +4950,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TLM</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4963,58 +4959,54 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>765466</v>
+        <v>97950.02</v>
       </c>
       <c r="E68" t="n">
-        <v>0.001873560456366487</v>
+        <v>0.02804405102724839</v>
       </c>
       <c r="F68" t="n">
-        <v>0.001648650814013947</v>
+        <v>0.03081</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-08-01 07:57</t>
+          <t>2026-07-31 17:13</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-01 10:31</t>
+          <t>2026-07-31 23:28</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1434.15</v>
+        <v>2746.92</v>
       </c>
       <c r="J68" t="n">
-        <v>-12</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>-172.16</v>
+        <v>270.92</v>
       </c>
       <c r="L68" t="n">
-        <v>-36.01</v>
+        <v>29.59</v>
       </c>
       <c r="M68" t="n">
-        <v>-516.48</v>
+        <v>812.77</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
-        <v>-60.02</v>
+        <v>49.31</v>
       </c>
       <c r="P68" t="n">
-        <v>-860.8</v>
+        <v>1354.62</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="n">
-        <v>-100</v>
+        <v>98.63</v>
       </c>
       <c r="S68" t="n">
-        <v>-1434.15</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+        <v>2709.25</v>
+      </c>
+      <c r="T68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5031,13 +5023,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>382734</v>
+        <v>765466</v>
       </c>
       <c r="E69" t="n">
         <v>0.001873560456366487</v>
       </c>
       <c r="F69" t="n">
-        <v>0.001648</v>
+        <v>0.001648650814013947</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -5050,35 +5042,103 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>717.08</v>
+        <v>1434.15</v>
       </c>
       <c r="J69" t="n">
-        <v>-12.04</v>
+        <v>-12</v>
       </c>
       <c r="K69" t="n">
-        <v>-86.33</v>
+        <v>-172.16</v>
       </c>
       <c r="L69" t="n">
-        <v>-36.12</v>
+        <v>-36.01</v>
       </c>
       <c r="M69" t="n">
-        <v>-258.99</v>
+        <v>-516.48</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
-        <v>-60.2</v>
+        <v>-60.02</v>
       </c>
       <c r="P69" t="n">
-        <v>-431.65</v>
+        <v>-860.8</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="n">
         <v>-100</v>
       </c>
       <c r="S69" t="n">
+        <v>-1434.15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>TLM</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>382734</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.001873560456366487</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.001648</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-08-01 07:57</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:31</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>717.08</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-12.04</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-86.33</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-36.12</v>
+      </c>
+      <c r="M70" t="n">
+        <v>-258.99</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="n">
+        <v>-60.2</v>
+      </c>
+      <c r="P70" t="n">
+        <v>-431.65</v>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="n">
+        <v>-100</v>
+      </c>
+      <c r="S70" t="n">
         <v>-717.08</v>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -5095,7 +5155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T69"/>
+  <dimension ref="A1:T70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5218,7 +5278,7 @@
         <v>12.61</v>
       </c>
       <c r="E2" t="n">
-        <v>1.426</v>
+        <v>1.434</v>
       </c>
       <c r="F2" t="n">
         <v>1.589</v>
@@ -5233,30 +5293,30 @@
         <v>20.04</v>
       </c>
       <c r="J2" t="n">
-        <v>11.43</v>
+        <v>10.81</v>
       </c>
       <c r="K2" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="L2" t="n">
-        <v>30.77</v>
+        <v>29.26</v>
       </c>
       <c r="M2" t="n">
-        <v>6.17</v>
+        <v>5.86</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>51.29</v>
+        <v>48.77</v>
       </c>
       <c r="P2" t="n">
-        <v>10.28</v>
+        <v>9.77</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>102.58</v>
+        <v>97.55</v>
       </c>
       <c r="S2" t="n">
-        <v>20.55</v>
+        <v>19.55</v>
       </c>
       <c r="T2" t="inlineStr"/>
     </row>
@@ -5278,7 +5338,7 @@
         <v>12.586</v>
       </c>
       <c r="E3" t="n">
-        <v>1.426</v>
+        <v>1.434</v>
       </c>
       <c r="F3" t="n">
         <v>1.588</v>
@@ -5293,30 +5353,30 @@
         <v>19.99</v>
       </c>
       <c r="J3" t="n">
-        <v>11.36</v>
+        <v>10.74</v>
       </c>
       <c r="K3" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="L3" t="n">
-        <v>30.6</v>
+        <v>29.09</v>
       </c>
       <c r="M3" t="n">
-        <v>6.12</v>
+        <v>5.81</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>51.01</v>
+        <v>48.49</v>
       </c>
       <c r="P3" t="n">
-        <v>10.19</v>
+        <v>9.69</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>102.02</v>
+        <v>96.98</v>
       </c>
       <c r="S3" t="n">
-        <v>20.39</v>
+        <v>19.38</v>
       </c>
       <c r="T3" t="inlineStr"/>
     </row>
@@ -5338,7 +5398,7 @@
         <v>12.586</v>
       </c>
       <c r="E4" t="n">
-        <v>1.426</v>
+        <v>1.434</v>
       </c>
       <c r="F4" t="n">
         <v>1.59</v>
@@ -5353,30 +5413,30 @@
         <v>20.01</v>
       </c>
       <c r="J4" t="n">
-        <v>11.5</v>
+        <v>10.88</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="L4" t="n">
-        <v>30.94</v>
+        <v>29.43</v>
       </c>
       <c r="M4" t="n">
-        <v>6.19</v>
+        <v>5.89</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>51.57</v>
+        <v>49.06</v>
       </c>
       <c r="P4" t="n">
-        <v>10.32</v>
+        <v>9.82</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>103.14</v>
+        <v>98.11</v>
       </c>
       <c r="S4" t="n">
-        <v>20.64</v>
+        <v>19.63</v>
       </c>
       <c r="T4" t="inlineStr"/>
     </row>
@@ -5462,7 +5522,7 @@
         <v>38</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00051</v>
+        <v>0.000496</v>
       </c>
       <c r="F6" t="n">
         <v>0.000529</v>
@@ -5477,27 +5537,27 @@
         <v>0.02</v>
       </c>
       <c r="J6" t="n">
-        <v>3.73</v>
+        <v>6.65</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>10.78</v>
+        <v>18.71</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>17.96</v>
+        <v>31.19</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>35.92</v>
+        <v>62.38</v>
       </c>
       <c r="S6" t="n">
         <v>0.01</v>
@@ -6574,7 +6634,7 @@
         <v>2.19</v>
       </c>
       <c r="E23" t="n">
-        <v>2.432</v>
+        <v>2.258</v>
       </c>
       <c r="F23" t="n">
         <v>2.68</v>
@@ -6589,30 +6649,30 @@
         <v>5.87</v>
       </c>
       <c r="J23" t="n">
-        <v>10.2</v>
+        <v>18.69</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="L23" t="n">
-        <v>27.76</v>
+        <v>47.24</v>
       </c>
       <c r="M23" t="n">
-        <v>1.63</v>
+        <v>2.77</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>46.27</v>
+        <v>78.73</v>
       </c>
       <c r="P23" t="n">
-        <v>2.72</v>
+        <v>4.62</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>92.54000000000001</v>
+        <v>157.46</v>
       </c>
       <c r="S23" t="n">
-        <v>5.43</v>
+        <v>9.24</v>
       </c>
       <c r="T23" t="inlineStr"/>
     </row>
@@ -8198,7 +8258,7 @@
         <v>8491</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0556</v>
+        <v>0.043</v>
       </c>
       <c r="F48" t="n">
         <v>0.1769</v>
@@ -8213,30 +8273,30 @@
         <v>1502.06</v>
       </c>
       <c r="J48" t="n">
-        <v>218.17</v>
+        <v>311.4</v>
       </c>
       <c r="K48" t="n">
-        <v>3276.97</v>
+        <v>4677.34</v>
       </c>
       <c r="L48" t="n">
-        <v>205.71</v>
+        <v>227.08</v>
       </c>
       <c r="M48" t="n">
-        <v>3089.87</v>
+        <v>3410.83</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="n">
-        <v>342.85</v>
+        <v>378.46</v>
       </c>
       <c r="P48" t="n">
-        <v>5149.79</v>
+        <v>5684.72</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="n">
-        <v>685.7</v>
+        <v>756.92</v>
       </c>
       <c r="S48" t="n">
-        <v>10299.58</v>
+        <v>11369.45</v>
       </c>
       <c r="T48" t="inlineStr"/>
     </row>
@@ -8782,7 +8842,7 @@
         <v>125409</v>
       </c>
       <c r="E57" t="n">
-        <v>0.01817</v>
+        <v>0.0191</v>
       </c>
       <c r="F57" t="n">
         <v>0.01825474902120262</v>
@@ -8797,30 +8857,30 @@
         <v>2289.31</v>
       </c>
       <c r="J57" t="n">
-        <v>0.47</v>
+        <v>-4.43</v>
       </c>
       <c r="K57" t="n">
-        <v>10.68</v>
+        <v>-101.31</v>
       </c>
       <c r="L57" t="n">
-        <v>1.39</v>
+        <v>-13.89</v>
       </c>
       <c r="M57" t="n">
-        <v>31.88</v>
+        <v>-318.01</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
-        <v>2.32</v>
+        <v>-23.15</v>
       </c>
       <c r="P57" t="n">
-        <v>53.14</v>
+        <v>-530.01</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="n">
-        <v>4.64</v>
+        <v>-46.3</v>
       </c>
       <c r="S57" t="n">
-        <v>106.28</v>
+        <v>-1060.02</v>
       </c>
       <c r="T57" t="inlineStr"/>
     </row>
@@ -8983,14 +9043,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>9356</v>
+        <v>9355</v>
       </c>
       <c r="E60" t="n">
-        <v>0.06426999999999999</v>
+        <v>0.06350149652592196</v>
       </c>
       <c r="F60" t="n">
         <v>0.07548835965087614</v>
@@ -9000,35 +9060,39 @@
           <t>2026-07-30 17:18</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-08-03 01:06</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>706.27</v>
+        <v>706.1900000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>17.46</v>
+        <v>18.88</v>
       </c>
       <c r="K60" t="n">
-        <v>123.28</v>
+        <v>133.3</v>
       </c>
       <c r="L60" t="n">
-        <v>44.58</v>
+        <v>47.64</v>
       </c>
       <c r="M60" t="n">
-        <v>314.88</v>
+        <v>336.41</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="n">
-        <v>74.31</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="P60" t="n">
-        <v>524.79</v>
+        <v>560.6900000000001</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="n">
-        <v>148.61</v>
+        <v>158.79</v>
       </c>
       <c r="S60" t="n">
-        <v>1049.59</v>
+        <v>1121.37</v>
       </c>
       <c r="T60" t="inlineStr"/>
     </row>
@@ -9038,7 +9102,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PEOPLE</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -9047,48 +9111,48 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>653866.1</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>0.00653</v>
+        <v>0.06585000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>0.006940588409461815</v>
+        <v>0.07548835965087614</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-30 17:47</t>
+          <t>2026-07-30 17:18</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>4538.22</v>
+        <v>0.08</v>
       </c>
       <c r="J61" t="n">
-        <v>6.29</v>
+        <v>14.64</v>
       </c>
       <c r="K61" t="n">
-        <v>285.35</v>
+        <v>0.01</v>
       </c>
       <c r="L61" t="n">
-        <v>17.75</v>
+        <v>38.3</v>
       </c>
       <c r="M61" t="n">
-        <v>805.41</v>
+        <v>0.03</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="n">
-        <v>29.58</v>
+        <v>63.84</v>
       </c>
       <c r="P61" t="n">
-        <v>1342.35</v>
+        <v>0.05</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="n">
-        <v>59.16</v>
+        <v>127.68</v>
       </c>
       <c r="S61" t="n">
-        <v>2684.7</v>
+        <v>0.1</v>
       </c>
       <c r="T61" t="inlineStr"/>
     </row>
@@ -9098,61 +9162,57 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ROBO</t>
+          <t>PEOPLE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>220379</v>
+        <v>653866.1</v>
       </c>
       <c r="E62" t="n">
-        <v>0.01228</v>
+        <v>0.00712</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0135</v>
+        <v>0.006940588409461815</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-31 08:27</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>2026-07-31 16:30</t>
-        </is>
-      </c>
+          <t>2026-07-30 17:47</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>2975.12</v>
+        <v>4538.22</v>
       </c>
       <c r="J62" t="n">
-        <v>9.93</v>
+        <v>-2.52</v>
       </c>
       <c r="K62" t="n">
-        <v>295.57</v>
+        <v>-114.36</v>
       </c>
       <c r="L62" t="n">
-        <v>27.11</v>
+        <v>-7.75</v>
       </c>
       <c r="M62" t="n">
-        <v>806.59</v>
+        <v>-351.93</v>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
-        <v>45.19</v>
+        <v>-12.92</v>
       </c>
       <c r="P62" t="n">
-        <v>1344.31</v>
+        <v>-586.5599999999999</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="n">
-        <v>90.37</v>
+        <v>-25.85</v>
       </c>
       <c r="S62" t="n">
-        <v>2688.62</v>
+        <v>-1173.11</v>
       </c>
       <c r="T62" t="inlineStr"/>
     </row>
@@ -9171,7 +9231,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>110190</v>
+        <v>220379</v>
       </c>
       <c r="E63" t="n">
         <v>0.01228</v>
@@ -9190,33 +9250,33 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1487.57</v>
+        <v>2975.12</v>
       </c>
       <c r="J63" t="n">
         <v>9.93</v>
       </c>
       <c r="K63" t="n">
-        <v>147.79</v>
+        <v>295.57</v>
       </c>
       <c r="L63" t="n">
         <v>27.11</v>
       </c>
       <c r="M63" t="n">
-        <v>403.3</v>
+        <v>806.59</v>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
         <v>45.19</v>
       </c>
       <c r="P63" t="n">
-        <v>672.16</v>
+        <v>1344.31</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="n">
         <v>90.37</v>
       </c>
       <c r="S63" t="n">
-        <v>1344.32</v>
+        <v>2688.62</v>
       </c>
       <c r="T63" t="inlineStr"/>
     </row>
@@ -9226,57 +9286,61 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CFX</t>
+          <t>ROBO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>106828</v>
+        <v>110190</v>
       </c>
       <c r="E64" t="n">
-        <v>0.04294</v>
+        <v>0.01228</v>
       </c>
       <c r="F64" t="n">
-        <v>0.04149347287228067</v>
+        <v>0.0135</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-31 13:00</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>2026-07-31 08:27</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:30</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>4432.66</v>
+        <v>1487.57</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.37</v>
+        <v>9.93</v>
       </c>
       <c r="K64" t="n">
-        <v>-149.32</v>
+        <v>147.79</v>
       </c>
       <c r="L64" t="n">
-        <v>-10.46</v>
+        <v>27.11</v>
       </c>
       <c r="M64" t="n">
-        <v>-463.59</v>
+        <v>403.3</v>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
-        <v>-17.43</v>
+        <v>45.19</v>
       </c>
       <c r="P64" t="n">
-        <v>-772.65</v>
+        <v>672.16</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="n">
-        <v>-34.86</v>
+        <v>90.37</v>
       </c>
       <c r="S64" t="n">
-        <v>-1545.3</v>
+        <v>1344.32</v>
       </c>
       <c r="T64" t="inlineStr"/>
     </row>
@@ -9286,7 +9350,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GMT</t>
+          <t>CFX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9295,48 +9359,48 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>325667.9</v>
+        <v>106828</v>
       </c>
       <c r="E65" t="n">
-        <v>0.00663</v>
+        <v>0.04085</v>
       </c>
       <c r="F65" t="n">
-        <v>0.00676</v>
+        <v>0.04149347287228067</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-31 13:55</t>
+          <t>2026-07-31 13:00</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>2201.52</v>
+        <v>4432.66</v>
       </c>
       <c r="J65" t="n">
-        <v>1.96</v>
+        <v>1.58</v>
       </c>
       <c r="K65" t="n">
-        <v>43.17</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>5.77</v>
+        <v>4.65</v>
       </c>
       <c r="M65" t="n">
-        <v>127.01</v>
+        <v>206.22</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
-        <v>9.619999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="P65" t="n">
-        <v>211.68</v>
+        <v>343.7</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="n">
-        <v>19.23</v>
+        <v>15.51</v>
       </c>
       <c r="S65" t="n">
-        <v>423.37</v>
+        <v>687.41</v>
       </c>
       <c r="T65" t="inlineStr"/>
     </row>
@@ -9346,7 +9410,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SAGA</t>
+          <t>GMT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9355,48 +9419,48 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>339939.6</v>
+        <v>325667.9</v>
       </c>
       <c r="E66" t="n">
-        <v>0.01236</v>
+        <v>0.00657</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0126</v>
+        <v>0.00676</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-31 17:04</t>
+          <t>2026-07-31 13:55</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
-        <v>4283.24</v>
+        <v>2201.52</v>
       </c>
       <c r="J66" t="n">
-        <v>1.94</v>
+        <v>2.89</v>
       </c>
       <c r="K66" t="n">
-        <v>83.17</v>
+        <v>63.67</v>
       </c>
       <c r="L66" t="n">
-        <v>5.71</v>
+        <v>8.43</v>
       </c>
       <c r="M66" t="n">
-        <v>244.76</v>
+        <v>185.63</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
-        <v>9.52</v>
+        <v>14.05</v>
       </c>
       <c r="P66" t="n">
-        <v>407.93</v>
+        <v>309.38</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="n">
-        <v>19.05</v>
+        <v>28.11</v>
       </c>
       <c r="S66" t="n">
-        <v>815.86</v>
+        <v>618.77</v>
       </c>
       <c r="T66" t="inlineStr"/>
     </row>
@@ -9406,61 +9470,57 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FLOW</t>
+          <t>SAGA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>97950.02</v>
+        <v>339939.6</v>
       </c>
       <c r="E67" t="n">
-        <v>0.03081</v>
+        <v>0.01293</v>
       </c>
       <c r="F67" t="n">
-        <v>0.02804405102724839</v>
+        <v>0.0126</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-31 17:13</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>2026-07-31 23:28</t>
-        </is>
-      </c>
+          <t>2026-07-31 17:04</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
-        <v>2746.92</v>
+        <v>4283.24</v>
       </c>
       <c r="J67" t="n">
-        <v>-8.98</v>
+        <v>-2.55</v>
       </c>
       <c r="K67" t="n">
-        <v>-246.6</v>
+        <v>-109.32</v>
       </c>
       <c r="L67" t="n">
-        <v>-29.59</v>
+        <v>-7.86</v>
       </c>
       <c r="M67" t="n">
-        <v>-812.77</v>
+        <v>-336.54</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
-        <v>-49.31</v>
+        <v>-13.1</v>
       </c>
       <c r="P67" t="n">
-        <v>-1354.62</v>
+        <v>-560.9</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="n">
-        <v>-98.63</v>
+        <v>-26.19</v>
       </c>
       <c r="S67" t="n">
-        <v>-2709.25</v>
+        <v>-1121.8</v>
       </c>
       <c r="T67" t="inlineStr"/>
     </row>
@@ -9470,7 +9530,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TLM</t>
+          <t>FLOW</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9479,52 +9539,52 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>765466</v>
+        <v>97950.02</v>
       </c>
       <c r="E68" t="n">
-        <v>0.001648650814013947</v>
+        <v>0.03081</v>
       </c>
       <c r="F68" t="n">
-        <v>0.001873560456366487</v>
+        <v>0.02804405102724839</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-08-01 07:57</t>
+          <t>2026-07-31 17:13</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-01 10:31</t>
+          <t>2026-07-31 23:28</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1434.15</v>
+        <v>2746.92</v>
       </c>
       <c r="J68" t="n">
-        <v>13.64</v>
+        <v>-8.98</v>
       </c>
       <c r="K68" t="n">
-        <v>195.65</v>
+        <v>-246.6</v>
       </c>
       <c r="L68" t="n">
-        <v>36.01</v>
+        <v>-29.59</v>
       </c>
       <c r="M68" t="n">
-        <v>516.48</v>
+        <v>-812.77</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
-        <v>60.02</v>
+        <v>-49.31</v>
       </c>
       <c r="P68" t="n">
-        <v>860.8</v>
+        <v>-1354.62</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="n">
-        <v>120.04</v>
+        <v>-98.63</v>
       </c>
       <c r="S68" t="n">
-        <v>1721.61</v>
+        <v>-2709.25</v>
       </c>
       <c r="T68" t="inlineStr"/>
     </row>
@@ -9543,10 +9603,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>382734</v>
+        <v>765466</v>
       </c>
       <c r="E69" t="n">
-        <v>0.001648</v>
+        <v>0.001648650814013947</v>
       </c>
       <c r="F69" t="n">
         <v>0.001873560456366487</v>
@@ -9562,35 +9622,99 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>717.08</v>
+        <v>1434.15</v>
       </c>
       <c r="J69" t="n">
-        <v>13.69</v>
+        <v>13.64</v>
       </c>
       <c r="K69" t="n">
-        <v>98.15000000000001</v>
+        <v>195.65</v>
       </c>
       <c r="L69" t="n">
-        <v>36.12</v>
+        <v>36.01</v>
       </c>
       <c r="M69" t="n">
-        <v>258.99</v>
+        <v>516.48</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
-        <v>60.2</v>
+        <v>60.02</v>
       </c>
       <c r="P69" t="n">
-        <v>431.65</v>
+        <v>860.8</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="n">
+        <v>120.04</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1721.61</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>TLM</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>382734</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.001648</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.001873560456366487</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-08-01 07:57</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:31</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>717.08</v>
+      </c>
+      <c r="J70" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="K70" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="L70" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="M70" t="n">
+        <v>258.99</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="P70" t="n">
+        <v>431.65</v>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="n">
         <v>120.39</v>
       </c>
-      <c r="S69" t="n">
+      <c r="S70" t="n">
         <v>863.3</v>
       </c>
-      <c r="T69" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/leverage_journal.xlsx
+++ b/leverage_journal.xlsx
@@ -459,10 +459,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.18</v>
+        <v>186.23</v>
       </c>
       <c r="C2" t="n">
-        <v>47.8</v>
+        <v>47.1</v>
       </c>
       <c r="D2" t="inlineStr"/>
     </row>
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2227.31</v>
+        <v>2337.59</v>
       </c>
       <c r="C3" t="n">
-        <v>47.8</v>
+        <v>47.1</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -489,10 +489,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4713.47</v>
+        <v>4897.26</v>
       </c>
       <c r="C4" t="n">
-        <v>47.8</v>
+        <v>47.1</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23502.04</v>
+        <v>23869.43</v>
       </c>
       <c r="C5" t="n">
-        <v>47.8</v>
+        <v>47.1</v>
       </c>
       <c r="D5" t="n">
         <v>19</v>
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4937.17</v>
+        <v>4282.67</v>
       </c>
       <c r="C6" t="n">
-        <v>50.7</v>
+        <v>51.4</v>
       </c>
       <c r="D6" t="inlineStr"/>
     </row>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-274.85</v>
+        <v>-515.04</v>
       </c>
       <c r="C7" t="n">
-        <v>50.7</v>
+        <v>51.4</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>534.3200000000001</v>
+        <v>134.01</v>
       </c>
       <c r="C8" t="n">
-        <v>52.2</v>
+        <v>52.9</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12593.43</v>
+        <v>11792.73</v>
       </c>
       <c r="C9" t="n">
-        <v>52.2</v>
+        <v>52.9</v>
       </c>
       <c r="D9" t="n">
         <v>16</v>
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T70"/>
+  <dimension ref="A1:T71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,7 +713,7 @@
         <v>1.589</v>
       </c>
       <c r="F2" t="n">
-        <v>1.434</v>
+        <v>1.468</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -725,30 +725,30 @@
         <v>20.04</v>
       </c>
       <c r="J2" t="n">
-        <v>-9.75</v>
+        <v>-7.61</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.95</v>
+        <v>-1.53</v>
       </c>
       <c r="L2" t="n">
-        <v>-29.26</v>
+        <v>-22.84</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.86</v>
+        <v>-4.58</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>-48.77</v>
+        <v>-38.07</v>
       </c>
       <c r="P2" t="n">
-        <v>-9.77</v>
+        <v>-7.63</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>-97.55</v>
+        <v>-76.15000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>-19.55</v>
+        <v>-15.26</v>
       </c>
       <c r="T2" t="inlineStr"/>
     </row>
@@ -773,7 +773,7 @@
         <v>1.588</v>
       </c>
       <c r="F3" t="n">
-        <v>1.434</v>
+        <v>1.468</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -785,30 +785,30 @@
         <v>19.99</v>
       </c>
       <c r="J3" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.56</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.94</v>
+        <v>-1.51</v>
       </c>
       <c r="L3" t="n">
-        <v>-29.09</v>
+        <v>-22.67</v>
       </c>
       <c r="M3" t="n">
-        <v>-5.81</v>
+        <v>-4.53</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>-48.49</v>
+        <v>-37.78</v>
       </c>
       <c r="P3" t="n">
-        <v>-9.69</v>
+        <v>-7.55</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>-96.98</v>
+        <v>-75.56999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>-19.38</v>
+        <v>-15.1</v>
       </c>
       <c r="T3" t="inlineStr"/>
     </row>
@@ -833,7 +833,7 @@
         <v>1.59</v>
       </c>
       <c r="F4" t="n">
-        <v>1.434</v>
+        <v>1.468</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -845,30 +845,30 @@
         <v>20.01</v>
       </c>
       <c r="J4" t="n">
-        <v>-9.81</v>
+        <v>-7.67</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.96</v>
+        <v>-1.54</v>
       </c>
       <c r="L4" t="n">
-        <v>-29.43</v>
+        <v>-23.02</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.89</v>
+        <v>-4.61</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>-49.06</v>
+        <v>-38.36</v>
       </c>
       <c r="P4" t="n">
-        <v>-9.82</v>
+        <v>-7.68</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>-98.11</v>
+        <v>-76.73</v>
       </c>
       <c r="S4" t="n">
-        <v>-19.63</v>
+        <v>-15.35</v>
       </c>
       <c r="T4" t="inlineStr"/>
     </row>
@@ -2073,7 +2073,7 @@
         <v>2.68</v>
       </c>
       <c r="F23" t="n">
-        <v>2.258</v>
+        <v>2.272</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2085,23 +2085,23 @@
         <v>5.87</v>
       </c>
       <c r="J23" t="n">
-        <v>-15.75</v>
+        <v>-15.22</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.92</v>
+        <v>-0.89</v>
       </c>
       <c r="L23" t="n">
-        <v>-47.24</v>
+        <v>-45.67</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.77</v>
+        <v>-2.68</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>-78.73</v>
+        <v>-76.12</v>
       </c>
       <c r="P23" t="n">
-        <v>-4.62</v>
+        <v>-4.47</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
@@ -3693,7 +3693,7 @@
         <v>0.1769</v>
       </c>
       <c r="F48" t="n">
-        <v>0.043</v>
+        <v>0.0481</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
         <v>1502.06</v>
       </c>
       <c r="J48" t="n">
-        <v>-75.69</v>
+        <v>-72.81</v>
       </c>
       <c r="K48" t="n">
-        <v>-1136.94</v>
+        <v>-1093.64</v>
       </c>
       <c r="L48" t="n">
         <v>-100</v>
@@ -4277,7 +4277,7 @@
         <v>0.01825474902120262</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0191</v>
+        <v>0.01919</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -4289,30 +4289,30 @@
         <v>2289.31</v>
       </c>
       <c r="J57" t="n">
-        <v>4.63</v>
+        <v>5.12</v>
       </c>
       <c r="K57" t="n">
-        <v>106</v>
+        <v>117.29</v>
       </c>
       <c r="L57" t="n">
-        <v>13.89</v>
+        <v>15.37</v>
       </c>
       <c r="M57" t="n">
-        <v>318.01</v>
+        <v>351.87</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
-        <v>23.15</v>
+        <v>25.62</v>
       </c>
       <c r="P57" t="n">
-        <v>530.01</v>
+        <v>586.4400000000001</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="n">
-        <v>46.3</v>
+        <v>51.23</v>
       </c>
       <c r="S57" t="n">
-        <v>1060.02</v>
+        <v>1172.89</v>
       </c>
       <c r="T57" t="inlineStr"/>
     </row>
@@ -4533,7 +4533,7 @@
         <v>0.07548835965087614</v>
       </c>
       <c r="F61" t="n">
-        <v>0.06585000000000001</v>
+        <v>0.06219</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4545,23 +4545,23 @@
         <v>0.08</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.77</v>
+        <v>-17.62</v>
       </c>
       <c r="K61" t="n">
         <v>-0.01</v>
       </c>
       <c r="L61" t="n">
-        <v>-38.3</v>
+        <v>-52.85</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="n">
-        <v>-63.84</v>
+        <v>-88.08</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="n">
@@ -4597,7 +4597,7 @@
         <v>0.006940588409461815</v>
       </c>
       <c r="F62" t="n">
-        <v>0.00712</v>
+        <v>0.00711</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -4609,30 +4609,30 @@
         <v>4538.22</v>
       </c>
       <c r="J62" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="K62" t="n">
-        <v>117.31</v>
+        <v>110.77</v>
       </c>
       <c r="L62" t="n">
-        <v>7.75</v>
+        <v>7.32</v>
       </c>
       <c r="M62" t="n">
-        <v>351.93</v>
+        <v>332.32</v>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
-        <v>12.92</v>
+        <v>12.2</v>
       </c>
       <c r="P62" t="n">
-        <v>586.5599999999999</v>
+        <v>553.86</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="n">
-        <v>25.85</v>
+        <v>24.41</v>
       </c>
       <c r="S62" t="n">
-        <v>1173.11</v>
+        <v>1107.72</v>
       </c>
       <c r="T62" t="inlineStr"/>
     </row>
@@ -4785,7 +4785,7 @@
         <v>0.04149347287228067</v>
       </c>
       <c r="F65" t="n">
-        <v>0.04085</v>
+        <v>0.03884</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4797,30 +4797,30 @@
         <v>4432.66</v>
       </c>
       <c r="J65" t="n">
-        <v>-1.55</v>
+        <v>-6.39</v>
       </c>
       <c r="K65" t="n">
-        <v>-68.73999999999999</v>
+        <v>-283.47</v>
       </c>
       <c r="L65" t="n">
-        <v>-4.65</v>
+        <v>-19.18</v>
       </c>
       <c r="M65" t="n">
-        <v>-206.22</v>
+        <v>-850.4</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
-        <v>-7.75</v>
+        <v>-31.97</v>
       </c>
       <c r="P65" t="n">
-        <v>-343.7</v>
+        <v>-1417.33</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="n">
-        <v>-15.51</v>
+        <v>-63.95</v>
       </c>
       <c r="S65" t="n">
-        <v>-687.41</v>
+        <v>-2834.65</v>
       </c>
       <c r="T65" t="inlineStr"/>
     </row>
@@ -4845,7 +4845,7 @@
         <v>0.00676</v>
       </c>
       <c r="F66" t="n">
-        <v>0.00657</v>
+        <v>0.00671</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4857,30 +4857,30 @@
         <v>2201.52</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.81</v>
+        <v>-0.74</v>
       </c>
       <c r="K66" t="n">
-        <v>-61.88</v>
+        <v>-16.28</v>
       </c>
       <c r="L66" t="n">
-        <v>-8.43</v>
+        <v>-2.22</v>
       </c>
       <c r="M66" t="n">
-        <v>-185.63</v>
+        <v>-48.85</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
-        <v>-14.05</v>
+        <v>-3.7</v>
       </c>
       <c r="P66" t="n">
-        <v>-309.38</v>
+        <v>-81.42</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="n">
-        <v>-28.11</v>
+        <v>-7.4</v>
       </c>
       <c r="S66" t="n">
-        <v>-618.77</v>
+        <v>-162.83</v>
       </c>
       <c r="T66" t="inlineStr"/>
     </row>
@@ -4905,7 +4905,7 @@
         <v>0.0126</v>
       </c>
       <c r="F67" t="n">
-        <v>0.01293</v>
+        <v>0.01356</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4917,30 +4917,30 @@
         <v>4283.24</v>
       </c>
       <c r="J67" t="n">
-        <v>2.62</v>
+        <v>7.62</v>
       </c>
       <c r="K67" t="n">
-        <v>112.18</v>
+        <v>326.34</v>
       </c>
       <c r="L67" t="n">
-        <v>7.86</v>
+        <v>22.86</v>
       </c>
       <c r="M67" t="n">
-        <v>336.54</v>
+        <v>979.03</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
-        <v>13.1</v>
+        <v>38.1</v>
       </c>
       <c r="P67" t="n">
-        <v>560.9</v>
+        <v>1631.71</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="n">
-        <v>26.19</v>
+        <v>76.19</v>
       </c>
       <c r="S67" t="n">
-        <v>1121.8</v>
+        <v>3263.42</v>
       </c>
       <c r="T67" t="inlineStr"/>
     </row>
@@ -5143,6 +5143,66 @@
           <t>YES</t>
         </is>
       </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>716.3200000000001</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1.613</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.593</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-08-05 09:01</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>1155.42</v>
+      </c>
+      <c r="J71" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-14.33</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-3.72</v>
+      </c>
+      <c r="M71" t="n">
+        <v>-42.98</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="P71" t="n">
+        <v>-71.63</v>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="S71" t="n">
+        <v>-143.26</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5155,7 +5215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T70"/>
+  <dimension ref="A1:T71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5278,7 +5338,7 @@
         <v>12.61</v>
       </c>
       <c r="E2" t="n">
-        <v>1.434</v>
+        <v>1.468</v>
       </c>
       <c r="F2" t="n">
         <v>1.589</v>
@@ -5293,30 +5353,30 @@
         <v>20.04</v>
       </c>
       <c r="J2" t="n">
-        <v>10.81</v>
+        <v>8.24</v>
       </c>
       <c r="K2" t="n">
-        <v>2.17</v>
+        <v>1.65</v>
       </c>
       <c r="L2" t="n">
-        <v>29.26</v>
+        <v>22.84</v>
       </c>
       <c r="M2" t="n">
-        <v>5.86</v>
+        <v>4.58</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>48.77</v>
+        <v>38.07</v>
       </c>
       <c r="P2" t="n">
-        <v>9.77</v>
+        <v>7.63</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>97.55</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>19.55</v>
+        <v>15.26</v>
       </c>
       <c r="T2" t="inlineStr"/>
     </row>
@@ -5338,7 +5398,7 @@
         <v>12.586</v>
       </c>
       <c r="E3" t="n">
-        <v>1.434</v>
+        <v>1.468</v>
       </c>
       <c r="F3" t="n">
         <v>1.588</v>
@@ -5353,30 +5413,30 @@
         <v>19.99</v>
       </c>
       <c r="J3" t="n">
-        <v>10.74</v>
+        <v>8.17</v>
       </c>
       <c r="K3" t="n">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="L3" t="n">
-        <v>29.09</v>
+        <v>22.67</v>
       </c>
       <c r="M3" t="n">
-        <v>5.81</v>
+        <v>4.53</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>48.49</v>
+        <v>37.78</v>
       </c>
       <c r="P3" t="n">
-        <v>9.69</v>
+        <v>7.55</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>96.98</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>19.38</v>
+        <v>15.1</v>
       </c>
       <c r="T3" t="inlineStr"/>
     </row>
@@ -5398,7 +5458,7 @@
         <v>12.586</v>
       </c>
       <c r="E4" t="n">
-        <v>1.434</v>
+        <v>1.468</v>
       </c>
       <c r="F4" t="n">
         <v>1.59</v>
@@ -5413,30 +5473,30 @@
         <v>20.01</v>
       </c>
       <c r="J4" t="n">
-        <v>10.88</v>
+        <v>8.31</v>
       </c>
       <c r="K4" t="n">
-        <v>2.18</v>
+        <v>1.66</v>
       </c>
       <c r="L4" t="n">
-        <v>29.43</v>
+        <v>23.02</v>
       </c>
       <c r="M4" t="n">
-        <v>5.89</v>
+        <v>4.61</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>49.06</v>
+        <v>38.36</v>
       </c>
       <c r="P4" t="n">
-        <v>9.82</v>
+        <v>7.68</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>98.11</v>
+        <v>76.73</v>
       </c>
       <c r="S4" t="n">
-        <v>19.63</v>
+        <v>15.35</v>
       </c>
       <c r="T4" t="inlineStr"/>
     </row>
@@ -6634,7 +6694,7 @@
         <v>2.19</v>
       </c>
       <c r="E23" t="n">
-        <v>2.258</v>
+        <v>2.272</v>
       </c>
       <c r="F23" t="n">
         <v>2.68</v>
@@ -6649,30 +6709,30 @@
         <v>5.87</v>
       </c>
       <c r="J23" t="n">
-        <v>18.69</v>
+        <v>17.96</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="L23" t="n">
-        <v>47.24</v>
+        <v>45.67</v>
       </c>
       <c r="M23" t="n">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>78.73</v>
+        <v>76.12</v>
       </c>
       <c r="P23" t="n">
-        <v>4.62</v>
+        <v>4.47</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>157.46</v>
+        <v>152.24</v>
       </c>
       <c r="S23" t="n">
-        <v>9.24</v>
+        <v>8.94</v>
       </c>
       <c r="T23" t="inlineStr"/>
     </row>
@@ -8258,7 +8318,7 @@
         <v>8491</v>
       </c>
       <c r="E48" t="n">
-        <v>0.043</v>
+        <v>0.0481</v>
       </c>
       <c r="F48" t="n">
         <v>0.1769</v>
@@ -8273,30 +8333,30 @@
         <v>1502.06</v>
       </c>
       <c r="J48" t="n">
-        <v>311.4</v>
+        <v>267.78</v>
       </c>
       <c r="K48" t="n">
-        <v>4677.34</v>
+        <v>4022.14</v>
       </c>
       <c r="L48" t="n">
-        <v>227.08</v>
+        <v>218.43</v>
       </c>
       <c r="M48" t="n">
-        <v>3410.83</v>
+        <v>3280.92</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="n">
-        <v>378.46</v>
+        <v>364.05</v>
       </c>
       <c r="P48" t="n">
-        <v>5684.72</v>
+        <v>5468.2</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="n">
-        <v>756.92</v>
+        <v>728.09</v>
       </c>
       <c r="S48" t="n">
-        <v>11369.45</v>
+        <v>10936.41</v>
       </c>
       <c r="T48" t="inlineStr"/>
     </row>
@@ -8842,7 +8902,7 @@
         <v>125409</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0191</v>
+        <v>0.01919</v>
       </c>
       <c r="F57" t="n">
         <v>0.01825474902120262</v>
@@ -8857,30 +8917,30 @@
         <v>2289.31</v>
       </c>
       <c r="J57" t="n">
-        <v>-4.43</v>
+        <v>-4.87</v>
       </c>
       <c r="K57" t="n">
-        <v>-101.31</v>
+        <v>-111.57</v>
       </c>
       <c r="L57" t="n">
-        <v>-13.89</v>
+        <v>-15.37</v>
       </c>
       <c r="M57" t="n">
-        <v>-318.01</v>
+        <v>-351.87</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
-        <v>-23.15</v>
+        <v>-25.62</v>
       </c>
       <c r="P57" t="n">
-        <v>-530.01</v>
+        <v>-586.4400000000001</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="n">
-        <v>-46.3</v>
+        <v>-51.23</v>
       </c>
       <c r="S57" t="n">
-        <v>-1060.02</v>
+        <v>-1172.89</v>
       </c>
       <c r="T57" t="inlineStr"/>
     </row>
@@ -9114,7 +9174,7 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>0.06585000000000001</v>
+        <v>0.06219</v>
       </c>
       <c r="F61" t="n">
         <v>0.07548835965087614</v>
@@ -9129,30 +9189,30 @@
         <v>0.08</v>
       </c>
       <c r="J61" t="n">
-        <v>14.64</v>
+        <v>21.38</v>
       </c>
       <c r="K61" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L61" t="n">
-        <v>38.3</v>
+        <v>52.85</v>
       </c>
       <c r="M61" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="n">
-        <v>63.84</v>
+        <v>88.08</v>
       </c>
       <c r="P61" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="n">
-        <v>127.68</v>
+        <v>176.16</v>
       </c>
       <c r="S61" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="T61" t="inlineStr"/>
     </row>
@@ -9174,7 +9234,7 @@
         <v>653866.1</v>
       </c>
       <c r="E62" t="n">
-        <v>0.00712</v>
+        <v>0.00711</v>
       </c>
       <c r="F62" t="n">
         <v>0.006940588409461815</v>
@@ -9189,30 +9249,30 @@
         <v>4538.22</v>
       </c>
       <c r="J62" t="n">
-        <v>-2.52</v>
+        <v>-2.38</v>
       </c>
       <c r="K62" t="n">
-        <v>-114.36</v>
+        <v>-108.13</v>
       </c>
       <c r="L62" t="n">
-        <v>-7.75</v>
+        <v>-7.32</v>
       </c>
       <c r="M62" t="n">
-        <v>-351.93</v>
+        <v>-332.32</v>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
-        <v>-12.92</v>
+        <v>-12.2</v>
       </c>
       <c r="P62" t="n">
-        <v>-586.5599999999999</v>
+        <v>-553.86</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="n">
-        <v>-25.85</v>
+        <v>-24.41</v>
       </c>
       <c r="S62" t="n">
-        <v>-1173.11</v>
+        <v>-1107.72</v>
       </c>
       <c r="T62" t="inlineStr"/>
     </row>
@@ -9362,7 +9422,7 @@
         <v>106828</v>
       </c>
       <c r="E65" t="n">
-        <v>0.04085</v>
+        <v>0.03884</v>
       </c>
       <c r="F65" t="n">
         <v>0.04149347287228067</v>
@@ -9377,30 +9437,30 @@
         <v>4432.66</v>
       </c>
       <c r="J65" t="n">
-        <v>1.58</v>
+        <v>6.83</v>
       </c>
       <c r="K65" t="n">
-        <v>69.81999999999999</v>
+        <v>302.83</v>
       </c>
       <c r="L65" t="n">
-        <v>4.65</v>
+        <v>19.18</v>
       </c>
       <c r="M65" t="n">
-        <v>206.22</v>
+        <v>850.4</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
-        <v>7.75</v>
+        <v>31.97</v>
       </c>
       <c r="P65" t="n">
-        <v>343.7</v>
+        <v>1417.33</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="n">
-        <v>15.51</v>
+        <v>63.95</v>
       </c>
       <c r="S65" t="n">
-        <v>687.41</v>
+        <v>2834.65</v>
       </c>
       <c r="T65" t="inlineStr"/>
     </row>
@@ -9422,7 +9482,7 @@
         <v>325667.9</v>
       </c>
       <c r="E66" t="n">
-        <v>0.00657</v>
+        <v>0.00671</v>
       </c>
       <c r="F66" t="n">
         <v>0.00676</v>
@@ -9437,30 +9497,30 @@
         <v>2201.52</v>
       </c>
       <c r="J66" t="n">
-        <v>2.89</v>
+        <v>0.75</v>
       </c>
       <c r="K66" t="n">
-        <v>63.67</v>
+        <v>16.4</v>
       </c>
       <c r="L66" t="n">
-        <v>8.43</v>
+        <v>2.22</v>
       </c>
       <c r="M66" t="n">
-        <v>185.63</v>
+        <v>48.85</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
-        <v>14.05</v>
+        <v>3.7</v>
       </c>
       <c r="P66" t="n">
-        <v>309.38</v>
+        <v>81.42</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="n">
-        <v>28.11</v>
+        <v>7.4</v>
       </c>
       <c r="S66" t="n">
-        <v>618.77</v>
+        <v>162.83</v>
       </c>
       <c r="T66" t="inlineStr"/>
     </row>
@@ -9482,7 +9542,7 @@
         <v>339939.6</v>
       </c>
       <c r="E67" t="n">
-        <v>0.01293</v>
+        <v>0.01356</v>
       </c>
       <c r="F67" t="n">
         <v>0.0126</v>
@@ -9497,30 +9557,30 @@
         <v>4283.24</v>
       </c>
       <c r="J67" t="n">
-        <v>-2.55</v>
+        <v>-7.08</v>
       </c>
       <c r="K67" t="n">
-        <v>-109.32</v>
+        <v>-303.24</v>
       </c>
       <c r="L67" t="n">
-        <v>-7.86</v>
+        <v>-22.86</v>
       </c>
       <c r="M67" t="n">
-        <v>-336.54</v>
+        <v>-979.03</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
-        <v>-13.1</v>
+        <v>-38.1</v>
       </c>
       <c r="P67" t="n">
-        <v>-560.9</v>
+        <v>-1631.71</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="n">
-        <v>-26.19</v>
+        <v>-76.19</v>
       </c>
       <c r="S67" t="n">
-        <v>-1121.8</v>
+        <v>-3263.42</v>
       </c>
       <c r="T67" t="inlineStr"/>
     </row>
@@ -9715,6 +9775,66 @@
         <v>863.3</v>
       </c>
       <c r="T70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>716.3200000000001</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1.593</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.613</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-08-05 09:01</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>1155.42</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K71" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="L71" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="M71" t="n">
+        <v>42.98</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P71" t="n">
+        <v>71.63</v>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="S71" t="n">
+        <v>143.26</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
